--- a/A549_EGF/GO_Enrichment_Results.xlsx
+++ b/A549_EGF/GO_Enrichment_Results.xlsx
@@ -520,23 +520,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GO:0043230</t>
+          <t>GO:0065010</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>extracellular organelle</t>
+          <t>extracellular membrane-bounded organelle</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.613576936154198e-10</v>
+        <v>1.666290685460938e-10</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, occurring outside the cell. Includes, for example, extracellular membrane vesicles (EMVs) and the cellulosomes of anaerobic bacteria and fungi." [GOC:jl, PMID:9914479]</t>
+          <t>"Organized structure of distinctive morphology and function, bounded by a lipid bilayer membrane and occurring outside the cell." [GOC:isa_complete]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -549,7 +549,7 @@
         <v>135</v>
       </c>
       <c r="J2" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K2" t="n">
         <v>0.3292682926829268</v>
@@ -564,17 +564,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>['GO:0005576', 'GO:0043226']</t>
+          <t>['GO:0043227', 'GO:0043230']</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'AXL', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CSRP1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'LGALS1', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'PRDX4', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'LGALS3BP', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'CD44', 'UBB', 'TXNDC17', 'DSP', 'CNTN1', 'PGD', 'CTSL', 'EXOSC9', 'KRT18', 'GPRC5A', 'ALDH2', 'PLAU', 'ANXA2', 'AKR1B1', 'RPL34', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'TUBA4A', 'EPS8', 'ITM2B', 'BLVRB', 'VDAC3', 'PPP1CB', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'SFRP1', 'LGALS3', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'F12', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'IDH1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ARPC3', 'SLPI', 'PSME2', 'CAPZA1', 'VIM', 'KRT7', 'HGD', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'LDHB', 'KRT19', 'PTPRS', 'CLU', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'TAX1BP1', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'CDC42', 'TMC5']</t>
+          <t>['PRSS23', 'SERINC2', 'HSPE1', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'GCNT3', 'PA2G4', 'VDAC3', 'DSP', 'TXN', 'CD70', 'CDC42', 'CD9', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'SERPINE2', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'TUBA4A', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'RPL28', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'IDH1', 'GDF15', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'MUC5AC', 'SH3BGRL3', 'S100A4', 'EEF1A1', 'VIM', 'TXNRD1', 'PKM', 'PRDX1', 'LTA4H', 'HGD', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'UBB', 'UBC', 'RPL34', 'SLC12A2', 'CD63', 'CAPG', 'GSN', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'HPGD', 'COTL1', 'AKR1B1', 'NCL', 'ITM2B', 'TUBB', 'RAN', 'LGALS3BP', 'CCT5', 'NPC2', 'AXL', 'EIF4A1', 'HSP90AA1', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'TXNDC17', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'UPK1B', 'RAP2B', 'ALDH2', 'PSAT1', 'LDHB', 'ARPC3', 'PSME2', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'S100A16']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -586,23 +586,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GO:0065010</t>
+          <t>GO:1903561</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>extracellular membrane-bounded organelle</t>
+          <t>extracellular vesicle</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.613576936154198e-10</v>
+        <v>1.666290685460938e-10</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, bounded by a lipid bilayer membrane and occurring outside the cell." [GOC:isa_complete]</t>
+          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -615,7 +615,7 @@
         <v>135</v>
       </c>
       <c r="J3" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K3" t="n">
         <v>0.3292682926829268</v>
@@ -630,17 +630,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>['GO:0043227', 'GO:0043230']</t>
+          <t>['GO:0031982', 'GO:0065010']</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'AXL', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CSRP1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'LGALS1', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'PRDX4', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'LGALS3BP', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'CD44', 'UBB', 'TXNDC17', 'DSP', 'CNTN1', 'PGD', 'CTSL', 'EXOSC9', 'KRT18', 'GPRC5A', 'ALDH2', 'PLAU', 'ANXA2', 'AKR1B1', 'RPL34', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'TUBA4A', 'EPS8', 'ITM2B', 'BLVRB', 'VDAC3', 'PPP1CB', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'SFRP1', 'LGALS3', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'F12', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'IDH1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ARPC3', 'SLPI', 'PSME2', 'CAPZA1', 'VIM', 'KRT7', 'HGD', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'LDHB', 'KRT19', 'PTPRS', 'CLU', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'TAX1BP1', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'CDC42', 'TMC5']</t>
+          <t>['PRSS23', 'SERINC2', 'HSPE1', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'GCNT3', 'PA2G4', 'VDAC3', 'DSP', 'TXN', 'CD70', 'CDC42', 'CD9', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'SERPINE2', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'TUBA4A', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'RPL28', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'IDH1', 'GDF15', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'MUC5AC', 'SH3BGRL3', 'S100A4', 'EEF1A1', 'VIM', 'TXNRD1', 'PKM', 'PRDX1', 'LTA4H', 'HGD', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'UBB', 'UBC', 'RPL34', 'SLC12A2', 'CD63', 'CAPG', 'GSN', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'HPGD', 'COTL1', 'AKR1B1', 'NCL', 'ITM2B', 'TUBB', 'RAN', 'LGALS3BP', 'CCT5', 'NPC2', 'AXL', 'EIF4A1', 'HSP90AA1', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'TXNDC17', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'UPK1B', 'RAP2B', 'ALDH2', 'PSAT1', 'LDHB', 'ARPC3', 'PSME2', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'S100A16']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -652,23 +652,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GO:1903561</t>
+          <t>GO:0043230</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>extracellular vesicle</t>
+          <t>extracellular organelle</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.613576936154198e-10</v>
+        <v>1.666290685460938e-10</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
+          <t>"Organized structure of distinctive morphology and function, occurring outside the cell. Includes, for example, extracellular membrane vesicles (EMVs) and the cellulosomes of anaerobic bacteria and fungi." [GOC:jl, PMID:9914479]</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -681,7 +681,7 @@
         <v>135</v>
       </c>
       <c r="J4" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K4" t="n">
         <v>0.3292682926829268</v>
@@ -696,17 +696,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>['GO:0031982', 'GO:0065010']</t>
+          <t>['GO:0005576', 'GO:0043226']</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'AXL', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CSRP1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'LGALS1', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'PRDX4', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'LGALS3BP', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'CD44', 'UBB', 'TXNDC17', 'DSP', 'CNTN1', 'PGD', 'CTSL', 'EXOSC9', 'KRT18', 'GPRC5A', 'ALDH2', 'PLAU', 'ANXA2', 'AKR1B1', 'RPL34', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'TUBA4A', 'EPS8', 'ITM2B', 'BLVRB', 'VDAC3', 'PPP1CB', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'SFRP1', 'LGALS3', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'F12', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'IDH1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ARPC3', 'SLPI', 'PSME2', 'CAPZA1', 'VIM', 'KRT7', 'HGD', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'LDHB', 'KRT19', 'PTPRS', 'CLU', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'TAX1BP1', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'CDC42', 'TMC5']</t>
+          <t>['PRSS23', 'SERINC2', 'HSPE1', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'GCNT3', 'PA2G4', 'VDAC3', 'DSP', 'TXN', 'CD70', 'CDC42', 'CD9', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'SERPINE2', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'TUBA4A', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'RPL28', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'IDH1', 'GDF15', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'MUC5AC', 'SH3BGRL3', 'S100A4', 'EEF1A1', 'VIM', 'TXNRD1', 'PKM', 'PRDX1', 'LTA4H', 'HGD', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'UBB', 'UBC', 'RPL34', 'SLC12A2', 'CD63', 'CAPG', 'GSN', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'HPGD', 'COTL1', 'AKR1B1', 'NCL', 'ITM2B', 'TUBB', 'RAN', 'LGALS3BP', 'CCT5', 'NPC2', 'AXL', 'EIF4A1', 'HSP90AA1', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'TXNDC17', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'UPK1B', 'RAP2B', 'ALDH2', 'PSAT1', 'LDHB', 'ARPC3', 'PSME2', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'S100A16']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.670055150938487e-10</v>
+        <v>1.724276109242102e-10</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -747,7 +747,7 @@
         <v>134</v>
       </c>
       <c r="J5" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K5" t="n">
         <v>0.3268292682926829</v>
@@ -767,12 +767,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'AXL', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'MARCKSL1', 'PSAT1', 'PRSS23', 'HSPA2', 'CSRP1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'LGALS1', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'PRDX4', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'LGALS3BP', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'CD44', 'UBB', 'TXNDC17', 'DSP', 'CNTN1', 'PGD', 'CTSL', 'EXOSC9', 'KRT18', 'GPRC5A', 'ALDH2', 'PLAU', 'ANXA2', 'AKR1B1', 'RPL34', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'TUBA4A', 'EPS8', 'ITM2B', 'BLVRB', 'VDAC3', 'PPP1CB', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'SFRP1', 'LGALS3', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'F12', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'IDH1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ARPC3', 'SLPI', 'PSME2', 'CAPZA1', 'VIM', 'KRT7', 'HGD', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'LDHB', 'KRT19', 'PTPRS', 'CLU', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'TAX1BP1', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'CDC42', 'TMC5']</t>
+          <t>['PRSS23', 'SERINC2', 'HSPE1', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'GCNT3', 'PA2G4', 'VDAC3', 'DSP', 'TXN', 'CD70', 'CDC42', 'CD9', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'TUBA4A', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'RPL28', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'IDH1', 'GDF15', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'MUC5AC', 'SH3BGRL3', 'S100A4', 'EEF1A1', 'VIM', 'TXNRD1', 'PKM', 'PRDX1', 'LTA4H', 'HGD', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'UBB', 'UBC', 'RPL34', 'SLC12A2', 'CD63', 'CAPG', 'GSN', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'HPGD', 'COTL1', 'AKR1B1', 'NCL', 'ITM2B', 'TUBB', 'RAN', 'LGALS3BP', 'CCT5', 'NPC2', 'AXL', 'EIF4A1', 'HSP90AA1', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'TXNDC17', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'UPK1B', 'RAP2B', 'ALDH2', 'PSAT1', 'LDHB', 'ARPC3', 'PSME2', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'S100A16']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.106307387334968e-10</v>
+        <v>2.577348772214434e-10</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H6" t="n">
         <v>410</v>
       </c>
       <c r="I6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J6" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4463414634146342</v>
+        <v>0.4487804878048781</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2407894736842105</v>
+        <v>0.2417871222076216</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'AXL', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'CALM2', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'PMEPA1', 'CDA', 'GAL', 'TMSB4X', 'UPK1B', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CSRP1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'LGALS1', 'CYBA', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'RHOV', 'RAB31', 'NANS', 'SLC12A2', 'PRDX4', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'PRSS3', 'LGALS3BP', 'DKK1', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'GOLIM4', 'CD44', 'UBB', 'TXNDC17', 'PSMC2', 'DSP', 'CNTN1', 'SMAGP', 'PGD', 'CTSL', 'EXOSC9', 'GRAMD1A', 'KRT18', 'ANG', 'SKIL', 'GPRC5A', 'ALDH2', 'PLAU', 'GSDMD', 'GLIPR1', 'ANXA2', 'AKR1B1', 'RPL34', 'CAV1', 'ANTXR1', 'AP1M2', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'PLAUR', 'PCSK1N', 'TUBA4A', 'EPS8', 'CAV2', 'ITM2B', 'XRCC6', 'BLVRB', 'VDAC3', 'PPP1CB', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'SFRP1', 'LGALS3', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'MYL6', 'MMD', 'CD70', 'B4GALT1', 'BCL2L1', 'PRKCA', 'SPP1', 'CD63', 'CACNG8', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'GCHFR', 'OCIAD2', 'MFSD12', 'F12', 'AP1S2', 'PHLDA1', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'RHOD', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'IDH1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'TUBA1C', 'ARPC3', 'SLPI', 'ADA', 'PSME2', 'CAPZA1', 'NTS', 'ANP32E', 'SAR1A', 'VIM', 'KRT7', 'HGD', 'BASP1', 'TUBB4B', 'RPL31', 'MAGED2', 'RAB10', 'LDHB', 'RIN2', 'KRT19', 'PTPRS', 'CLU', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'HILPDA', 'TAX1BP1', 'GABARAPL1', 'CCT4', 'PRDX1', 'ITGA3', 'YPEL5', 'LITAF', 'DYNLL1', 'EEF1A1', 'ULK1', 'PTP4A1', 'CDC42', 'TMC5']</t>
+          <t>['PRSS23', 'SERINC2', 'HSPE1', 'CALM2', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'GCNT3', 'GAL', 'PA2G4', 'ULK1', 'VDAC3', 'DSP', 'TXN', 'CYBA', 'CD70', 'CDC42', 'CD9', 'MMD', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'PHLDA1', 'SERPINE2', 'DKK1', 'NTS', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'SKIL', 'TUBA4A', 'MFSD12', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'RPL28', 'AP1M2', 'RHOD', 'F12', 'FABP5', 'CDA', 'ACTG1', 'VAMP8', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'SAR1A', 'GCHFR', 'IDH1', 'GDF15', 'GRAMD1A', 'ANTXR1', 'HILPDA', 'SMAGP', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'PCSK1N', 'MUC5AC', 'CAV1', 'SH3BGRL3', 'GOLIM4', 'LITAF', 'S100A4', 'EEF1A1', 'VIM', 'TMSB4X', 'RIN2', 'TXNRD1', 'PKM', 'DYNLL1', 'PRDX1', 'LTA4H', 'HGD', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'ANG', 'YPEL5', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'RPL34', 'SLC12A2', 'CACNG8', 'CD63', 'CAPG', 'GSN', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'PSMC2', 'XRCC6', 'HPGD', 'COTL1', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'ADA', 'ITM2B', 'TUBB', 'MAGED2', 'RAN', 'LGALS3BP', 'CCT5', 'NPC2', 'CAV2', 'AXL', 'EIF4A1', 'ANP32E', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'AP1S2', 'TXNDC17', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'RAB31', 'ALDH1A1', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'PMEPA1', 'UPK1B', 'RAP2B', 'ALDH2', 'PSAT1', 'LDHB', 'ARPC3', 'RHOV', 'PSME2', 'PTP4A1', 'PRSS3', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'GABARAPL1', 'GLIPR1', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'S100A16']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['IEA'], ['HDA', 'IEA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['IDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['TAS'], ['IDA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['TAS'], ['IBA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'ISS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IDA', 'HDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['ISS', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IEA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.075991945221708e-08</v>
+        <v>8.703456824463748e-08</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="H7" t="n">
         <v>410</v>
       </c>
       <c r="I7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J7" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5170731707317073</v>
+        <v>0.5195121951219512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2203742203742204</v>
+        <v>0.2182377049180328</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'NOP58', 'GPX1', 'BIRC2', 'PLK1', 'ARL6IP1', 'S100A13', 'EIF4A1', 'GSN', 'AKR1C3', 'CALM2', 'LTA4H', 'NUDC', 'EIF2S3', 'RAD21', 'CDA', 'PINK1', 'TMSB4X', 'MAP1B', 'DDX21', 'NCAPD2', 'PSAT1', 'SERPINE2', 'HSPA2', 'CCND3', 'INPP1', 'NUDT19', 'YARS2', 'HMOX1', 'DDIT4', 'TRIB3', 'KRT8', 'ARL4C', 'GPX2', 'PKM', 'CTNNB1', 'SQSTM1', 'SSB', 'KIF18B', 'ALDH3A1', 'LGALS1', 'CDC20', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'ID2', 'RAB31', 'NANS', 'PRDX4', 'KRT81', 'RAP2B', 'PKMYT1', 'CDK1', 'AKAP12', 'RPL41', 'AURKA', 'UBE2S', 'POLR2L', 'EZR', 'RHOF', 'PPP1R14A', 'UMPS', 'CD44', 'CCNB2', 'JADE1', 'UBB', 'OAS1', 'TXNDC17', 'PSMC2', 'RPS27L', 'PGD', 'EXOSC9', 'GRAMD1A', 'KRT18', 'ANG', 'TYMP', 'LACTB', 'PGM2L1', 'NQO1', 'AKR1B10', 'GSDMD', 'KPNA2', 'ANXA2', 'AKR1B1', 'RPL34', 'AP1M2', 'TXNRD2', 'NT5E', 'ZFP36L1', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'DCAF13', 'TUBA4A', 'RPL38', 'CDKN1A', 'XRCC6', 'BLVRB', 'PMM2', 'PPP1CB', 'YARS', 'CALB2', 'ODC1', 'CCT5', 'RPLP2', 'AKR1C2', 'TXNRD1', 'SLBP', 'HNRNPH1', 'AKR1C1', 'RPS17', 'DOCK5', 'SFRP1', 'BIRC3', 'LGALS3', 'SLC7A5', 'RAN', 'HMGA1', 'MYL6', 'GIGYF1', 'BCL2L1', 'PRKCA', 'S100A4', 'UBE2L6', 'PFDN2', 'UBC', 'NAMPT', 'ACTB', 'UPP1', 'SAT1', 'AHNAK', 'GCHFR', 'HERC4', 'AP1S2', 'PHLDA1', 'MT2A', 'ATF4', 'ANXA5', 'ECH1', 'BAG1', 'HSP90AA1', 'RHOD', 'LDHA', 'MGLL', 'SNRPF', 'PSMC6', 'RPL28', 'CES1', 'PDLIM5', 'IDH1', 'HJURP', 'EIF3D', 'SPATS2', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ELF3', 'UCHL1', 'ARPC3', 'ADA', 'NEK6', 'MYBL2', 'PSME2', 'CAPZA1', 'PTTG1', 'SAR1A', 'VIM', 'AHNAK2', 'KRT7', 'RGS2', 'HGD', 'PSMC4', 'TPM1', 'CPLX2', 'PRMT1', 'RPS4Y1', 'SET', 'TUBB4B', 'RPL31', 'AURKB', 'MAGED2', 'KYNU', 'RAB10', 'CTNNBL1', 'TSC22D1', 'LDHB', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'BIRC5', 'PTGES3', 'S100A16', 'CCT3', 'CCND1', 'HILPDA', 'TAX1BP1', 'GABARAPL1', 'CCT4', 'PRDX1', 'C19orf33', 'DYNLL1', 'EEF1A1', 'ULK1', 'CCNB1', 'CDC42']</t>
+          <t>['ALDH3A1', 'BIRC3', 'CALM2', 'PKMYT1', 'AKR1C1', 'DDIT4', 'KPNA2', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'ULK1', 'PFDN2', 'TXN', 'PINK1', 'AURKA', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SPATS2', 'SQSTM1', 'AHNAK2', 'ARL6IP1', 'UMPS', 'NANS', 'RPS27L', 'EIF3D', 'KIF18B', 'PHLDA1', 'SNRPF', 'SERPINE2', 'AKR1C3', 'PSMC6', 'ARL4C', 'PGM2L1', 'CTNNBL1', 'AKAP12', 'SAT1', 'POLR2L', 'TUBA4A', 'SFRP1', 'HERC4', 'RPLP2', 'LACTB', 'HMOX1', 'JADE1', 'RPL28', 'PDLIM5', 'AP1M2', 'RHOD', 'FABP5', 'YARS', 'HJURP', 'CDA', 'RPL41', 'ACTG1', 'VAMP8', 'S100A6', 'SAR1A', 'GCHFR', 'GIGYF1', 'OAS1', 'CDKN1A', 'IDH1', 'CCNB1', 'MGLL', 'RGS2', 'GRAMD1A', 'HILPDA', 'KIF23', 'CLU', 'SLC7A5', 'PPP1R14A', 'NEK6', 'YARS2', 'ODC1', 'RSL1D1', 'PRMT1', 'NQO1', 'NUDT19', 'SH3BGRL3', 'TPM1', 'RPL38', 'MT2A', 'UPP1', 'CCND1', 'UCHL1', 'ID2', 'S100A4', 'EEF1A1', 'VIM', 'PTGES3', 'TMSB4X', 'DDX21', 'RIN2', 'TXNRD1', 'TXNRD2', 'PKM', 'S100A13', 'DYNLL1', 'PRDX1', 'LTA4H', 'HGD', 'KRT81', 'MYL6', 'PSMA4', 'PPP1CB', 'NOP58', 'TRIB3', 'PTPRS', 'CES1', 'ANG', 'MYBL2', 'EZR', 'PTTG1', 'UBE2L6', 'HSPA2', 'RAB10', 'KYNU', 'UBB', 'UBC', 'BCL2L1', 'RPL34', 'AKR1C2', 'GPX1', 'ZFP36L1', 'RPS17', 'GSN', 'SET', 'C19orf33', 'CCT3', 'NAMPT', 'CDK1', 'DOCK5', 'UBE2S', 'NCAPD2', 'AURKB', 'PSMC2', 'XRCC6', 'HPGD', 'COTL1', 'AKR1B1', 'ADA', 'GPX2', 'TUBB', 'MAGED2', 'RAN', 'CCT5', 'EIF4A1', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'DCAF13', 'TAX1BP1', 'PRDX4', 'HSP90AB1', 'NT5E', 'BLVRB', 'AP1S2', 'CALB2', 'AKR1B10', 'TXNDC17', 'GSTO1', 'SLBP', 'CTNNB1', 'CCNB2', 'RAB31', 'ALDH1A1', 'HNRNPH1', 'BIRC2', 'RPL31', 'BAG1', 'SSB', 'PGD', 'TYMP', 'BIRC5', 'CAPZA1', 'KRT7', 'RAP2B', 'PSAT1', 'LDHB', 'ARPC3', 'PSME2', 'ELF3', 'PMM2', 'ATF4', 'HMGA1', 'RAD21', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'GABARAPL1', 'MAP1B', 'CDC20', 'INPP1', 'KRT18', 'RPS4Y1', 'ECH1', 'MYL12A', 'PLK1', 'TSC22D1', 'S100A16', 'CPLX2']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['TAS'], ['TAS'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'ISS', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IBA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'NAS'], ['IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IBA'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA']]</t>
+          <t>[['IDA', 'ISS', 'TAS'], ['IDA', 'TAS'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'ISS', 'TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['ISS', 'IEA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'IBA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'TAS', 'NAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA'], ['IDA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.06655121501337e-06</v>
+        <v>5.043475371432832e-07</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -942,16 +942,16 @@
         <v>410</v>
       </c>
       <c r="I8" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J8" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3926829268292683</v>
+        <v>0.3951219512195122</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2343522561863173</v>
+        <v>0.2358078602620087</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -965,59 +965,59 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'ADM', 'TSKU', 'AXL', 'S100A13', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'GAL', 'UPK1B', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CSRP1', 'HMOX1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'ALDH3A1', 'LGALS1', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'PRDX4', 'KRT81', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'PRSS3', 'LGALS3BP', 'DKK1', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'CD44', 'CCL2', 'UBB', 'TXNDC17', 'DSP', 'CNTN1', 'PGD', 'CTSL', 'EXOSC9', 'KRT18', 'ANG', 'IGFBP4', 'GPRC5A', 'ALDH2', 'PLAU', 'GSDMD', 'GLIPR1', 'ANXA2', 'AKR1B1', 'RPL34', 'NT5E', 'MTHFD2', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'PCSK1N', 'TUBA4A', 'EPS8', 'ITM2B', 'BLVRB', 'VDAC3', 'PPP1CB', 'YARS', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'HMGB2', 'AGR2', 'SFRP1', 'LGALS3', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'CXCL5', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'F12', 'CRELD2', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'IDH1', 'TFF1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ARPC3', 'SLPI', 'PSME2', 'CAPZA1', 'VIM', 'KRT7', 'HGD', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'LDHB', 'KRT19', 'PTPRS', 'CLU', 'NMB', 'S100A16', 'S100A10', 'CXCL3', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'INSL4', 'HILPDA', 'TAX1BP1', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'CDC42', 'TMC5']</t>
+          <t>['ALDH3A1', 'PRSS23', 'SERINC2', 'HSPE1', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'TFF1', 'GCNT3', 'GAL', 'PA2G4', 'VDAC3', 'DSP', 'TXN', 'CD70', 'CDC42', 'CD9', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'RSPO3', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'SERPINE2', 'DKK1', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'CRELD2', 'TUBA4A', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'HMOX1', 'RPL28', 'F12', 'FABP5', 'YARS', 'ACTG1', 'VAMP8', 'CXCL3', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'IDH1', 'GDF15', 'HILPDA', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'PCSK1N', 'MUC5AC', 'SH3BGRL3', 'S100A4', 'EEF1A1', 'VIM', 'INSL4', 'TSKU', 'TXNRD1', 'PKM', 'S100A13', 'PRDX1', 'LTA4H', 'HGD', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'ANG', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'ADM', 'UBB', 'UBC', 'RPL34', 'SLC12A2', 'CD63', 'CAPG', 'GSN', 'CXCL5', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'HPGD', 'COTL1', 'AKR1B1', 'NCL', 'ITM2B', 'TUBB', 'RAN', 'LGALS3BP', 'CCT5', 'CCL2', 'NPC2', 'AXL', 'EIF4A1', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'TXNDC17', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'IGFBP4', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'UPK1B', 'RAP2B', 'ALDH2', 'PSAT1', 'AGR2', 'LDHB', 'MTHFD2', 'ARPC3', 'PSME2', 'PRSS3', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'GLIPR1', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'NMB', 'S100A16']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['ISS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['ISS'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IMP', 'HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['IBA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['ISS'], ['IDA', 'HDA', 'IBA']]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GO:MF</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GO:0003723</t>
+          <t>GO:0005576</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RNA binding</t>
+          <t>extracellular region</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.133357880722101e-06</v>
+        <v>2.49896165633235e-06</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>"Binding to an RNA molecule or a portion thereof." [GOC:jl, GOC:mah]</t>
+          <t>"The space external to the outermost structure of a cell. For cells without external protective or external encapsulating structures this refers to space outside of the plasma membrane. This term covers the host cell environment outside an intracellular parasite." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>264</v>
+        <v>792</v>
       </c>
       <c r="H9" t="n">
         <v>410</v>
       </c>
       <c r="I9" t="n">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="J9" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.4341463414634146</v>
       </c>
       <c r="L9" t="n">
-        <v>0.303030303030303</v>
+        <v>0.2247474747474748</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1026,64 +1026,64 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>['GO:0003676']</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'NOP58', 'EIF4A1', 'LTA4H', 'EIF2S3', 'RAD21', 'TOP2A', 'TMSB4X', 'DDX21', 'CSRP1', 'YARS2', 'PKM', 'PUS1', 'EBNA1BP2', 'SSB', 'RRS1', 'LGALS1', 'LYAR', 'SLC16A3', 'TUBA1B', 'DDX10', 'RPL41', 'EZR', 'OAS1', 'UNC50', 'DSP', 'RPS27L', 'NOL7', 'EXOSC9', 'KRT18', 'ANG', 'NR0B1', 'NQO1', 'KPNA2', 'ANXA2', 'RPL34', 'SART3', 'ZFP36L1', 'YWHAE', 'TXN', 'DCAF13', 'RPL38', 'MYC', 'XRCC6', 'YARS', 'CCT5', 'SLBP', 'HNRNPH1', 'HMGB2', 'RPS17', 'LGALS3', 'RAN', 'HMGA1', 'NCL', 'RPL22L1', 'S100A4', 'UBC', 'AHNAK', 'HSP90AA1', 'HSPE1', 'SNRPF', 'RPL28', 'EIF3D', 'SPATS2', 'BICC1', 'SLPI', 'RSL1D1', 'VIM', 'PRMT1', 'RPS4Y1', 'TUBB4B', 'RPL31', 'LACTB2', 'ISG20', 'S100A16', 'PA2G4', 'CCT3', 'CCT4', 'PRDX1', 'EEF1A1']</t>
+          <t>['ALDH3A1', 'C1orf56', 'PRSS23', 'SERINC2', 'HSPE1', 'MFGE8', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'TFF1', 'GCNT3', 'GAL', 'PA2G4', 'VDAC3', 'DSP', 'TXN', 'CD70', 'CDC42', 'CD9', 'B4GALT1', 'CCT4', 'CPNE7', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'RSPO3', 'SQSTM1', 'SERPINB1', 'NANS', 'EPS8', 'SERPINE2', 'DKK1', 'NTS', 'AKR1C3', 'TMC5', 'PSMC6', 'CSRP1', 'CRELD2', 'TUBA4A', 'SFRP1', 'RPLP2', 'C1GALT1C1', 'HMOX1', 'RPL28', 'F12', 'FABP5', 'YARS', 'CDA', 'ACTG1', 'VAMP8', 'CXCL3', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'OAS1', 'IDH1', 'GDF15', 'HILPDA', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'SPAG16', 'PCSK1N', 'MUC5AC', 'SH3BGRL3', 'S100A4', 'EEF1A1', 'VIM', 'INSL4', 'TMSB4X', 'TSKU', 'TXNRD1', 'PKM', 'S100A13', 'PRDX1', 'LTA4H', 'HGD', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'PTPRS', 'ANG', 'YPEL5', 'EZR', 'HSPA2', 'RAB10', 'S100A10', 'ITGB4', 'ADM', 'UBB', 'UBC', 'RPL34', 'SLC12A2', 'CD63', 'CAPG', 'GSN', 'CXCL5', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'PSMC2', 'XRCC6', 'HPGD', 'COTL1', 'AKR1B1', 'NCL', 'PLAUR', 'ITM2B', 'TUBB', 'MAGED2', 'RAN', 'LGALS3BP', 'CCT5', 'CCL2', 'NPC2', 'AXL', 'EIF4A1', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'AKR1B10', 'TXNDC17', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'IGFBP4', 'JAG1', 'SPP1', 'RPL31', 'PGD', 'CAPZA1', 'KRT7', 'UPK1B', 'RAP2B', 'EVA1C', 'ALDH2', 'PSAT1', 'AGR2', 'LDHB', 'MTHFD2', 'ARPC3', 'PSME2', 'B4GALT4', 'PRSS3', 'ACTB', 'RHOF', 'LDHA', 'ANXA5', 'YWHAE', 'NRP2', 'GLIPR1', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'NMB', 'S100A16']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['IDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IPI'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA']]</t>
+          <t>[['HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['ISS', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'TAS'], ['ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['NAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA']]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:MF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GO:0005576</t>
+          <t>GO:0003723</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>extracellular region</t>
+          <t>RNA binding</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.734144180170454e-06</v>
+        <v>4.137268377600854e-06</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>"The space external to the outermost structure of a cell. For cells without external protective or external encapsulating structures this refers to space outside of the plasma membrane. This term covers the host cell environment outside an intracellular parasite." [GOC:go_curators]</t>
+          <t>"Binding to an RNA molecule or a portion thereof." [GOC:jl, GOC:mah]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>793</v>
+        <v>267</v>
       </c>
       <c r="H10" t="n">
         <v>410</v>
       </c>
       <c r="I10" t="n">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="J10" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4341463414634146</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2244640605296343</v>
+        <v>0.299625468164794</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1092,17 +1092,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0003676']</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'ADM', 'TSKU', 'AXL', 'S100A13', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'LTA4H', 'RTN4RL2', 'EIF2S3', 'CDA', 'GAL', 'TMSB4X', 'UPK1B', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CSRP1', 'HMOX1', 'GDF15', 'KRT8', 'PKM', 'CTNNB1', 'SQSTM1', 'S100A11', 'ALDH3A1', 'LGALS1', 'COTL1', 'PSMA4', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'PRDX4', 'KRT81', 'FN1', 'RAP2B', 'CPNE7', 'C1GALT1C1', 'CDK1', 'PRSS3', 'LGALS3BP', 'DKK1', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'CD44', 'CCL2', 'UBB', 'OAS1', 'TXNDC17', 'PSMC2', 'DSP', 'CNTN1', 'PGD', 'CTSL', 'EXOSC9', 'KRT18', 'ANG', 'IGFBP4', 'AKR1B10', 'GPRC5A', 'ALDH2', 'PLAU', 'GSDMD', 'GLIPR1', 'ANXA2', 'AKR1B1', 'RPL34', 'NT5E', 'MTHFD2', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'PLAUR', 'PCSK1N', 'C1orf56', 'TUBA4A', 'EPS8', 'ITM2B', 'XRCC6', 'BLVRB', 'VDAC3', 'PPP1CB', 'YARS', 'EVA1C', 'CCT5', 'RPLP2', 'TXNRD1', 'AKR1C1', 'HMGB2', 'B4GALT4', 'AGR2', 'SFRP1', 'LGALS3', 'SLC7A5', 'JAG1', 'RAN', 'NCL', 'MFGE8', 'CXCL5', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBC', 'NAMPT', 'ACTB', 'AHNAK', 'F12', 'CRELD2', 'CAPG', 'GCNT3', 'ANXA5', 'SERPINB1', 'ECH1', 'HSP90AA1', 'LDHA', 'HSPE1', 'PSMC6', 'RPL28', 'SPAG16', 'IDH1', 'TFF1', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ARPC3', 'SLPI', 'PSME2', 'CAPZA1', 'NTS', 'VIM', 'KRT7', 'HGD', 'NRP2', 'BASP1', 'TUBB4B', 'RPL31', 'MAGED2', 'RSPO3', 'RAB10', 'LDHB', 'KRT19', 'PTPRS', 'CLU', 'NMB', 'S100A16', 'S100A10', 'CXCL3', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'INSL4', 'HILPDA', 'TAX1BP1', 'CCT4', 'PRDX1', 'ITGA3', 'YPEL5', 'EEF1A1', 'CDC42', 'TMC5']</t>
+          <t>['HSPE1', 'RRS1', 'KPNA2', 'EXOSC9', 'LGALS1', 'SLC16A3', 'PA2G4', 'DSP', 'TXN', 'NR0B1', 'UNC50', 'CCT4', 'AHNAK', 'MYC', 'LGALS3', 'EIF2S3', 'ANXA2', 'SPATS2', 'RPS27L', 'EIF3D', 'SNRPF', 'LYAR', 'CSRP1', 'RPL28', 'BICC1', 'YARS', 'EBNA1BP2', 'RPL41', 'ISG20', 'OAS1', 'YARS2', 'DDX10', 'RSL1D1', 'PRMT1', 'NQO1', 'RPL38', 'S100A4', 'EEF1A1', 'VIM', 'TMSB4X', 'DDX21', 'PKM', 'PRDX1', 'LTA4H', 'HMGB2', 'RPL22L1', 'SLPI', 'NOP58', 'NOL7', 'ANG', 'EZR', 'UBC', 'RPL34', 'ZFP36L1', 'RPS17', 'CCT3', 'XRCC6', 'NCL', 'RAN', 'CCT5', 'EIF4A1', 'HSP90AA1', 'TUBB4B', 'DCAF13', 'HSP90AB1', 'SLBP', 'HNRNPH1', 'RPL31', 'SSB', 'TOP2A', 'PUS1', 'HMGA1', 'RAD21', 'YWHAE', 'SART3', 'LACTB2', 'KRT18', 'RPS4Y1', 'TUBA1B', 'S100A16']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['NAS'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IPI'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.162719792925337e-05</v>
+        <v>2.096177523729233e-05</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -1134,22 +1134,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1931</v>
+        <v>1942</v>
       </c>
       <c r="H11" t="n">
         <v>410</v>
       </c>
       <c r="I11" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J11" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8365853658536585</v>
+        <v>0.8439024390243902</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1776281719316416</v>
+        <v>0.1781668383110196</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'NOP58', 'GPX1', 'ADM', 'BIRC2', 'PLK1', 'NDUFB4', 'ARL6IP1', 'UCP2', 'S100A13', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'CALM2', 'LTA4H', 'NUDC', 'EIF2S3', 'FADS1', 'PMEPA1', 'RAD21', 'TOP2A', 'CDA', 'GAL', 'PINK1', 'TMSB4X', 'FDXR', 'MAP1B', 'DDX21', 'NCAPD2', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CCND3', 'GADD45B', 'INPP1', 'CSRP1', 'ID1', 'NUDT19', 'YARS2', 'HMOX1', 'GDF15', 'DDIT4', 'FKBP11', 'PMPCB', 'TRIB3', 'ALG8', 'KRT8', 'ARL4C', 'CEBPB', 'GPX2', 'PKM', 'CTNNB1', 'PUS1', 'SQSTM1', 'S100A11', 'SSB', 'KIF18B', 'ALDH3A1', 'RRS1', 'LGALS1', 'LYAR', 'CDC20', 'CYBA', 'COTL1', 'DHRS3', 'PSMA4', 'FABP5', 'TUBB', 'PLEK2', 'ID2', 'RHOV', 'RAB31', 'NANS', 'SLC12A2', 'PRDX4', 'TUBA1B', 'KRT81', 'PWP1', 'MCU', 'NDUFA4', 'FN1', 'RAP2B', 'ID3', 'CPNE7', 'C1GALT1C1', 'PKMYT1', 'CDK1', 'PRSS3', 'AKAP12', 'RPL41', 'AURKA', 'CYP1B1', 'LGALS3BP', 'UBE2S', 'PLPP5', 'HCFC1R1', 'DKK1', 'POLR2L', 'EZR', 'RHOF', 'GOLIM4', 'PPP1R14A', 'TOR1AIP2', 'UMPS', 'CD44', 'NUPR1', 'CCNB2', 'GAL3ST1', 'JADE1', 'UBB', 'OAS1', 'TXNDC17', 'TPPP3', 'UNC50', 'PSMC2', 'DSP', 'SMAGP', 'RPS27L', 'SLC39A8', 'PGD', 'CTSL', 'NOL7', 'EXOSC9', 'GRAMD1A', 'KRT18', 'ANG', 'TYMP', 'LACTB', 'IGFBP4', 'SKIL', 'DUSP1', 'NR0B1', 'PGM2L1', 'NQO1', 'AKR1B10', 'GPRC5A', 'ALDH2', 'PLAU', 'GSDMD', 'KPNA2', 'HES1', 'GLIPR1', 'ANXA2', 'AKR1B1', 'TMBIM6', 'RPL34', 'CAV1', 'ANTXR1', 'AP1M2', 'TXNRD2', 'NT5E', 'SART3', 'ZFP36L1', 'MTHFD2', 'YWHAE', 'CDC123', 'TXN', 'S100A6', 'ALDH1A1', 'CYP24A1', 'DCAF13', 'PLAUR', 'PCSK1N', 'TUBA4A', 'RPL38', 'MYC', 'EPS8', 'CAV2', 'ITM2B', 'CDKN1A', 'XRCC6', 'BLVRB', 'VDAC3', 'PMM2', 'PPP1CB', 'YARS', 'CALB2', 'ODC1', 'CCT5', 'RPLP2', 'AKR1C2', 'TXNRD1', 'EGR1', 'SLBP', 'LRRC75A', 'HNRNPH1', 'AKR1C1', 'HMGB2', 'RPS17', 'B4GALT4', 'AGR2', 'DOCK5', 'SFRP1', 'BIRC3', 'LGALS3', 'SLC7A5', 'RAN', 'HMGA1', 'NCL', 'MFGE8', 'MYL6', 'GIGYF1', 'MMD', 'B4GALT1', 'BCL2L1', 'PRKCA', 'SPP1', 'CD63', 'CACNG8', 'S100A4', 'UBE2L6', 'PFDN2', 'IGFBP7', 'CRIP2', 'B4GALT5', 'UBC', 'NAMPT', 'ACTB', 'UPP1', 'ORMDL2', 'SAT1', 'COX14', 'AHNAK', 'NDUFS2', 'GCHFR', 'HERC4', 'COX17', 'OCIAD2', 'MFSD12', 'F12', 'CRELD2', 'AP1S2', 'PHLDA1', 'CAPG', 'MT2A', 'ATF4', 'GCNT3', 'ANXA5', 'SERPINB1', 'IK', 'ECH1', 'BAG1', 'PIF1', 'HSP90AA1', 'RHOD', 'LDHA', 'MGLL', 'HSPE1', 'SNRPF', 'PSMC6', 'RPL28', 'CES1', 'SPAG16', 'PDLIM5', 'IDH1', 'HJURP', 'EIF3D', 'SPATS2', 'GSTO1', 'HPGD', 'VAMP8', 'BICC1', 'MYL12A', 'ELF3', 'UCHL1', 'TUBA1C', 'ARPC3', 'HERPUD1', 'SLPI', 'ADA', 'NEK6', 'MYBL2', 'PSME2', 'CAPZA1', 'NTS', 'ANP32E', 'PTTG1', 'SAR1A', 'RNF26', 'VIM', 'AHNAK2', 'KRT7', 'RGS2', 'HGD', 'EPHX1', 'PSMC4', 'TPM1', 'BASP1', 'CPLX2', 'PRMT1', 'RPS4Y1', 'SET', 'TUBB4B', 'RPL31', 'PERP', 'AURKB', 'MAGED2', 'KYNU', 'RAB10', 'CTNNBL1', 'TSC22D1', 'LDHB', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'BIRC5', 'PTGES3', 'LACTB2', 'ISG20', 'S100A16', 'S100A10', 'NPC2', 'PA2G4', 'CCT3', 'CCND1', 'MRPS22', 'HILPDA', 'TAX1BP1', 'GABARAPL1', 'CCT4', 'PRDX1', 'ITGA3', 'CLSPN', 'YPEL5', 'BTG1', 'C19orf33', 'LITAF', 'TM4SF20', 'DYNLL1', 'EEF1A1', 'ULK1', 'TMPO', 'CCNB1', 'PTP4A1', 'CDC42']</t>
+          <t>['ALDH3A1', 'BIRC3', 'PRSS23', 'HSPE1', 'CALM2', 'PKMYT1', 'RRS1', 'MFGE8', 'IGFBP7', 'HES1', 'NDUFS2', 'AKR1C1', 'DDIT4', 'KPNA2', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'ULK1', 'CYP1B1', 'PFDN2', 'LRRC75A', 'VDAC3', 'DSP', 'TXN', 'NR0B1', 'ID3', 'CYBA', 'UNC50', 'PINK1', 'CLSPN', 'AURKA', 'PLEK2', 'CDC42', 'CD9', 'MMD', 'B4GALT1', 'CEBPB', 'CCT4', 'CPNE7', 'AHNAK', 'MYC', 'LGALS3', 'EIF2S3', 'ANXA2', 'SPATS2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'ARL6IP1', 'UMPS', 'NANS', 'RPS27L', 'EPHX1', 'EPS8', 'EIF3D', 'KIF18B', 'PHLDA1', 'SNRPF', 'SERPINE2', 'DKK1', 'NTS', 'AKR1C3', 'PSMC6', 'ARL4C', 'PGM2L1', 'CTNNBL1', 'LYAR', 'AKAP12', 'CSRP1', 'SAT1', 'CRELD2', 'SKIL', 'POLR2L', 'TUBA4A', 'FADS1', 'PWP1', 'MFSD12', 'B4GALT5', 'SFRP1', 'DHRS3', 'HERC4', 'RPLP2', 'LACTB', 'C1GALT1C1', 'HMOX1', 'JADE1', 'TM4SF20', 'RPL28', 'PDLIM5', 'BICC1', 'GAL3ST1', 'AP1M2', 'RHOD', 'F12', 'FABP5', 'YARS', 'HJURP', 'CDA', 'RPL41', 'ACTG1', 'ISG20', 'VAMP8', 'CTSL', 'S100A6', 'MARCKSL1', 'BASP1', 'SAR1A', 'GCHFR', 'GIGYF1', 'OAS1', 'CDKN1A', 'IDH1', 'GDF15', 'DUSP1', 'CCNB1', 'MGLL', 'RGS2', 'GRAMD1A', 'ANTXR1', 'HILPDA', 'ID1', 'SMAGP', 'KIF23', 'CLU', 'ITGA3', 'SLC7A5', 'GPRC5A', 'PPP1R14A', 'NEK6', 'SPAG16', 'YARS2', 'PCSK1N', 'CDC123', 'MUC5AC', 'DDX10', 'ODC1', 'CAV1', 'RSL1D1', 'PRMT1', 'NQO1', 'NUDT19', 'COX17', 'SMIM6', 'SH3BGRL3', 'IK', 'TPM1', 'RPL38', 'MT2A', 'UPP1', 'CCND1', 'GOLIM4', 'UCHL1', 'ID2', 'LITAF', 'S100A4', 'EEF1A1', 'VIM', 'PTGES3', 'GADD45B', 'TMSB4X', 'DDX21', 'RIN2', 'TXNRD1', 'TXNRD2', 'PKM', 'S100A13', 'BTG1', 'DYNLL1', 'PRDX1', 'LTA4H', 'HGD', 'TMBIM6', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'NOP58', 'TRIB3', 'PTPRS', 'EGR1', 'CES1', 'NOL7', 'ANG', 'YPEL5', 'MYBL2', 'NDUFA4', 'EZR', 'PTTG1', 'UBE2L6', 'HSPA2', 'RAB10', 'S100A10', 'PERP', 'MRPS22', 'KYNU', 'ADM', 'UBB', 'UBC', 'COX14', 'BCL2L1', 'RPL34', 'AKR1C2', 'GPX1', 'ZFP36L1', 'SLC12A2', 'CACNG8', 'CD63', 'CAPG', 'RPS17', 'GSN', 'SET', 'C19orf33', 'CCT3', 'NAMPT', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'NCAPD2', 'AURKB', 'PSMC2', 'XRCC6', 'HPGD', 'COTL1', 'AKR1B1', 'OCIAD2', 'PMPCB', 'NCL', 'PLAUR', 'ADA', 'ITM2B', 'GPX2', 'TUBB', 'MAGED2', 'RAN', 'LGALS3BP', 'CCT5', 'NPC2', 'CAV2', 'EIF4A1', 'ANP32E', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'DCAF13', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'PIF1', 'BLVRB', 'AP1S2', 'CALB2', 'AKR1B10', 'TXNDC17', 'TUBA1C', 'GSTO1', 'SLBP', 'CTNNB1', 'FN1', 'CCNB2', 'MCU', 'RAB31', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'RNF26', 'HNRNPH1', 'SPP1', 'BIRC2', 'HCFC1R1', 'RPL31', 'BAG1', 'CRIP2', 'SSB', 'PGD', 'TYMP', 'BIRC5', 'CAPZA1', 'TOP2A', 'KRT7', 'PMEPA1', 'FDXR', 'RAP2B', 'SLC39A8', 'ALDH2', 'PSAT1', 'CYP24A1', 'AGR2', 'LDHB', 'MTHFD2', 'ARPC3', 'RHOV', 'PSME2', 'ELF3', 'B4GALT4', 'PUS1', 'PMM2', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'CCND3', 'PSMC4', 'UCP2', 'NUDC', 'ACTB', 'RHOF', 'NDUFB4', 'HERPUD1', 'LDHA', 'ANXA5', 'YWHAE', 'SART3', 'GABARAPL1', 'ALG8', 'MAP1B', 'CDC20', 'INPP1', 'TOR1AIP2', 'LACTB2', 'GLIPR1', 'KRT18', 'ORMDL2', 'RPS4Y1', 'ECH1', 'TMPO', 'MYL12A', 'NUPR1', 'S100A11', 'PLK1', 'TUBA1B', 'TSC22D1', 'S100A16', 'CPLX2']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IMP'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IBA', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS', 'NAS', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IEA'], ['IEA'], ['HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['HTP', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'NAS'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01590232309546847</v>
+        <v>0.00676241321670356</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1200,22 +1200,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1994</v>
+        <v>2007</v>
       </c>
       <c r="H12" t="n">
         <v>410</v>
       </c>
       <c r="I12" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J12" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8390243902439024</v>
+        <v>0.8463414634146341</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1725175526579739</v>
+        <v>0.1728948679621325</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'NOP58', 'GPX1', 'BIRC2', 'PLK1', 'NDUFB4', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'CALM2', 'LTA4H', 'NUDC', 'RTN4RL2', 'EIF2S3', 'FADS1', 'PMEPA1', 'RAD21', 'TOP2A', 'SAAL1', 'CDA', 'GAL', 'PINK1', 'TMSB4X', 'FDXR', 'MAP1B', 'DDX21', 'UPK1B', 'NCAPD2', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CCND3', 'GADD45B', 'CSRP1', 'ID1', 'NUDT19', 'YARS2', 'HMOX1', 'GDF15', 'DDIT4', 'FKBP11', 'PMPCB', 'TRIB3', 'ALG8', 'KRT8', 'ARL4C', 'CEBPB', 'PKM', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'SQSTM1', 'S100A11', 'SSB', 'KIF18B', 'ALDH3A1', 'RRS1', 'LGALS1', 'LYAR', 'CDC20', 'CYBA', 'COTL1', 'DHRS3', 'PSMA4', 'FABP5', 'TUBB', 'ID2', 'HIRIP3', 'RHOV', 'RAB31', 'NANS', 'SLC12A2', 'PRDX4', 'SLC16A3', 'PWP1', 'MCU', 'NDUFA4', 'FN1', 'RAP2B', 'ID3', 'CPNE7', 'C1GALT1C1', 'PKMYT1', 'CDK1', 'DDX10', 'PRSS3', 'RPL41', 'AURKA', 'CYP1B1', 'LGALS3BP', 'UBE2S', 'HCFC1R1', 'DKK1', 'POLR2L', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'GOLIM4', 'TOR1AIP2', 'UMPS', 'CD44', 'NUPR1', 'CCNB2', 'GAL3ST1', 'JADE1', 'UBB', 'OAS1', 'TXNDC17', 'UNC50', 'PSMC2', 'DSP', 'CNTN1', 'SMAGP', 'RPS27L', 'SLC39A8', 'PGD', 'CTSL', 'NOL7', 'EXOSC9', 'GRAMD1A', 'KRT18', 'ANG', 'LACTB', 'IGFBP4', 'SKIL', 'DUSP1', 'NR0B1', 'NQO1', 'AKR1B10', 'GPRC5A', 'ALDH2', 'PLAU', 'GSDMD', 'KPNA2', 'HES1', 'GLIPR1', 'ANXA2', 'AKR1B1', 'TMBIM6', 'RPL34', 'CAV1', 'ANTXR1', 'AP1M2', 'TXNRD2', 'NT5E', 'SART3', 'ZFP36L1', 'MTHFD2', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'CYP24A1', 'DCAF13', 'PLAUR', 'PCSK1N', 'TUBA4A', 'MYC', 'EPS8', 'CAV2', 'ITM2B', 'CDKN1A', 'XRCC6', 'BLVRB', 'VDAC3', 'PMM2', 'PPP1CB', 'YARS', 'CALB2', 'CCT5', 'RPLP2', 'TXNRD1', 'FRA10AC1', 'EGR1', 'SLBP', 'HNRNPH1', 'TCEAL8', 'AKR1C1', 'HMGB2', 'RPS17', 'B4GALT4', 'AGR2', 'SFRP1', 'BIRC3', 'LGALS3', 'SLC7A5', 'RAN', 'HMGA1', 'NCL', 'MFGE8', 'MYL6', 'MMD', 'CD70', 'B4GALT1', 'BCL2L1', 'FOSL1', 'PRKCA', 'SPP1', 'CD63', 'CACNG8', 'S100A4', 'UBE2L6', 'PFDN2', 'IGFBP7', 'B4GALT5', 'UBC', 'NAMPT', 'ACTB', 'UPP1', 'ORMDL2', 'CKS1B', 'COX14', 'AHNAK', 'NDUFS2', 'GCHFR', 'HERC4', 'COX17', 'OCIAD2', 'MFSD12', 'F12', 'CRELD2', 'AP1S2', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'ATF4', 'GCNT3', 'ANXA5', 'SERPINB1', 'IK', 'ECH1', 'BAG1', 'PIF1', 'HSP90AA1', 'RHOD', 'LDHA', 'SNHG10', 'TMEM92', 'MGLL', 'HSPE1', 'SNRPF', 'PSMC6', 'RPL28', 'CES1', 'SPAG16', 'IDH1', 'HJURP', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ELF3', 'UCHL1', 'TUBA1C', 'ARPC3', 'HERPUD1', 'SLPI', 'ADA', 'NEK6', 'MYBL2', 'PSME2', 'CAPZA1', 'NTS', 'ANP32E', 'PTTG1', 'RSL1D1', 'SAR1A', 'RNF26', 'VIM', 'AHNAK2', 'KRT7', 'RGS2', 'HGD', 'EPHX1', 'PSMC4', 'OSR2', 'BASP1', 'CPLX2', 'PRMT1', 'RPS4Y1', 'SET', 'TUBB4B', 'RPL31', 'PERP', 'AURKB', 'MAGED2', 'KYNU', 'RAB10', 'CTNNBL1', 'CD24', 'TSC22D1', 'MORC4', 'LDHB', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'BIRC5', 'PTGES3', 'LACTB2', 'ISG20', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'CCND1', 'MRPS22', 'HILPDA', 'TAX1BP1', 'GABARAPL1', 'CCT4', 'PRDX1', 'ITGA3', 'CLSPN', 'YPEL5', 'BTG1', 'C19orf33', 'LITAF', 'TM4SF20', 'DYNLL1', 'EEF1A1', 'MESP1', 'ULK1', 'TMPO', 'DDB2', 'CCNB1', 'PTP4A1', 'CDC42', 'TMC5']</t>
+          <t>['ALDH3A1', 'BIRC3', 'PRSS23', 'SERINC2', 'HSPE1', 'CALM2', 'PKMYT1', 'RRS1', 'MFGE8', 'IGFBP7', 'HES1', 'NDUFS2', 'AKR1C1', 'DDIT4', 'KPNA2', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'SLC16A3', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'ULK1', 'CYP1B1', 'PFDN2', 'MORC4', 'VDAC3', 'DSP', 'TXN', 'NR0B1', 'ID3', 'CYBA', 'UNC50', 'DDB2', 'PINK1', 'CLSPN', 'AURKA', 'CD70', 'CDC42', 'CD9', 'MMD', 'B4GALT1', 'CEBPB', 'CCT4', 'CPNE7', 'AHNAK', 'MYC', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'ARL6IP1', 'UMPS', 'NANS', 'RPS27L', 'EPHX1', 'EPS8', 'KIF18B', 'PHLDA1', 'SNRPF', 'SERPINE2', 'DKK1', 'NTS', 'AKR1C3', 'TMC5', 'PSMC6', 'ARL4C', 'CTNNBL1', 'LYAR', 'CSRP1', 'CRELD2', 'SKIL', 'POLR2L', 'TUBA4A', 'FADS1', 'PWP1', 'MFSD12', 'B4GALT5', 'SFRP1', 'DHRS3', 'HERC4', 'RPLP2', 'LACTB', 'C1GALT1C1', 'HMOX1', 'JADE1', 'TM4SF20', 'RPL28', 'GAL3ST1', 'FRA10AC1', 'AP1M2', 'RHOD', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'HJURP', 'CDA', 'RPL41', 'SAAL1', 'ACTG1', 'ISG20', 'VAMP8', 'CTSL', 'CKS1B', 'S100A6', 'MARCKSL1', 'BASP1', 'MESP1', 'SAR1A', 'GCHFR', 'TMEM92', 'OAS1', 'SNHG10', 'HIRIP3', 'CDKN1A', 'IDH1', 'GDF15', 'DUSP1', 'CCNB1', 'MGLL', 'RGS2', 'GRAMD1A', 'ANTXR1', 'HILPDA', 'ID1', 'SMAGP', 'TCEAL8', 'KIF23', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'NEK6', 'SPAG16', 'YARS2', 'PCSK1N', 'MUC5AC', 'DDX10', 'CAV1', 'RSL1D1', 'PRMT1', 'NQO1', 'NUDT19', 'COX17', 'SMIM6', 'CD24', 'SH3BGRL3', 'IK', 'MT2A', 'UPP1', 'CCND1', 'GOLIM4', 'UCHL1', 'ID2', 'LITAF', 'S100A4', 'EEF1A1', 'VIM', 'PTGES3', 'GADD45B', 'TMSB4X', 'DDX21', 'RIN2', 'TXNRD1', 'TXNRD2', 'PKM', 'S100A13', 'BTG1', 'DYNLL1', 'PRDX1', 'LTA4H', 'HGD', 'TMBIM6', 'HMGB2', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'NOP58', 'TRIB3', 'PTPRS', 'EGR1', 'CES1', 'NOL7', 'ANG', 'YPEL5', 'MYBL2', 'NDUFA4', 'EZR', 'PTTG1', 'UBE2L6', 'HSPA2', 'RAB10', 'S100A10', 'PERP', 'ITGB4', 'MRPS22', 'KYNU', 'ADM', 'OSR2', 'UBB', 'UBC', 'COX14', 'BCL2L1', 'RPL34', 'GPX1', 'ZFP36L1', 'SLC12A2', 'CACNG8', 'CD63', 'CAPG', 'RPS17', 'GSN', 'SET', 'C19orf33', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'UBE2S', 'NCAPD2', 'AURKB', 'PSMC2', 'XRCC6', 'HPGD', 'COTL1', 'AKR1B1', 'OCIAD2', 'PMPCB', 'NCL', 'PLAUR', 'ADA', 'ITM2B', 'TUBB', 'MAGED2', 'RAN', 'LGALS3BP', 'FOSL1', 'CCT5', 'NPC2', 'CAV2', 'AXL', 'AMIGO2', 'EIF4A1', 'ANP32E', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'DCAF13', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'PIF1', 'BLVRB', 'AP1S2', 'CALB2', 'AKR1B10', 'TXNDC17', 'TUBA1C', 'GSTO1', 'SLBP', 'CTNNB1', 'FN1', 'CCNB2', 'MCU', 'RAB31', 'ALDH1A1', 'IGFBP4', 'RNF26', 'HNRNPH1', 'SPP1', 'BIRC2', 'HCFC1R1', 'RPL31', 'BAG1', 'SSB', 'PGD', 'BIRC5', 'CAPZA1', 'TOP2A', 'KRT7', 'PMEPA1', 'FDXR', 'UPK1B', 'RAP2B', 'SLC39A8', 'ALDH2', 'PSAT1', 'CYP24A1', 'AGR2', 'LDHB', 'MTHFD2', 'ARPC3', 'RHOV', 'PSME2', 'ELF3', 'B4GALT4', 'PUS1', 'PMM2', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'CCND3', 'PSMC4', 'UCP2', 'NUDC', 'ACTB', 'RHOF', 'NDUFB4', 'HERPUD1', 'LDHA', 'ANXA5', 'YWHAE', 'SART3', 'GABARAPL1', 'ALG8', 'MAP1B', 'CDC20', 'TOR1AIP2', 'LACTB2', 'GLIPR1', 'KRT18', 'ORMDL2', 'RPS4Y1', 'ECH1', 'TMPO', 'MYL12A', 'NUPR1', 'S100A11', 'PLK1', 'TUBA1B', 'TSC22D1', 'S100A16', 'CPLX2']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'ISO', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IEA'], ['IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['HTP', 'TAS'], ['EXP', 'IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HTP', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['HDA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA'], ['IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['HDA'], ['IDA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HTP', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['IDA'], ['HDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISO', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IEA'], ['IDA', 'HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HTP', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS'], ['HDA', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02013107124744812</v>
+        <v>0.01240727064118597</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -1266,22 +1266,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="H13" t="n">
         <v>410</v>
       </c>
       <c r="I13" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J13" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8731707317073171</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1700712589073634</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'SH3BGRL3', 'ACTG1', 'MUC5AC', 'NOP58', 'GPX1', 'BIRC2', 'PLK1', 'NDUFB4', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CD9', 'EIF4A1', 'GSN', 'AKR1C3', 'CALM2', 'LTA4H', 'NUDC', 'RTN4RL2', 'EIF2S3', 'FADS1', 'PMEPA1', 'RAD21', 'TOP2A', 'SAAL1', 'CDA', 'GAL', 'PINK1', 'TMSB4X', 'FDXR', 'MAP1B', 'DDX21', 'UPK1B', 'NCAPD2', 'MARCKSL1', 'PSAT1', 'SERPINE2', 'PRSS23', 'HSPA2', 'CCND3', 'GADD45B', 'CSRP1', 'ID1', 'NUDT19', 'YARS2', 'HMOX1', 'GDF15', 'DDIT4', 'FKBP11', 'PMPCB', 'TRIB3', 'ALG8', 'KRT8', 'ARL4C', 'CEBPB', 'GPX2', 'PKM', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'SQSTM1', 'S100A11', 'SSB', 'KIF18B', 'ALDH3A1', 'CAMK2N1', 'RRS1', 'LGALS1', 'LYAR', 'CDC20', 'CYBA', 'COTL1', 'DHRS3', 'PSMA4', 'FABP5', 'TUBB', 'PLEK2', 'ID2', 'HIRIP3', 'RHOV', 'RAB31', 'NANS', 'SLC12A2', 'PRDX4', 'SLC16A3', 'TUBA1B', 'KRT81', 'PWP1', 'MCU', 'NDUFA4', 'FN1', 'RAP2B', 'ID3', 'CPNE7', 'C1GALT1C1', 'PKMYT1', 'CDK1', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'AURKA', 'CYP1B1', 'LGALS3BP', 'UBE2S', 'HCFC1R1', 'DKK1', 'POLR2L', 'RARRES1', 'SERINC2', 'EZR', 'RHOF', 'GOLIM4', 'TOR1AIP2', 'UMPS', 'CD44', 'NUPR1', 'CCNB2', 'GAL3ST1', 'JADE1', 'UBB', 'OAS1', 'TXNDC17', 'TPPP3', 'UNC50', 'PSMC2', 'DSP', 'CNTN1', 'SMAGP', 'RPS27L', 'SLC39A8', 'PGD', 'CTSL', 'NOL7', 'EXOSC9', 'GRAMD1A', 'KRT18', 'ANG', 'LACTB', 'IGFBP4', 'SKIL', 'DUSP1', 'NR0B1', 'NQO1', 'AKR1B10', 'GPRC5A', 'ALDH2', 'PLAU', 'GSDMD', 'KPNA2', 'HES1', 'GLIPR1', 'ANXA2', 'AKR1B1', 'TMBIM6', 'RPL34', 'CAV1', 'ANTXR1', 'AP1M2', 'TXNRD2', 'NT5E', 'SART3', 'ZFP36L1', 'MTHFD2', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'CYP24A1', 'DCAF13', 'PLAUR', 'PCSK1N', 'TUBA4A', 'RPL38', 'MYC', 'EPS8', 'CAV2', 'ITM2B', 'CDKN1A', 'XRCC6', 'BLVRB', 'VDAC3', 'PMM2', 'PPP1CB', 'YARS', 'CALB2', 'CCT5', 'RPLP2', 'TXNRD1', 'FRA10AC1', 'EGR1', 'SLBP', 'HNRNPH1', 'TCEAL8', 'AKR1C1', 'HMGB2', 'RPS17', 'B4GALT4', 'AGR2', 'DOCK5', 'SFRP1', 'BIRC3', 'LGALS3', 'SLC7A5', 'RAN', 'HMGA1', 'NCL', 'MFGE8', 'MYL6', 'MMD', 'RPL22L1', 'CD70', 'B4GALT1', 'BCL2L1', 'FOSL1', 'PRKCA', 'SPP1', 'CD63', 'CACNG8', 'S100A4', 'UBE2L6', 'PFDN2', 'IGFBP7', 'B4GALT5', 'UBC', 'NAMPT', 'ACTB', 'UPP1', 'ORMDL2', 'CKS1B', 'COX14', 'AHNAK', 'NDUFS2', 'GCHFR', 'HERC4', 'COX17', 'OCIAD2', 'MFSD12', 'F12', 'CRELD2', 'AP1S2', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'ATF4', 'GCNT3', 'ANXA5', 'SERPINB1', 'IK', 'ECH1', 'BAG1', 'PIF1', 'HSP90AA1', 'RHOD', 'LDHA', 'SNHG10', 'TMEM92', 'MGLL', 'HSPE1', 'SNRPF', 'PSMC6', 'RPL28', 'CES1', 'SPAG16', 'PDLIM5', 'SEMA4B', 'IDH1', 'HJURP', 'GSTO1', 'HPGD', 'VAMP8', 'MYL12A', 'ELF3', 'UCHL1', 'TUBA1C', 'ARPC3', 'HERPUD1', 'SLPI', 'ADA', 'NEK6', 'MYBL2', 'PSME2', 'CAPZA1', 'NTS', 'ANP32E', 'PTTG1', 'RSL1D1', 'SAR1A', 'RNF26', 'VIM', 'AHNAK2', 'KRT7', 'RGS2', 'HGD', 'EPHX1', 'PSMC4', 'OSR2', 'TPM1', 'BASP1', 'CPLX2', 'PRMT1', 'RPS4Y1', 'SET', 'TUBB4B', 'RPL31', 'PERP', 'AURKB', 'MAGED2', 'KYNU', 'RAB10', 'CTNNBL1', 'CD24', 'TSC22D1', 'MORC4', 'LDHB', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'BIRC5', 'PTGES3', 'LACTB2', 'ISG20', 'S100A16', 'S100A10', 'ITGB4', 'NPC2', 'PA2G4', 'CCT3', 'CCND1', 'MRPS22', 'HILPDA', 'TAX1BP1', 'GABARAPL1', 'CCT4', 'PRDX1', 'ITGA3', 'CLSPN', 'YPEL5', 'BTG1', 'C19orf33', 'LITAF', 'TM4SF20', 'DYNLL1', 'EEF1A1', 'MESP1', 'SLC4A7', 'ULK1', 'TMPO', 'DDB2', 'CCNB1', 'PTP4A1', 'CDC42', 'TMC5']</t>
+          <t>['ALDH3A1', 'BIRC3', 'PRSS23', 'SERINC2', 'HSPE1', 'CALM2', 'PKMYT1', 'RRS1', 'MFGE8', 'IGFBP7', 'HES1', 'NDUFS2', 'AKR1C1', 'DDIT4', 'KPNA2', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'RARRES1', 'SLC16A3', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'ULK1', 'CYP1B1', 'PFDN2', 'MORC4', 'VDAC3', 'DSP', 'TXN', 'NR0B1', 'ID3', 'CYBA', 'UNC50', 'DDB2', 'PINK1', 'CLSPN', 'AURKA', 'CD70', 'PLEK2', 'CDC42', 'CD9', 'MMD', 'B4GALT1', 'CEBPB', 'CCT4', 'CPNE7', 'AHNAK', 'MYC', 'LGALS3', 'EIF2S3', 'ANXA2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'ARL6IP1', 'UMPS', 'NANS', 'RPS27L', 'EPHX1', 'EPS8', 'KIF18B', 'PHLDA1', 'SNRPF', 'SERPINE2', 'DKK1', 'NTS', 'AKR1C3', 'TMC5', 'PSMC6', 'ARL4C', 'CTNNBL1', 'LYAR', 'AKAP12', 'CSRP1', 'SEMA4B', 'CRELD2', 'SKIL', 'POLR2L', 'TUBA4A', 'FADS1', 'PWP1', 'MFSD12', 'B4GALT5', 'SFRP1', 'DHRS3', 'HERC4', 'RPLP2', 'LACTB', 'C1GALT1C1', 'HMOX1', 'JADE1', 'TM4SF20', 'RPL28', 'PDLIM5', 'GAL3ST1', 'FRA10AC1', 'AP1M2', 'RHOD', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'HJURP', 'CDA', 'RPL41', 'SAAL1', 'ACTG1', 'ISG20', 'VAMP8', 'CTSL', 'CKS1B', 'S100A6', 'MARCKSL1', 'BASP1', 'MESP1', 'SAR1A', 'GCHFR', 'TMEM92', 'OAS1', 'SNHG10', 'HIRIP3', 'CDKN1A', 'IDH1', 'GDF15', 'DUSP1', 'CCNB1', 'MGLL', 'RGS2', 'GRAMD1A', 'ANTXR1', 'HILPDA', 'ID1', 'SMAGP', 'TCEAL8', 'KIF23', 'CLU', 'RTN4RL2', 'ITGA3', 'SLC7A5', 'GPRC5A', 'NEK6', 'SPAG16', 'YARS2', 'PCSK1N', 'MUC5AC', 'DDX10', 'CAV1', 'RSL1D1', 'PRMT1', 'NQO1', 'NUDT19', 'COX17', 'SMIM6', 'CD24', 'SH3BGRL3', 'IK', 'TPM1', 'RPL38', 'MT2A', 'UPP1', 'CCND1', 'GOLIM4', 'UCHL1', 'ID2', 'LITAF', 'S100A4', 'EEF1A1', 'VIM', 'PTGES3', 'GADD45B', 'TMSB4X', 'DDX21', 'RIN2', 'TXNRD1', 'TXNRD2', 'PKM', 'S100A13', 'BTG1', 'DYNLL1', 'PRDX1', 'LTA4H', 'HGD', 'TMBIM6', 'KRT81', 'HMGB2', 'RPL22L1', 'MYL6', 'PSMA4', 'PPP1CB', 'SLPI', 'NOP58', 'TRIB3', 'PTPRS', 'EGR1', 'CES1', 'NOL7', 'ANG', 'YPEL5', 'MYBL2', 'NDUFA4', 'EZR', 'PTTG1', 'UBE2L6', 'HSPA2', 'RAB10', 'S100A10', 'PERP', 'ITGB4', 'MRPS22', 'KYNU', 'ADM', 'OSR2', 'UBB', 'UBC', 'COX14', 'BCL2L1', 'RPL34', 'GPX1', 'ZFP36L1', 'SLC12A2', 'CACNG8', 'CD63', 'CAPG', 'RPS17', 'GSN', 'SET', 'C19orf33', 'CCT3', 'CNTN1', 'NAMPT', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'NCAPD2', 'AURKB', 'PSMC2', 'XRCC6', 'HPGD', 'COTL1', 'AKR1B1', 'OCIAD2', 'PMPCB', 'NCL', 'PLAUR', 'ADA', 'ITM2B', 'GPX2', 'TUBB', 'MAGED2', 'RAN', 'LGALS3BP', 'FOSL1', 'CCT5', 'NPC2', 'CAV2', 'AXL', 'AMIGO2', 'EIF4A1', 'ANP32E', 'HSP90AA1', 'GSDMD', 'TUBB4B', 'DCAF13', 'TAX1BP1', 'PRDX4', 'PLAU', 'HSP90AB1', 'NT5E', 'PIF1', 'BLVRB', 'AP1S2', 'CALB2', 'AKR1B10', 'TXNDC17', 'TUBA1C', 'GSTO1', 'SLBP', 'CTNNB1', 'FN1', 'CCNB2', 'MCU', 'RAB31', 'ALDH1A1', 'IGFBP4', 'RNF26', 'SLC4A7', 'HNRNPH1', 'SPP1', 'BIRC2', 'HCFC1R1', 'RPL31', 'BAG1', 'SSB', 'PGD', 'BIRC5', 'CAPZA1', 'TOP2A', 'KRT7', 'PMEPA1', 'FDXR', 'UPK1B', 'RAP2B', 'SLC39A8', 'ALDH2', 'PSAT1', 'CYP24A1', 'AGR2', 'LDHB', 'MTHFD2', 'ARPC3', 'RHOV', 'PSME2', 'ELF3', 'B4GALT4', 'PUS1', 'PMM2', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'CCND3', 'PSMC4', 'UCP2', 'NUDC', 'ACTB', 'RHOF', 'NDUFB4', 'HERPUD1', 'LDHA', 'ANXA5', 'YWHAE', 'SART3', 'GABARAPL1', 'ALG8', 'MAP1B', 'CDC20', 'TOR1AIP2', 'LACTB2', 'GLIPR1', 'KRT18', 'ORMDL2', 'RPS4Y1', 'ECH1', 'TMPO', 'MYL12A', 'NUPR1', 'S100A11', 'PLK1', 'TUBA1B', 'TSC22D1', 'CAMK2N1', 'S100A16', 'CPLX2']</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'ISO', 'IBA', 'NAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IEA'], ['IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HTP', 'TAS'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HTP', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA'], ['IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HTP', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HTP', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.333675141164633e-12</v>
+        <v>6.465057950089537e-13</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H2" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J2" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K2" t="n">
-        <v>0.209349593495935</v>
+        <v>0.2129817444219067</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3901515151515151</v>
+        <v>0.3932584269662922</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'RPL35', 'ANXA7', 'AIMP1', 'HSPD1', 'EIF4A1', 'PPIB', 'HSPA8', 'EIF2S3', 'DKC1', 'TOP2A', 'TMSB4X', 'DDX21', 'SUCLG1', 'RPL37A', 'PKM', 'EBNA1BP2', 'SSB', 'RRS1', 'LGALS1', 'UTP18', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'GLRX3', 'ANP32A', 'RPL26', 'DDX10', 'RPL41', 'EZR', 'ILF2', 'OAS1', 'SLC3A2', 'RPS27L', 'EXOSC9', 'GTPBP4', 'KRT18', 'HLA-A', 'SNW1', 'NQO1', 'KPNA2', 'ANXA2', 'RPL34', 'ZFP36L1', 'YWHAE', 'TXN', 'APOBEC3C', 'DCAF13', 'ENO1', 'MYC', 'MKI67', 'RPS28', 'RAD51AP1', 'FDPS', 'CCT5', 'YARS', 'HNRNPH1', 'RPS17', 'HMGB2', 'EIF1AY', 'LGALS3', 'RAN', 'RPL39', 'BZW1', 'HMGA1', 'NCL', 'S100A4', 'RPS15A', 'NPM1', 'RBFOX3', 'RPL27', 'HSP90AA1', 'HSPE1', 'RPL28', 'SNRPF', 'MRPS30', 'EIF3D', 'TNRC6B', 'SLPI', 'MRPL13', 'RSL1D1', 'VIM', 'RPS29', 'CBX6', 'TRA2A', 'XRCC5', 'PRMT1', 'TUBB4B', 'RPL31', 'DDX39A', 'RPS18', 'NIP7', 'S100A16', 'TRMT6', 'RPF2', 'PA2G4', 'CCT4', 'PRDX1', 'SOX4', 'RPS24', 'HMGB3', 'EEF1A1', 'FSCN1']</t>
+          <t>['DKC1', 'HSPE1', 'XRCC5', 'RRS1', 'KPNA2', 'EXOSC9', 'PPP1R7', 'LGALS1', 'SLC16A3', 'PA2G4', 'RBFOX3', 'TXN', 'SUCLG1', 'HSPA8', 'CCT4', 'RPS15A', 'MYC', 'LGALS3', 'EIF2S3', 'ANXA2', 'ZC3H4', 'TNRC6B', 'UTP18', 'EIF1AY', 'RPS27L', 'EIF3D', 'SNRPF', 'RPL35', 'RPS18', 'APOBEC3C', 'RPL28', 'ANP32A', 'RPL39', 'YARS', 'EBNA1BP2', 'RPL41', 'NEAT1', 'NPM1', 'OAS1', 'GTPBP4', 'S100A16', 'MRPS30', 'HSPD1', 'DDX10', 'NQO1', 'PRMT1', 'RSL1D1', 'ANXA7', 'RPS24', 'S100A4', 'EEF1A1', 'TRA2A', 'VIM', 'BZW1', 'TMSB4X', 'DDX21', 'PKM', 'ILF2', 'CBX6', 'PRDX1', 'MRPL13', 'HMGB2', 'SLPI', 'EZR', 'ENO1', 'HLA-A', 'FDPS', 'RPL34', 'RPS17', 'GLRX3', 'RPS28', 'AIMP1', 'RPF2', 'NCL', 'RPL27', 'CCT5', 'RAN', 'FSCN1', 'EIF4A1', 'HSP90AA1', 'TUBB4B', 'NIP7', 'DCAF13', 'HSP90AB1', 'TRMT6', 'RAD51AP1', 'HNRNPH1', 'RPL31', 'DDX39A', 'SSB', 'TOP2A', 'PPIB', 'SLC3A2', 'MKI67', 'HMGA1', 'RPL26', 'YWHAE', 'RPS29', 'SNW1', 'HMGB3', 'KRT18', 'SOX4', 'TUBA1B', 'ZFP36L1', 'RPL37A']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IPI', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA'], ['TAS'], ['HDA'], ['IPI'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'NAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IMP', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IEA'], ['IDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['HDA', 'TAS'], ['HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA']]</t>
+          <t>[['IPI', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'NAS'], ['IDA'], ['HDA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['IPI'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.925485703771384e-11</v>
+        <v>2.479530050958517e-11</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1497,16 +1497,16 @@
         <v>485</v>
       </c>
       <c r="H3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I3" t="n">
         <v>155</v>
       </c>
       <c r="J3" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3150406504065041</v>
+        <v>0.3144016227180527</v>
       </c>
       <c r="L3" t="n">
         <v>0.3195876288659794</v>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'AXL', 'PROCR', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'HSPA2', 'MARCKSL1', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'CPNE7', 'CDK1', 'RPL26', 'LGALS3BP', 'EZR', 'RHOF', 'CD44', 'SLC3A2', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'HLA-A', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PPP1R7', 'EPS8', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'SLC2A1', 'CCT5', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'MMP7', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'NCL', 'CKB', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'RPS15A', 'IGFBP7', 'ACTB', 'TIMP1', 'MYL12B', 'SYNGR2', 'F12', 'CAPG', 'RPL27', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'KIF3A', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'ARPC3', 'SLPI', 'CAPZA1', 'CHP1', 'VIM', 'RPS29', 'KRT7', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'FGB', 'ANXA1', 'PSMA3', 'LDHB', 'ANXA4', 'KRT19', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'S100A16', 'S100A10', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'FSCN1', 'CDC42']</t>
+          <t>['HSPE1', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'GCNT3', 'PA2G4', 'TUBA1A', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'CFD', 'FGB', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'PHGDH', 'S100A16', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'GPRC5A', 'CKB', 'MUC5AC', 'ANXA7', 'S100A4', 'EEF1A1', 'VIM', 'TIMP1', 'TXNRD1', 'HSPA5', 'PKM', 'PRDX1', 'ATP1B1', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'EZR', 'HSPA2', 'ENO1', 'S100A10', 'HLA-A', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'ANXA3', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'MARCKS', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'UPK1B', 'RAP2B', 'PSAT1', 'PPIB', 'SLC3A2', 'GLA', 'LDHB', 'ARPC3', 'MMP7', 'CST3', 'APOE', 'RPL26', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.210938719612641e-11</v>
+        <v>2.84986654633669e-11</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1563,16 +1563,16 @@
         <v>490</v>
       </c>
       <c r="H4" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I4" t="n">
         <v>156</v>
       </c>
       <c r="J4" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3164300202839757</v>
       </c>
       <c r="L4" t="n">
         <v>0.3183673469387755</v>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'AXL', 'PROCR', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'CPNE7', 'CDK1', 'RPL26', 'LGALS3BP', 'EZR', 'RHOF', 'CD44', 'SLC3A2', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'HLA-A', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PPP1R7', 'EPS8', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'SLC2A1', 'CCT5', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'MMP7', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'NCL', 'CKB', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'RPS15A', 'IGFBP7', 'ACTB', 'TIMP1', 'MYL12B', 'SYNGR2', 'F12', 'CAPG', 'RPL27', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'KIF3A', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'ARPC3', 'SLPI', 'CAPZA1', 'CHP1', 'VIM', 'RPS29', 'KRT7', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'FGB', 'ANXA1', 'PSMA3', 'LDHB', 'ANXA4', 'KRT19', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'S100A16', 'S100A10', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'FSCN1', 'CDC42']</t>
+          <t>['HSPE1', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'GCNT3', 'PA2G4', 'TUBA1A', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'SERPINE2', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'CFD', 'FGB', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'PHGDH', 'S100A16', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'GPRC5A', 'CKB', 'MUC5AC', 'ANXA7', 'S100A4', 'EEF1A1', 'VIM', 'TIMP1', 'TXNRD1', 'HSPA5', 'PKM', 'PRDX1', 'ATP1B1', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'EZR', 'HSPA2', 'ENO1', 'S100A10', 'HLA-A', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'ANXA3', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'MARCKS', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'UPK1B', 'RAP2B', 'PSAT1', 'PPIB', 'SLC3A2', 'GLA', 'LDHB', 'ARPC3', 'MMP7', 'CST3', 'APOE', 'RPL26', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.210938719612641e-11</v>
+        <v>2.84986654633669e-11</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1629,16 +1629,16 @@
         <v>490</v>
       </c>
       <c r="H5" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I5" t="n">
         <v>156</v>
       </c>
       <c r="J5" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3164300202839757</v>
       </c>
       <c r="L5" t="n">
         <v>0.3183673469387755</v>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'AXL', 'PROCR', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'CPNE7', 'CDK1', 'RPL26', 'LGALS3BP', 'EZR', 'RHOF', 'CD44', 'SLC3A2', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'HLA-A', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PPP1R7', 'EPS8', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'SLC2A1', 'CCT5', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'MMP7', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'NCL', 'CKB', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'RPS15A', 'IGFBP7', 'ACTB', 'TIMP1', 'MYL12B', 'SYNGR2', 'F12', 'CAPG', 'RPL27', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'KIF3A', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'ARPC3', 'SLPI', 'CAPZA1', 'CHP1', 'VIM', 'RPS29', 'KRT7', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'FGB', 'ANXA1', 'PSMA3', 'LDHB', 'ANXA4', 'KRT19', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'S100A16', 'S100A10', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'FSCN1', 'CDC42']</t>
+          <t>['HSPE1', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'GCNT3', 'PA2G4', 'TUBA1A', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'SERPINE2', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'CFD', 'FGB', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'PHGDH', 'S100A16', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'GPRC5A', 'CKB', 'MUC5AC', 'ANXA7', 'S100A4', 'EEF1A1', 'VIM', 'TIMP1', 'TXNRD1', 'HSPA5', 'PKM', 'PRDX1', 'ATP1B1', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'EZR', 'HSPA2', 'ENO1', 'S100A10', 'HLA-A', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'ANXA3', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'MARCKS', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'UPK1B', 'RAP2B', 'PSAT1', 'PPIB', 'SLC3A2', 'GLA', 'LDHB', 'ARPC3', 'MMP7', 'CST3', 'APOE', 'RPL26', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.210938719612641e-11</v>
+        <v>2.84986654633669e-11</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1695,16 +1695,16 @@
         <v>490</v>
       </c>
       <c r="H6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I6" t="n">
         <v>156</v>
       </c>
       <c r="J6" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3164300202839757</v>
       </c>
       <c r="L6" t="n">
         <v>0.3183673469387755</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'AXL', 'PROCR', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'UPK1B', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'CPNE7', 'CDK1', 'RPL26', 'LGALS3BP', 'EZR', 'RHOF', 'CD44', 'SLC3A2', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'HLA-A', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PPP1R7', 'EPS8', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'SLC2A1', 'CCT5', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'MMP7', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'NCL', 'CKB', 'MYL6', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'RPS15A', 'IGFBP7', 'ACTB', 'TIMP1', 'MYL12B', 'SYNGR2', 'F12', 'CAPG', 'RPL27', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'KIF3A', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'ARPC3', 'SLPI', 'CAPZA1', 'CHP1', 'VIM', 'RPS29', 'KRT7', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'FGB', 'ANXA1', 'PSMA3', 'LDHB', 'ANXA4', 'KRT19', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'S100A16', 'S100A10', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'FSCN1', 'CDC42']</t>
+          <t>['HSPE1', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'GCNT3', 'PA2G4', 'TUBA1A', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'SERPINE2', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'CFD', 'FGB', 'F12', 'FABP5', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'PHGDH', 'S100A16', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'GPRC5A', 'CKB', 'MUC5AC', 'ANXA7', 'S100A4', 'EEF1A1', 'VIM', 'TIMP1', 'TXNRD1', 'HSPA5', 'PKM', 'PRDX1', 'ATP1B1', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'EZR', 'HSPA2', 'ENO1', 'S100A10', 'HLA-A', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'ANXA3', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'MARCKS', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'SPP1', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'UPK1B', 'RAP2B', 'PSAT1', 'PPIB', 'SLC3A2', 'GLA', 'LDHB', 'ARPC3', 'MMP7', 'CST3', 'APOE', 'RPL26', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.453337004344128e-08</v>
+        <v>8.272747613519036e-09</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -1758,22 +1758,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I7" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J7" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4186991869918699</v>
+        <v>0.4219066937119675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2710526315789474</v>
+        <v>0.2733245729303548</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'AXL', 'PROCR', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'RABAC1', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'PMEPA1', 'CDA', 'GAL', 'TMSB4X', 'UPK1B', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'CNIH4', 'DEGS1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST1', 'CPNE7', 'CDK1', 'RPL26', 'PRSS3', 'LGALS3BP', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'ILF2', 'CD44', 'PSMD14', 'SLC3A2', 'EMP2', 'LY6K', 'PSMC2', 'SMAGP', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'PHACTR2', 'HLA-A', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'CAV1', 'AP1M2', 'ANTXR1', 'NT5E', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'PPP1R7', 'EPS8', 'CAV2', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'SLC2A1', 'CCT5', 'TXNRD1', 'AP3S1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'MMP7', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'NCL', 'CKB', 'MYL6', 'MMD', 'CD70', 'B4GALT1', 'BCL2L1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'RPS15A', 'IGFBP7', 'ACTB', 'PSMD1', 'GCHFR', 'TIMP1', 'MYL12B', 'SYNGR2', 'OCIAD2', 'CNN2', 'F12', 'ERGIC1', 'PHLDA1', 'CAPG', 'RPL27', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'CTTN', 'KIF3A', 'OPTN', 'LAPTM4A', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'VIM', 'RPS29', 'KRT7', 'XRCC5', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'MAGED2', 'FGB', 'ANXA1', 'PSMA3', 'RAB11FIP1', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'S100A16', 'S100A10', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'CCT4', 'PRDX1', 'ITGA3', 'YPEL5', 'DYNLL1', 'LITAF', 'EEF1A1', 'SH3KBP1', 'FSCN1', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['HSPE1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'RIPK2', 'PRKCA', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'GCNT3', 'GAL', 'PA2G4', 'TUBA1A', 'CNN2', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'MMD', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'FGFR1', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'PHLDA1', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'EMP2', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'CFD', 'FGB', 'RABAC1', 'AP1M2', 'F12', 'FABP5', 'CDA', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'GCHFR', 'PHGDH', 'ANTXR1', 'S100A16', 'SMAGP', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'GPRC5A', 'LY6K', 'PCSK1N', 'CKB', 'MUC5AC', 'CAV1', 'RAB11FIP1', 'GOLIM4', 'ANXA7', 'LITAF', 'S100A4', 'EEF1A1', 'VIM', 'TMSB4X', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'ILF2', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'YPEL5', 'EZR', 'HSPA2', 'ENO1', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'ADM', 'BCL2L1', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'LAPTM4A', 'ANXA3', 'CDK1', 'SH3KBP1', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'MAGED2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'PSMD1', 'NT5E', 'BLVRB', 'MARCKS', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'MGST1', 'SPP1', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'PMEPA1', 'UPK1B', 'CNIH4', 'RAP2B', 'PSAT1', 'PPIB', 'SLC3A2', 'GLA', 'LDHB', 'ARPC3', 'MMP7', 'CST3', 'APOE', 'PTP4A1', 'RPL26', 'DEGS1', 'PRSS3', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['TAS'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['TAS'], ['HDA', 'IEA'], ['ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['HDA'], ['IBA', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['TAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA', 'ISS'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IBA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['ISS', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'IEA'], ['IDA']]</t>
+          <t>[['HDA'], ['IBA'], ['HDA', 'ISS', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'IBA', 'TAS'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['TAS'], ['HDA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['IBA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['TAS'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['ISS', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['ISS', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IBA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.893822304835142e-07</v>
+        <v>2.186002502944478e-07</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1824,22 +1824,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H8" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I8" t="n">
         <v>210</v>
       </c>
       <c r="J8" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4268292682926829</v>
+        <v>0.4259634888438134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2648171500630517</v>
+        <v>0.2651515151515151</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'ADM', 'AXL', 'S100A13', 'PROCR', 'ADAMTS12', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'CDA', 'GAL', 'TMSB4X', 'UPK1B', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'INA', 'ALDH3A1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'KRT81', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'CPNE7', 'CDK1', 'RPL26', 'PRSS3', 'LGALS3BP', 'DKK1', 'EZR', 'RHOF', 'ILF2', 'CD44', 'CCL2', 'PSMD14', 'OAS1', 'SLC3A2', 'LY6K', 'PSMC2', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'HLA-A', 'IGFBP4', 'PTPRF', 'AKR1B10', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'NT5E', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'C1orf56', 'PPP1R7', 'LIPH', 'EPS8', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'MDK', 'SLC2A1', 'CCT5', 'YARS', 'EVA1C', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'RPL39', 'COL5A2', 'NCL', 'CKB', 'MYL6', 'CXCL5', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'NINJ1', 'CD63', 'PAPPA', 'S100A4', 'RPS15A', 'IGFBP7', 'MUC3A', 'ACTB', 'PSMD1', 'TIMP1', 'MYL12B', 'SYNGR2', 'CNN2', 'F12', 'CRELD2', 'CAPG', 'RPL27', 'LXN', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'KIF3A', 'TFF1', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'ARPC3', 'SLPI', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'STC2', 'VIM', 'RPS29', 'KRT7', 'XRCC5', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'MAGED2', 'RSPO3', 'FGB', 'ANXA1', 'PSMA3', 'LDHB', 'ANXA4', 'KRT19', 'TGFBR2', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'IGFBP6', 'S100A16', 'S100A10', 'CXCL3', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'INSL4', 'CCT4', 'PRDX1', 'ITGA3', 'YPEL5', 'EEF1A1', 'FSCN1', 'CDC42']</t>
+          <t>['ALDH3A1', 'C1orf56', 'HSPE1', 'XRCC5', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'LIPH', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'TFF1', 'GCNT3', 'GAL', 'PA2G4', 'TUBA1A', 'CNN2', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'MDK', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'FGFR1', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'RSPO3', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'NINJ1', 'COL5A2', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'CRELD2', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'ADAMTS12', 'CFD', 'FGB', 'RPL39', 'F12', 'FABP5', 'YARS', 'IGFBP6', 'CDA', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'CXCL3', 'BASP1', 'OAS1', 'PHGDH', 'S100A16', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'LXN', 'GPRC5A', 'LY6K', 'TGFBR2', 'PCSK1N', 'CKB', 'MUC5AC', 'ANXA7', 'S100A4', 'EEF1A1', 'VIM', 'INSL4', 'TMSB4X', 'TIMP1', 'TXNRD1', 'HSPA5', 'PKM', 'S100A13', 'ILF2', 'PRDX1', 'ATP1B1', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'YPEL5', 'EZR', 'HSPA2', 'ENO1', 'PSMD14', 'S100A10', 'HLA-A', 'ADM', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'CXCL5', 'ANXA3', 'CDK1', 'RPS28', 'AIMP1', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'PLAUR', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'MAGED2', 'CCL2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'INA', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'PSMD1', 'NT5E', 'BLVRB', 'MARCKS', 'AKR1B10', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'IGFBP4', 'SPP1', 'PAPPA', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'UPK1B', 'RAP2B', 'EVA1C', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'LDHB', 'MTHFD2', 'ARPC3', 'B4GALT4', 'MMP7', 'CST3', 'APOE', 'RPL26', 'PRSS3', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'IGFBP3', 'KRT18', 'MUC3A', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'IEP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['HDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'ISS', 'IBA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['NAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['NAS'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['NAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['IMP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'HDA'], ['HDA'], ['IBA'], ['HDA', 'IBA'], ['TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['ISS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA'], ['NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.007377667200571e-06</v>
+        <v>1.254855583096166e-06</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1893,19 +1893,19 @@
         <v>687</v>
       </c>
       <c r="H9" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J9" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3760162601626016</v>
+        <v>0.3772819472616633</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2692867540029112</v>
+        <v>0.2707423580786026</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'MUC5AC', 'ANXA7', 'ADM', 'AXL', 'S100A13', 'PROCR', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'PPIB', 'HSPA8', 'RTN4RL2', 'EIF2S3', 'GAL', 'UPK1B', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'RPL37A', 'KRT8', 'ATP1B1', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'S100A11', 'PGK1', 'INA', 'ALDH3A1', 'TGFBI', 'LGALS1', 'COTL1', 'FABP5', 'TUBB', 'NANS', 'SLC12A2', 'CFD', 'KRT81', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'CPNE7', 'CDK1', 'RPL26', 'PRSS3', 'LGALS3BP', 'DKK1', 'EZR', 'RHOF', 'CD44', 'CCL2', 'SLC3A2', 'CTSL', 'EXOSC9', 'PGD', 'TAGLN2', 'KRT18', 'HLA-A', 'IGFBP4', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'NT5E', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'S100A6', 'ALDH1A1', 'ENO1', 'EIF6', 'PCSK1N', 'PPP1R7', 'LIPH', 'EPS8', 'RPS28', 'BLVRB', 'HSPA5', 'PPP1CB', 'SLC2A1', 'CCT5', 'YARS', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'AKR1C1', 'MMP7', 'HMGB2', 'AGR2', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'RPL39', 'COL5A2', 'NCL', 'CKB', 'MYL6', 'CXCL5', 'CD70', 'B4GALT1', 'PRKCA', 'SPP1', 'CD63', 'PAPPA', 'S100A4', 'RPS15A', 'IGFBP7', 'ACTB', 'TIMP1', 'MYL12B', 'SYNGR2', 'F12', 'CRELD2', 'CAPG', 'RPL27', 'LXN', 'GCNT3', 'ANXA5', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'KIF3A', 'TFF1', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'PHGDH', 'ARPC3', 'SLPI', 'CAPZA1', 'CHP1', 'STC2', 'VIM', 'RPS29', 'KRT7', 'BASP1', 'ANXA3', 'TUBB4B', 'RPL31', 'FGB', 'ANXA1', 'PSMA3', 'LDHB', 'ANXA4', 'KRT19', 'PTPRS', 'CLU', 'RPS18', 'NEU1', 'IGFBP6', 'S100A16', 'S100A10', 'CXCL3', 'SLC27A2', 'PA2G4', 'CCT7', 'B2M', 'INSL4', 'CCT4', 'PRDX1', 'ITGA3', 'EEF1A1', 'FSCN1', 'CDC42']</t>
+          <t>['ALDH3A1', 'HSPE1', 'MYL12B', 'B2M', 'CHP1', 'IGFBP7', 'AKR1C1', 'LIPH', 'PRKCA', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'TFF1', 'GCNT3', 'GAL', 'PA2G4', 'TUBA1A', 'SLC27A2', 'CCT7', 'TXN', 'CD70', 'CDC42', 'B4GALT1', 'NEU1', 'HSPA8', 'CCT4', 'CPNE7', 'RPS15A', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'RSPO3', 'ALDH7A1', 'SQSTM1', 'SFN', 'NANS', 'TAGLN2', 'EPS8', 'COL5A2', 'SERPINE2', 'DKK1', 'GLRX', 'RPS18', 'ANXA1', 'SDC4', 'CRELD2', 'TGFBI', 'EIF6', 'SFRP1', 'SLC35F6', 'SYNGR2', 'RPL28', 'CFD', 'FGB', 'RPL39', 'F12', 'FABP5', 'YARS', 'IGFBP6', 'ACTG1', 'VAMP8', 'CTSL', 'MARCKSL1', 'S100A6', 'SULT2B1', 'CXCL3', 'BASP1', 'PHGDH', 'S100A16', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'LXN', 'GPRC5A', 'PCSK1N', 'CKB', 'MUC5AC', 'ANXA7', 'S100A4', 'EEF1A1', 'VIM', 'INSL4', 'TIMP1', 'TXNRD1', 'HSPA5', 'PKM', 'S100A13', 'PRDX1', 'ATP1B1', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'PTPRS', 'PPA1', 'EZR', 'HSPA2', 'ENO1', 'S100A10', 'HLA-A', 'ADM', 'RPL34', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'CXCL5', 'ANXA3', 'CDK1', 'RPS28', 'AIMP1', 'COTL1', 'AKR1B1', 'NCL', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CCL2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'INA', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'PLAU', 'HSP90AB1', 'NT5E', 'BLVRB', 'MARCKS', 'GSTO1', 'CTNNB1', 'FN1', 'ALDH1A1', 'IGFBP4', 'SPP1', 'PAPPA', 'RPL31', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'UPK1B', 'RAP2B', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'LDHB', 'MTHFD2', 'ARPC3', 'MMP7', 'CST3', 'APOE', 'RPL26', 'PRSS3', 'ACTB', 'RHOF', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'IGFBP3', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA'], ['IBA'], ['HDA'], ['HDA', 'ISS', 'IBA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['TAS'], ['IMP', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA'], ['HDA'], ['IBA'], ['HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['ISS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.621334531367479e-05</v>
+        <v>9.613489162344046e-06</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -1956,22 +1956,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="H10" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I10" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J10" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4817073170731707</v>
+        <v>0.4888438133874239</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2463617463617464</v>
+        <v>0.2469262295081967</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'RPL35', 'GPX1', 'ARL6IP1', 'S100A13', 'AIMP1', 'GLRX', 'HSPD1', 'EIF4A1', 'S100A3', 'NUDC', 'PPIB', 'HSPA8', 'EIF2S3', 'CDA', 'TMSB4X', 'RQCD1', 'NFKBIA', 'DDX21', 'HSPA2', 'SERPINE2', 'PSAT1', 'CCND3', 'INPP1', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'TRIB3', 'KRT8', 'LMNA', 'GPX2', 'RBCK1', 'PKM', 'CTNNB1', 'SQSTM1', 'SSB', 'PGK1', 'PHKG1', 'ALDH3A1', 'LGALS1', 'COTL1', 'CDK6', 'FABP5', 'TUBB', 'FBXO2', 'PTRH2', 'NANS', 'ZC3H4', 'TNNT1', 'KRT81', 'GLRX3', 'RAP2B', 'PKMYT1', 'CDK1', 'RPL26', 'ANKRD28', 'AKAP12', 'RPL41', 'UBE2S', 'EZR', 'RHOF', 'PPP1R14A', 'ILF2', 'UMPS', 'CD44', 'CCNB2', 'PSMD14', 'OAS1', 'PSMC2', 'RPS27L', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'NDUFAF4', 'TP53I3', 'NQO1', 'CDCA4', 'AKR1B10', 'KPNA2', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'HEXA', 'RPL34', 'PPA1', 'AP1M2', 'NT5E', 'ZFP36L1', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'DCAF13', 'ENO1', 'EIF6', 'RND3', 'RPS28', 'CDKN1A', 'IDI1', 'BLVRB', 'MCL1', 'HSPA5', 'PPP1CB', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'AKR1C2', 'TXNRD1', 'CENPA', 'SULT2B1', 'SLC35F6', 'HNRNPH1', 'CAMK1', 'AKR1C1', 'RPS17', 'DOCK5', 'SFRP1', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'HMGA1', 'CKB', 'MYL6', 'UBE2C', 'GMPS', 'BCL2L1', 'PRKCA', 'S100A4', 'RPS15A', 'PFDN2', 'ACTB', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'GCHFR', 'HERC4', 'MYL12B', 'CDKN3', 'PHLDA1', 'MT2A', 'RPL27', 'ATF4', 'ANXA5', 'ECH1', 'RAI14', 'HSP90AA1', 'TUBA1A', 'LDHA', 'PDLIM7', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'CES1', 'PDLIM5', 'EIF3D', 'TNRC6B', 'AMOTL2', 'GSTO1', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'ARPC3', 'FGFR1', 'CAPZA1', 'CTNNAL1', 'PTTG1', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'PSMC4', 'TPM1', 'XRCC5', 'CPLX2', 'PRMT1', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'TSC22D1', 'ANXA1', 'PSMA3', 'RAB11FIP1', 'LDHB', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'RPS18', 'BIRC5', 'NIP7', 'PTGES3', 'S100A16', 'SLC27A2', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'CCT4', 'PRDX1', 'NNMT', 'PIR', 'DYNLL1', 'RPS24', 'C19orf33', 'EEF1A1', 'SH3KBP1', 'FSCN1', 'CCNB1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'PKMYT1', 'AKR1C1', 'RQCD1', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'KRT19', 'CD44', 'KRT8', 'EXOSC9', 'LGALS1', 'TUBA1A', 'TP53I3', 'PIR', 'PFDN2', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'CDC42', 'NFKBIA', 'HSPA8', 'CCT4', 'RPS15A', 'FGFR1', 'LGALS3', 'EIF2S3', 'PSMA3', 'ANXA2', 'LMNA', 'ALDH7A1', 'SQSTM1', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'SFN', 'NANS', 'RPS27L', 'TAGLN2', 'EIF3D', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'GLRX', 'CENPA', 'AKAP12', 'RPS18', 'ANXA1', 'SAT1', 'INO80C', 'ARL1', 'EIF6', 'SFRP1', 'SLC35F6', 'HERC4', 'RND3', 'KRT80', 'RPL28', 'PDLIM5', 'AP1M2', 'RPL39', 'RBCK1', 'FABP5', 'YARS', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'NT5DC3', 'VAMP8', 'CDKN3', 'S100A6', 'SULT2B1', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'CDK6', 'CCNB1', 'GTPBP4', 'PHGDH', 'S100A16', 'KIF23', 'CLU', 'HSPD1', 'SLC7A5', 'PPP1R14A', 'TGFBR2', 'CKB', 'ODC1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'PDLIM7', 'RAB11FIP1', 'TPM1', 'MT2A', 'CCND1', 'RPS24', 'UCHL1', 'S100A4', 'EEF1A1', 'VIM', 'PTGES3', 'TMSB4X', 'DDX21', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'UBE2C', 'ILF2', 'PRDX1', 'DYNLL1', 'KRT81', 'MYL6', 'PPP1CB', 'TRIB3', 'PTPRS', 'PPA1', 'CES1', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'IDI1', 'KYNU', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'AKR1C2', 'GMPS', 'GPX1', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'GLRX3', 'CDK1', 'DOCK5', 'UBE2S', 'SH3KBP1', 'RPS28', 'AIMP1', 'PSMC2', 'COTL1', 'AKR1B1', 'GPX2', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'MAGED2', 'FSCN1', 'OPTN', 'EIF4A1', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'HSP90AB1', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'MARCKS', 'AKR1B10', 'GSTO1', 'CTNNB1', 'CCNB2', 'ALDH1A1', 'HNRNPH1', 'PTRH2', 'RPL31', 'SSB', 'PGD', 'TYMP', 'KRT7', 'BIRC5', 'CAPZA1', 'EIF4EBP1', 'RAP2B', 'PSAT1', 'PPIB', 'S100A3', 'LDHB', 'ARPC3', 'NNMT', 'ELF3', 'ATF4', 'NDUFAF4', 'HMGA1', 'RPL26', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'YWHAE', 'RPS29', 'PPP3CA', 'INPP1', 'KRT18', 'KIF3A', 'ECH1', 'MYL12A', 'TNNT1', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'TAS', 'IEA'], ['IMP', 'IBA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IBA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IBA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'NAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS']]</t>
+          <t>[['IDA', 'ISS', 'TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['IDA', 'ISS', 'TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS'], ['IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IBA'], ['IDA'], ['IDA'], ['IDA', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'TAS', 'NAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IBA', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IMP', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.00028878419989275</v>
+        <v>0.0001079472326771498</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1931</v>
+        <v>1942</v>
       </c>
       <c r="H11" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I11" t="n">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J11" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2092180217503884</v>
+        <v>0.2100926879505664</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2051,59 +2051,59 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ADM', 'ARL6IP1', 'S100A13', 'PROCR', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'RABAC1', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'FEZ2', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'INPP1', 'TRIML2', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'ALG8', 'KRT8', 'CNIH4', 'CEBPB', 'PHLDA2', 'DEGS1', 'LMNA', 'GPX2', 'RBCK1', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'PHKG1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'COTL1', 'CDK6', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'NANS', 'SLC12A2', 'CFD', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'RPL26', 'ANKRD28', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'PLPP5', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'PPP1R14A', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'PHACTR2', 'HLA-A', 'IGFBP4', 'NDUFAF4', 'DUSP1', 'TP53I3', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'HEXA', 'RPL34', 'PPA1', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'PPP1R7', 'RND3', 'MYC', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'CDKN1A', 'IDI1', 'BLVRB', 'MCL1', 'HSPA5', 'PPP1CB', 'TRAM1', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'AKR1C2', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'SLC35F6', 'MUC12', 'HNRNPH1', 'LRRC75A', 'CAMK1', 'GCNT2', 'AKR1C1', 'RPS17', 'B4GALT4', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'EIF1AY', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'BZW1', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'MMD', 'GMPS', 'B4GALT1', 'BCL2L1', 'PRKCA', 'SPP1', 'CD63', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'CRIP2', 'ETFB', 'B4GALT5', 'MUC3A', 'ACTB', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'COX14', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'LXN', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HSP90AA1', 'TUBA1A', 'LDHA', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'MRPS30', 'EIF3D', 'LAPTM4A', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'EPHX1', 'PSMC4', 'TPM1', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'FGB', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'DNAJC12', 'S100A16', 'IRF2BP2', 'S100A10', 'SLC27A2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'CCT4', 'PRDX1', 'SOX4', 'NNMT', 'ITGA3', 'CLSPN', 'YPEL5', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'PHLDA3', 'SMIM14', 'TMPO', 'FSCN1', 'CCNB1', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'DKC1', 'HSPE1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'AKR1C1', 'RQCD1', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'RBFOX3', 'TUBA1A', 'TP53I3', 'PIR', 'COX7B', 'PFDN2', 'CNN2', 'LRRC75A', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'MKNK2', 'SUCLG1', 'CLSPN', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'NFKBIA', 'DNAJC12', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'ALDH7A1', 'MUC12', 'SQSTM1', 'TRIML2', 'PHLDA3', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'SFN', 'G0S2', 'NANS', 'EPHX1', 'EIF1AY', 'RPS27L', 'TAGLN2', 'EPS8', 'EIF3D', 'COL5A2', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SAT1', 'SDC4', 'EMP2', 'INO80C', 'CRELD2', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'HERC4', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'CFD', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'RBCK1', 'F12', 'FABP5', 'YARS', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'NT5DC3', 'VAMP8', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'SMAGP', 'KIF23', 'CLU', 'ITGA3', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'TGFBR2', 'PCSK1N', 'CKB', 'DDX10', 'ODC1', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'GOLIM4', 'MT2A', 'CCND1', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'VIM', 'PTGES3', 'BZW1', 'TMSB4X', 'FDFT1', 'PHLDA2', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'FEZ2', 'ILF2', 'BTG1', 'PRDX1', 'DYNLL1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'AKR1C2', 'SCD', 'GMPS', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'GPX2', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'MAGED2', 'LGALS3BP', 'FSCN1', 'OPTN', 'INA', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'MARCKS', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'ABCG2', 'RPL31', 'DDX39A', 'CRIP2', 'SSB', 'PGD', 'TYMP', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'NNMT', 'ELF3', 'B4GALT4', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'INPP1', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA'], ['TAS'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['IDA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['TAS'], ['IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:MF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GO:0005622</t>
+          <t>GO:0019899</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>intracellular anatomical structure</t>
+          <t>enzyme binding</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.0004610693005017077</v>
+        <v>0.0006122826722998968</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>"A component of a cell contained within (but not including) the plasma membrane. In eukaryotes it includes the nucleus and cytoplasm." [ISBN:0198506732]</t>
+          <t>"Binding to an enzyme, a protein with catalytic activity." [GOC:jl]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2196</v>
+        <v>370</v>
       </c>
       <c r="H12" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I12" t="n">
-        <v>444</v>
+        <v>109</v>
       </c>
       <c r="J12" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.2210953346855984</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2021857923497268</v>
+        <v>0.2945945945945946</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0005515']</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ADM', 'ARL6IP1', 'AXL', 'S100A13', 'PROCR', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'RABAC1', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'FEZ2', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'INPP1', 'TSPYL1', 'TRIML2', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'CNIH4', 'CEBPB', 'PHLDA2', 'DEGS1', 'LMNA', 'GPX2', 'RBCK1', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'PHKG1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'NANS', 'SLC12A2', 'CFD', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'PLPP5', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'PPP1R14A', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'PHACTR2', 'HLA-A', 'IGFBP4', 'NDUFAF4', 'SNW1', 'DUSP1', 'TP53I3', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'PPP1R7', 'RND3', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'TRAM1', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'AKR1C2', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'SLC35F6', 'MUC12', 'HNRNPH1', 'TCEAL8', 'LRRC75A', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'RPS17', 'B4GALT4', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'EIF1AY', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'BZW1', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'MMD', 'GMPS', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'PRKCA', 'SPP1', 'NEAT1', 'CD63', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'CRIP2', 'ETFB', 'B4GALT5', 'FOXM1', 'MUC3A', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'COX14', 'HES4', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'LXN', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'MRPS30', 'EIF3D', 'LAPTM4A', 'SFR1', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'DNAJC12', 'S100A16', 'IRF2BP2', 'S100A10', 'TRMT6', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'CCT4', 'PRDX1', 'SOX4', 'NNMT', 'ITGA3', 'CLSPN', 'YPEL5', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'PHLDA3', 'SMIM14', 'TMPO', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['HM13', 'CALM2', 'XRCC5', 'CHP1', 'RQCD1', 'KPNA2', 'RIPK2', 'PRKCA', 'PA2G4', 'SLC27A2', 'CDC42', 'NFKBIA', 'HSPA8', 'CEBPB', 'LGALS3', 'PSMA3', 'ANXA2', 'SQSTM1', 'TDG', 'SFN', 'EPS8', 'CKS2', 'AKAP12', 'SDC4', 'EMP2', 'FOXM1', 'RND3', 'PDLIM5', 'RABAC1', 'PHKG1', 'ACTG1', 'CKS1B', 'GCHFR', 'NPM1', 'CDKN1A', 'DUSP1', 'CCNB1', 'CLU', 'ITGA3', 'HSPD1', 'CKB', 'CAV1', 'PRMT1', 'CD24', 'RAB11FIP1', 'CCND1', 'UBE2T', 'UCHL1', 'EEF1A1', 'PTGES3', 'TMSB4X', 'TIMP1', 'RIN2', 'HSPA5', 'UBE2C', 'BTG1', 'ATP1B1', 'SLPI', 'PPP1CB', 'TRIB3', 'EGR1', 'EZR', 'HSPA2', 'ENO1', 'BCL2L1', 'SLC12A2', 'GLRX3', 'DOCK5', 'SH3KBP1', 'AIMP1', 'COTL1', 'TSPYL1', 'NCL', 'PLAUR', 'TUBB', 'CAV2', 'CDT1', 'PCNA', 'FGD6', 'SLC2A1', 'HSP90AA1', 'HSP90AB1', 'CYB5A', 'PSMD1', 'MARCKS', 'MDM4', 'CTNNB1', 'FN1', 'BIRC5', 'TOP2A', 'STC2', 'PPIB', 'LDHB', 'ATF4', 'CST3', 'APOE', 'HMGA1', 'CCND3', 'ACTB', 'RHOF', 'HACD3', 'EGLN1', 'YWHAE', 'SNW1', 'PPP3CA', 'TOB1', 'TOR1AIP2', 'KIF3A', 'TUBA1B']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IBA', 'NAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA']]</t>
+          <t>[['IPI'], ['IPI'], ['IPI'], ['ISS'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['ISS', 'IEA'], ['IBA'], ['IPI'], ['IEA'], ['IPI'], ['IPI'], ['IBA'], ['ISS'], ['IEA'], ['IEA'], ['IPI', 'IBA'], ['IBA'], ['IBA'], ['IPI'], ['IPI'], ['ISS', 'IEA'], ['IPI'], ['IDA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IBA'], ['IPI'], ['IPI'], ['IPI', 'NAS'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IBA'], ['IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IBA', 'IEA'], ['IBA'], ['IPI', 'IEA'], ['ISS'], ['IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['EXP', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA'], ['IPI'], ['IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IBA'], ['IDA'], ['ISS'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IDA'], ['IPI'], ['IPI'], ['IPI']]</t>
         </is>
       </c>
     </row>
@@ -2134,42 +2134,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GO:0005575</t>
+          <t>GO:0005622</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cellular_component</t>
+          <t>intracellular anatomical structure</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.001877876634482963</v>
+        <v>0.0009480959224505942</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>"A location, relative to cellular compartments and structures, occupied by a macromolecular machine. There are three types of cellular components described in the gene ontology: (1) the cellular anatomical entity where a gene product carries out a molecular function (e.g., plasma membrane, cytoskeleton) or membrane-enclosed compartments (e.g., mitochondrion); (2) virion components, where viral proteins act, and (3) the stable macromolecular complexes of which gene product are parts (e.g., the clathrin complex)." [GOC:pdt]</t>
+          <t>"A component of a cell contained within (but not including) the plasma membrane. In eukaryotes it includes the nucleus and cytoplasm." [ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2521</v>
+        <v>2202</v>
       </c>
       <c r="H13" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I13" t="n">
-        <v>485</v>
+        <v>445</v>
       </c>
       <c r="J13" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9857723577235772</v>
+        <v>0.9026369168356998</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1923839746132487</v>
+        <v>0.2020890099909173</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2178,64 +2178,64 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ADM', 'ARL6IP1', 'DNAJC22', 'AXL', 'S100A13', 'PROCR', 'ADAMTS12', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'TM4SF1', 'RABAC1', 'CKS2', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'RTN4RL2', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'PCDH9', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'FEZ2', 'UPK1B', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'INPP1', 'TSPYL1', 'HPCAL1', 'TRIML2', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'ATP1B1', 'CNIH4', 'CEBPB', 'PHLDA2', 'DEGS1', 'LMNA', 'GPX2', 'RBCK1', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'PHKG1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'NANS', 'SLC12A2', 'CFD', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'PMP22', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'PLPP5', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'PPP1R14A', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCL2', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'PHACTR2', 'HLA-A', 'TMEM205', 'IGFBP4', 'NDUFAF4', 'SLC35F3', 'SNW1', 'DUSP1', 'TP53I3', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'DCBLD2', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'C1orf56', 'PPP1R7', 'RND3', 'LIPH', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'MDK', 'TRAM1', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'AKR1C2', 'EVA1C', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'TNFRSF12A', 'SLC35F6', 'MUC12', 'HNRNPH1', 'TCEAL8', 'LRRC75A', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'RPS17', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'EIF1AY', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'BZW1', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'CXCL5', 'MMD', 'GMPS', 'CD70', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'SMIM6', 'PRKCA', 'SPP1', 'NINJ1', 'NEAT1', 'CD63', 'PAPPA', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'CRIP2', 'ETFB', 'B4GALT5', 'FOXM1', 'MUC3A', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'COX14', 'TM4SF4', 'HES4', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'LXN', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'SEMA4B', 'MRPS30', 'EIF3D', 'KCNMA1', 'LAPTM4A', 'SFR1', 'TFF1', 'EFHD2', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'SLC16A5', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'RSPO3', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'ANKRD40', 'IGFBP6', 'DNAJC12', 'S100A16', 'IRF2BP2', 'S100A10', 'CXCL3', 'TRMT6', 'PBDC1', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'INSL4', 'CCT4', 'PRDX1', 'SOX4', 'NNMT', 'ITGA3', 'CLSPN', 'EMP3', 'YPEL5', 'TMEM54', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'PHLDA3', 'SLC4A7', 'SMIM14', 'TMPO', 'PAQR5', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'DKC1', 'HSPE1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'AKR1C1', 'RQCD1', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'RBFOX3', 'TUBA1A', 'TP53I3', 'PIR', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'LRRC75A', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'NFKBIA', 'DNAJC12', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'ALDH7A1', 'MUC12', 'HES4', 'SQSTM1', 'TRIML2', 'PHLDA3', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'NANS', 'EPHX1', 'EIF1AY', 'RPS27L', 'TAGLN2', 'EPS8', 'EIF3D', 'COL5A2', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SAT1', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'HERC4', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'CFD', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'RBCK1', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'TGFBR2', 'PCSK1N', 'CKB', 'DDX10', 'ODC1', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'CD24', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'GOLIM4', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'PTGES3', 'BZW1', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'PHLDA2', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'FEZ2', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'AKR1C2', 'SCD', 'GMPS', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'GPX2', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'CRIP2', 'SSB', 'PGD', 'TYMP', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'NNMT', 'ELF3', 'B4GALT4', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'INPP1', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS'], ['IDA', 'IEP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['HDA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'ND', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ND', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'ND', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ND', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'ND', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'ND', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ND'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['ND'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ND', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GO:MF</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GO:0019899</t>
+          <t>GO:0043227</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>enzyme binding</t>
+          <t>membrane-bounded organelle</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.002353355563613063</v>
+        <v>0.002306039972220594</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>"Binding to an enzyme, a protein with catalytic activity." [GOC:jl]</t>
+          <t>"Organized structure of distinctive morphology and function, bounded by a single or double lipid bilayer membrane. Includes the nucleus, mitochondria, plastids, vacuoles, and vesicles. Excludes the plasma membrane." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>379</v>
+        <v>2007</v>
       </c>
       <c r="H14" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I14" t="n">
-        <v>109</v>
+        <v>414</v>
       </c>
       <c r="J14" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2215447154471545</v>
+        <v>0.8397565922920892</v>
       </c>
       <c r="L14" t="n">
-        <v>0.287598944591029</v>
+        <v>0.2062780269058296</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2244,17 +2244,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>['GO:0005515']</t>
+          <t>['GO:0043226']</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'ACTG1', 'AIMP1', 'HSPD1', 'APOE', 'RABAC1', 'CKS2', 'PPIB', 'HSPA8', 'TOP2A', 'TMSB4X', 'RQCD1', 'NFKBIA', 'HSPA2', 'MARCKS', 'CCND3', 'TSPYL1', 'TRIB3', 'TDG', 'ATP1B1', 'CEBPB', 'CTNNB1', 'SQSTM1', 'PHKG1', 'COTL1', 'TUBB', 'SLC12A2', 'TUBA1B', 'GLRX3', 'SDC4', 'FN1', 'AKAP12', 'TOB1', 'EZR', 'RHOF', 'TOR1AIP2', 'EMP2', 'CYB5A', 'SNW1', 'DUSP1', 'KPNA2', 'ANXA2', 'PCNA', 'CAV1', 'FGD6', 'YWHAE', 'PPP3CA', 'ENO1', 'PLAUR', 'RND3', 'EPS8', 'CAV2', 'CDKN1A', 'HSPA5', 'PPP1CB', 'SLC2A1', 'EGR1', 'MDM4', 'DOCK5', 'LGALS3', 'HMGA1', 'NCL', 'CKB', 'UBE2C', 'BCL2L1', 'UBE2T', 'PRKCA', 'FOXM1', 'ACTB', 'CKS1B', 'PSMD1', 'NPM1', 'GCHFR', 'TIMP1', 'ATF4', 'HSP90AA1', 'KIF3A', 'PDLIM5', 'CST3', 'SFN', 'UCHL1', 'SLPI', 'CDT1', 'CHP1', 'HM13', 'STC2', 'EGLN1', 'XRCC5', 'PRMT1', 'CD24', 'PSMA3', 'RAB11FIP1', 'LDHB', 'RIN2', 'CLU', 'BIRC5', 'PTGES3', 'SLC27A2', 'PA2G4', 'CCND1', 'ITGA3', 'DYNLL1', 'BTG1', 'HACD3', 'EEF1A1', 'SH3KBP1', 'CCNB1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'DKC1', 'HSPE1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'AKR1C1', 'RQCD1', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'RBFOX3', 'TUBA1A', 'PIR', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'CD70', 'CDC42', 'MMD', 'GRPEL1', 'NFKBIA', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'ALDH7A1', 'MUC12', 'HES4', 'SQSTM1', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'NANS', 'EPHX1', 'RPS27L', 'TAGLN2', 'EPS8', 'COL5A2', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'PDHA1', 'RPS18', 'APOBEC3C', 'ANXA1', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'HERC4', 'RND3', 'SYNGR2', 'TM4SF20', 'RPL28', 'CFD', 'ANP32A', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'CDA', 'RPL41', 'ACTG1', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'GPRC5A', 'LY6K', 'TGFBR2', 'PCSK1N', 'CKB', 'DDX10', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'CD24', 'PDLIM7', 'RAB11FIP1', 'IK', 'GOLIM4', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'PTGES3', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MRPL13', 'CCDC85B', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'SCD', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'GLRX3', 'ANXA3', 'CDK1', 'UBE2S', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'ALDH1A1', 'IGFBP4', 'MGST1', 'SPP1', 'HNRNPH1', 'PTRH2', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'PTPRF', 'SSB', 'PGD', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'UPK1B', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'ELF3', 'B4GALT4', 'MMP7', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IBA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IPI', 'IEA'], ['IEA'], ['EXP', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IEA'], ['IPI'], ['IPI'], ['IDA'], ['IPI'], ['IBA'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['ISS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['ISS'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IBA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IPI', 'IEA'], ['IPI'], ['IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA'], ['IPI'], ['IPI', 'IBA'], ['IBA', 'IEA'], ['IPI'], ['IPI'], ['IBA'], ['IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['ISS'], ['IPI'], ['IBA', 'IEA'], ['IPI'], ['IPI'], ['IBA'], ['ISS'], ['IPI'], ['IDA'], ['ISS'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IEA'], ['IBA'], ['IDA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IEA'], ['IPI', 'NAS'], ['IDA'], ['IPI'], ['IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI']]</t>
+          <t>[['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IBA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['IDA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['HTP'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['HDA', 'ISS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'NAS'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA'], ['ISS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA'], ['HDA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -2266,42 +2266,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GO:0043227</t>
+          <t>GO:0005575</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>membrane-bounded organelle</t>
+          <t>cellular_component</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.008970471148758615</v>
+        <v>0.003115492449484222</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, bounded by a single or double lipid bilayer membrane. Includes the nucleus, mitochondria, plastids, vacuoles, and vesicles. Excludes the plasma membrane." [GOC:go_curators]</t>
+          <t>"A location, relative to cellular compartments and structures, occupied by a macromolecular machine. There are three types of cellular components described in the gene ontology: (1) the cellular anatomical entity where a gene product carries out a molecular function (e.g., plasma membrane, cytoskeleton) or membrane-enclosed compartments (e.g., mitochondrion); (2) virion components, where viral proteins act, and (3) the stable macromolecular complexes of which gene product are parts (e.g., the clathrin complex)." [GOC:pdt]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1994</v>
+        <v>2514</v>
       </c>
       <c r="H15" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I15" t="n">
-        <v>409</v>
+        <v>485</v>
       </c>
       <c r="J15" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8313008130081301</v>
+        <v>0.9837728194726166</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2051153460381143</v>
+        <v>0.1929196499602228</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2310,17 +2310,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>['GO:0043226']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ARL6IP1', 'AXL', 'S100A13', 'PROCR', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'RABAC1', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'RTN4RL2', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'UPK1B', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'TSPYL1', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'ATP1B1', 'CNIH4', 'CEBPB', 'DEGS1', 'LMNA', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'LETM1', 'PTRH2', 'NANS', 'SLC12A2', 'CFD', 'SLC16A3', 'ZC3H4', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'CUTC', 'PHACTR2', 'HLA-A', 'IGFBP4', 'NDUFAF4', 'SNW1', 'DUSP1', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'PPP1R7', 'RND3', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'TRAM1', 'FDPS', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'SLC35F6', 'MUC12', 'HNRNPH1', 'TCEAL8', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'RPS17', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'SFRP1', 'SLC7A5', 'LGALS3', 'ALDH7A1', 'RAN', 'RPL39', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'MMD', 'CD70', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'PRKCA', 'SPP1', 'NEAT1', 'CD63', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'ETFB', 'B4GALT5', 'FOXM1', 'MUC3A', 'ACTB', 'CKS1B', 'PSMD1', 'NPM1', 'COX14', 'HES4', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'MRPS30', 'LAPTM4A', 'SFR1', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'S100A16', 'IRF2BP2', 'S100A10', 'TRMT6', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'CCT4', 'PRDX1', 'SOX4', 'ITGA3', 'CLSPN', 'YPEL5', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'SMIM14', 'TMPO', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'C1orf56', 'DKC1', 'HSPE1', 'CTTN', 'TNFRSF12A', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'PAQR5', 'AKR1C1', 'RQCD1', 'LIPH', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'TFF1', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'TM4SF1', 'RBFOX3', 'TUBA1A', 'TP53I3', 'PIR', 'TMEM205', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'LRRC75A', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'CD70', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'MDK', 'NFKBIA', 'DNAJC12', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'DCBLD2', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'RSPO3', 'ALDH7A1', 'MUC12', 'HES4', 'SQSTM1', 'TRIML2', 'PHLDA3', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'NANS', 'EPHX1', 'EIF1AY', 'RPS27L', 'TAGLN2', 'EPS8', 'NINJ1', 'EIF3D', 'COL5A2', 'ANKRD40', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'CKS2', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SAT1', 'SEMA4B', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'EMP3', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'HERC4', 'KCNMA1', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'ADAMTS12', 'CFD', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'RBCK1', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'IGFBP6', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'TMEM54', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'CXCL3', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'TGFBR2', 'PCSK1N', 'PMP22', 'CKB', 'DDX10', 'ODC1', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'CD24', 'PCDH9', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'GOLIM4', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'INSL4', 'PTGES3', 'BZW1', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'PHLDA2', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'FEZ2', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'AKR1C2', 'SCD', 'GMPS', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'SLC35F3', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'CXCL5', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'TM4SF4', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'GPX2', 'RPL27', 'DNAJC22', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'CCL2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'SLC16A5', 'EFHD2', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'SLC4A7', 'PAPPA', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'PTPRF', 'CRIP2', 'SSB', 'PGD', 'TYMP', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'UPK1B', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'EVA1C', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'NNMT', 'ELF3', 'B4GALT4', 'MMP7', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'HPCAL1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'INPP1', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA'], ['IDA', 'IBA'], ['IBA', 'NAS'], ['IMP', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS'], ['IBA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['HTP', 'ISS', 'IEA'], ['TAS'], ['HDA', 'IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['ISS', 'IBA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HTP'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA']]</t>
+          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ND'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IPI', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01253035630100025</v>
+        <v>0.004262989808113037</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -2352,22 +2352,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="H16" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I16" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J16" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8658536585365854</v>
+        <v>0.8722109533468559</v>
       </c>
       <c r="L16" t="n">
-        <v>0.202375296912114</v>
+        <v>0.2033096926713948</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ARL6IP1', 'AXL', 'S100A13', 'PROCR', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'RABAC1', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'RTN4RL2', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'UPK1B', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'TSPYL1', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'ATP1B1', 'CNIH4', 'CEBPB', 'DEGS1', 'LMNA', 'GPX2', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'NANS', 'SLC12A2', 'CFD', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'CUTC', 'PHACTR2', 'HLA-A', 'IGFBP4', 'NDUFAF4', 'SNW1', 'DUSP1', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'PPP1R7', 'RND3', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'TRAM1', 'FDPS', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'SLC35F6', 'MUC12', 'HNRNPH1', 'TCEAL8', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'RPS17', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'MMD', 'CD70', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'PRKCA', 'SPP1', 'NEAT1', 'CD63', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'ETFB', 'B4GALT5', 'FOXM1', 'MUC3A', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'COX14', 'HES4', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'SEMA4B', 'MRPS30', 'LAPTM4A', 'SFR1', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'S100A16', 'IRF2BP2', 'S100A10', 'TRMT6', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'CCT4', 'PRDX1', 'SOX4', 'ITGA3', 'CLSPN', 'YPEL5', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'SLC4A7', 'SMIM14', 'TMPO', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'DKC1', 'HSPE1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'AKR1C1', 'RQCD1', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'RBFOX3', 'TUBA1A', 'PIR', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'CD70', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'NFKBIA', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'ALDH7A1', 'MUC12', 'HES4', 'SQSTM1', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'NANS', 'EPHX1', 'RPS27L', 'TAGLN2', 'EPS8', 'COL5A2', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SEMA4B', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'HERC4', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'CFD', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'CDA', 'RPL41', 'ACTG1', 'PARD3', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'GPRC5A', 'LY6K', 'TGFBR2', 'PCSK1N', 'CKB', 'DDX10', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'CD24', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'GOLIM4', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'PTGES3', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'SCD', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'GPX2', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'ALDH1A1', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'SLC4A7', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'PTPRF', 'SSB', 'PGD', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'UPK1B', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'ELF3', 'B4GALT4', 'MMP7', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['HDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['HDA', 'IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HTP'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA']]</t>
+          <t>[['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['TAS'], ['ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['HDA', 'ISS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['IDA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HTP'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['HDA', 'ISS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA'], ['HDA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -2398,42 +2398,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GO:0045296</t>
+          <t>GO:0005488</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cadherin binding</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01283147536354302</v>
+        <v>0.006121785118908814</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>"Binding to cadherin, a type I membrane protein involved in cell adhesion." [GOC:bf]</t>
+          <t>"The selective, non-covalent, often stoichiometric, interaction of a molecule with one or more specific sites on another molecule." [GOC:ceb, GOC:mah, ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>83</v>
+        <v>2380</v>
       </c>
       <c r="H17" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>468</v>
       </c>
       <c r="J17" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07113821138211382</v>
+        <v>0.949290060851927</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4216867469879518</v>
+        <v>0.1966386554621849</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>['GO:0050839']</t>
+          <t>['GO:0003674']</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'NUDC', 'HSPA8', 'EIF2S3', 'PKM', 'CTNNB1', 'S100A11', 'EZR', 'CCNB2', 'SLC3A2', 'TAGLN2', 'KRT18', 'GPRC5A', 'PDLIM1', 'ANXA2', 'RPL34', 'YWHAE', 'ENO1', 'HSPA5', 'RAN', 'BZW1', 'CNN2', 'CAPG', 'LDHA', 'CTTN', 'PDLIM5', 'EFHD2', 'SFN', 'CAPZA1', 'CTNNAL1', 'RSL1D1', 'ANXA1', 'PRDX1', 'TMPO', 'FSCN1']</t>
+          <t>['ALDH3A1', 'HM13', 'C1orf56', 'DKC1', 'HSPE1', 'CTTN', 'TNFRSF12A', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'PAQR5', 'AKR1C1', 'RQCD1', 'LIPH', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'TFF1', 'GAL', 'PA2G4', 'TM4SF1', 'RBFOX3', 'TUBA1A', 'TP53I3', 'PIR', 'TMEM205', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'CD70', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'MDK', 'NFKBIA', 'DNAJC12', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'DCBLD2', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'RSPO3', 'ALDH7A1', 'HES4', 'SQSTM1', 'TRIML2', 'PHLDA3', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'EPHX1', 'EIF1AY', 'RPS27L', 'TAGLN2', 'EPS8', 'NINJ1', 'EIF3D', 'COL5A2', 'ANKRD40', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'CKS2', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SAT1', 'SEMA4B', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'EMP3', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'KCNMA1', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'ADAMTS12', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'RBCK1', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'IGFBP6', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'TMEM54', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'CXCL3', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'LXN', 'GPRC5A', 'TGFBR2', 'PCSK1N', 'PMP22', 'CKB', 'DDX10', 'ODC1', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'CD24', 'PCDH9', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'INSL4', 'PTGES3', 'BZW1', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'PHLDA2', 'C16orf74', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'FEZ2', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'AKR1C2', 'SCD', 'GMPS', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'CXCL5', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'TM4SF4', 'NCL', 'PLAUR', 'ETFB', 'RPL27', 'DNAJC22', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'CCL2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'PBDC1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'SLC16A5', 'EFHD2', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'SLC4A7', 'PAPPA', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'PTPRF', 'CRIP2', 'SSB', 'PGD', 'TYMP', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'UPK1B', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'EVA1C', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'ELF3', 'B4GALT4', 'MMP7', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'HPCAL1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'INPP1', 'KRT18', 'TOR1AIP2', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'ISS', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IPI', 'TAS', 'IC', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI'], ['IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'NAS'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IMP', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS'], ['IPI'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'TAS'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['TAS'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IC', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'HDA'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'TAS'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IEA'], ['IPI', 'IBA'], ['IDA'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP'], ['ISS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'IC', 'IEA'], ['IPI', 'ISS'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['TAS'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'NAS'], ['IPI', 'HDA', 'IEA'], ['IPI', 'IBA'], ['IPI', 'HDA', 'ISS', 'IEA'], ['IPI', 'HDA', 'IBA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IMP', 'IGI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IC'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'TAS'], ['IPI', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['HDA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'NAS', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['HDA', 'IBA', 'IEA'], ['IPI', 'ISS', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['EXP', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA'], ['IPI', 'IBA'], ['IPI', 'HDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'ISS', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA'], ['IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA'], ['EXP', 'IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'ISS', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2464,42 +2464,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GO:0110165</t>
+          <t>GO:0043229</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cellular anatomical structure</t>
+          <t>intracellular organelle</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01687983705028559</v>
+        <v>0.008178926077146396</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>"A part of a cellular organism consisting of a material entity with granularity above the level of a protein complex but below that of an anatomical system. Note that cellular organisms exclude viruses." [GOC:kmv]</t>
+          <t>"Organized structure of distinctive morphology and function, occurring within the cell. Includes the nucleus, mitochondria, plastids, vacuoles, vesicles, ribosomes and the cytoskeleton. Excludes the plasma membrane." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2507</v>
+        <v>2000</v>
       </c>
       <c r="H18" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I18" t="n">
-        <v>482</v>
+        <v>411</v>
       </c>
       <c r="J18" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9796747967479674</v>
+        <v>0.8336713995943205</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1922616673314719</v>
+        <v>0.2055</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2508,64 +2508,64 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>['GO:0005575']</t>
+          <t>['GO:0005622', 'GO:0043226']</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ADM', 'ARL6IP1', 'DNAJC22', 'AXL', 'S100A13', 'PROCR', 'ADAMTS12', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'TM4SF1', 'RABAC1', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'RTN4RL2', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'PCDH9', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'FEZ2', 'UPK1B', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'INPP1', 'TSPYL1', 'HPCAL1', 'TRIML2', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'ATP1B1', 'CNIH4', 'CEBPB', 'PHLDA2', 'DEGS1', 'LMNA', 'GPX2', 'RBCK1', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'PHKG1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'NANS', 'SLC12A2', 'CFD', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'PMP22', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'PLPP5', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'PPP1R14A', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCL2', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'PHACTR2', 'HLA-A', 'TMEM205', 'IGFBP4', 'NDUFAF4', 'SLC35F3', 'SNW1', 'DUSP1', 'TP53I3', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'DCBLD2', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'C1orf56', 'PPP1R7', 'RND3', 'LIPH', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'MDK', 'TRAM1', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'AKR1C2', 'EVA1C', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'TNFRSF12A', 'SLC35F6', 'MUC12', 'HNRNPH1', 'TCEAL8', 'LRRC75A', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'RPS17', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'EIF1AY', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'BZW1', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'CXCL5', 'MMD', 'GMPS', 'CD70', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'SMIM6', 'PRKCA', 'SPP1', 'NINJ1', 'NEAT1', 'CD63', 'PAPPA', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'CRIP2', 'ETFB', 'B4GALT5', 'FOXM1', 'MUC3A', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'COX14', 'TM4SF4', 'HES4', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'LXN', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'SEMA4B', 'MRPS30', 'EIF3D', 'KCNMA1', 'LAPTM4A', 'SFR1', 'TFF1', 'EFHD2', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'SLC16A5', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'RSPO3', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'IGFBP6', 'DNAJC12', 'S100A16', 'IRF2BP2', 'S100A10', 'CXCL3', 'TRMT6', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'INSL4', 'CCT4', 'PRDX1', 'SOX4', 'NNMT', 'ITGA3', 'CLSPN', 'EMP3', 'YPEL5', 'TMEM54', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'PHLDA3', 'SLC4A7', 'SMIM14', 'TMPO', 'PAQR5', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'DKC1', 'HSPE1', 'CTTN', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'RQCD1', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'RBFOX3', 'TUBA1A', 'PIR', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'NFKBIA', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'ALDH7A1', 'MUC12', 'HES4', 'SQSTM1', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'EPHX1', 'RPS27L', 'TAGLN2', 'COL5A2', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SLC35F6', 'HERC4', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'CFD', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'CDA', 'RPL41', 'ACTG1', 'PARD3', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'GPRC5A', 'LY6K', 'TGFBR2', 'PCSK1N', 'CKB', 'DDX10', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'CD24', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'GOLIM4', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'PTGES3', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'SCD', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'GPX2', 'RPL27', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'CTNNB1', 'FN1', 'CCNB2', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'SSB', 'PGD', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'STC2', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'ELF3', 'B4GALT4', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS'], ['IDA', 'IEP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['HDA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HTP', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA']]</t>
+          <t>[['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['TAS'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HTP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA'], ['IDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:MF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GO:0043229</t>
+          <t>GO:0045296</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>intracellular organelle</t>
+          <t>cadherin binding</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03588605388599021</v>
+        <v>0.01365148201731066</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, occurring within the cell. Includes the nucleus, mitochondria, plastids, vacuoles, vesicles, ribosomes and the cytoskeleton. Excludes the plasma membrane." [GOC:go_curators]</t>
+          <t>"Binding to cadherin, a type I membrane protein involved in cell adhesion." [GOC:bf]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1989</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I19" t="n">
-        <v>406</v>
+        <v>35</v>
       </c>
       <c r="J19" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8252032520325203</v>
+        <v>0.07099391480730223</v>
       </c>
       <c r="L19" t="n">
-        <v>0.20412267471091</v>
+        <v>0.4216867469879518</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2574,17 +2574,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>['GO:0005622', 'GO:0043226']</t>
+          <t>['GO:0050839']</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ARL6IP1', 'AXL', 'S100A13', 'PROCR', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'RABAC1', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'G0S2', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'MARCKS', 'CCND3', 'TSPYL1', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'FKBP11', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'CNIH4', 'CEBPB', 'DEGS1', 'LMNA', 'GPX2', 'IFI27L2', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'INA', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'SLC12A2', 'CFD', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'DKK1', 'EZR', 'RHOF', 'GOLIM4', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'LY6K', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'CUTC', 'PHACTR2', 'HLA-A', 'IGFBP4', 'NDUFAF4', 'SNW1', 'DUSP1', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'PPP1R7', 'RND3', 'MYC', 'MKI67', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'TRAM1', 'FDPS', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'ZFAS1', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'SLC35F6', 'MUC12', 'HNRNPH1', 'TCEAL8', 'CAMK1', 'GCNT2', 'MDM4', 'RPS17', 'B4GALT4', 'HMGB2', 'AGR2', 'DOCK5', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'MMD', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'PRKCA', 'SPP1', 'NEAT1', 'CD63', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'ETFB', 'B4GALT5', 'FOXM1', 'MUC3A', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'COX14', 'HES4', 'GCHFR', 'HERC4', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'OCIAD2', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'GCNT3', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'MRPS30', 'LAPTM4A', 'SFR1', 'TNRC6B', 'AMOTL2', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'S100A16', 'IRF2BP2', 'S100A10', 'TRMT6', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'CCT4', 'PRDX1', 'SOX4', 'CLSPN', 'YPEL5', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'C19orf33', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'SMIM14', 'TMPO', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['CTTN', 'CNN2', 'HSPA8', 'EIF2S3', 'ANXA2', 'SFN', 'TAGLN2', 'ANXA1', 'PDLIM5', 'GPRC5A', 'RSL1D1', 'BZW1', 'HSPA5', 'PKM', 'PRDX1', 'EZR', 'ENO1', 'RPL34', 'CAPG', 'RAN', 'FSCN1', 'HSP90AB1', 'CTNNB1', 'CCNB2', 'EFHD2', 'PDLIM1', 'CAPZA1', 'SLC3A2', 'NUDC', 'CTNNAL1', 'LDHA', 'YWHAE', 'KRT18', 'TMPO', 'S100A11']</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.04396397513857113</v>
+        <v>0.01558282114442863</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -2616,22 +2616,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2248</v>
+        <v>2239</v>
       </c>
       <c r="H20" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I20" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J20" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9065040650406504</v>
+        <v>0.9066937119675457</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1983985765124555</v>
+        <v>0.1996426976328718</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2645,59 +2645,59 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'MUC5AC', 'ANXA7', 'GPX1', 'ADM', 'ARL6IP1', 'DNAJC22', 'AXL', 'S100A13', 'PROCR', 'ADAMTS12', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'TM4SF1', 'RABAC1', 'CKS2', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'RTN4RL2', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'FEZ2', 'UPK1B', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'INPP1', 'TSPYL1', 'HPCAL1', 'TRIML2', 'RPL37A', 'DDIT4', 'KMT5A', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'ATP1B1', 'CNIH4', 'CEBPB', 'PHLDA2', 'DEGS1', 'LMNA', 'RBCK1', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'PHKG1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'LETM1', 'PTRH2', 'SLC12A2', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'PMP22', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'PLPP5', 'DKK1', 'EZR', 'RHOF', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCL2', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'PHACTR2', 'HLA-A', 'TMEM205', 'IGFBP4', 'NDUFAF4', 'SNW1', 'DUSP1', 'TP53I3', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'DCBLD2', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'C1orf56', 'PPP1R7', 'RND3', 'LIPH', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'MDK', 'TRAM1', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'TNFRSF12A', 'SLC35F6', 'HNRNPH1', 'TCEAL8', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'EIF1AY', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'BZW1', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'CXCL5', 'MMD', 'CD70', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'PRKCA', 'SPP1', 'NINJ1', 'CD63', 'PAPPA', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'CRIP2', 'ETFB', 'B4GALT5', 'FOXM1', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'COX14', 'TM4SF4', 'HES4', 'GCHFR', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'CNN2', 'F12', 'CRELD2', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'LXN', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'SEMA4B', 'EIF3D', 'KCNMA1', 'LAPTM4A', 'SFR1', 'TFF1', 'EFHD2', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'SLC16A5', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'RSPO3', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'ANKRD40', 'IGFBP6', 'C16orf74', 'DNAJC12', 'S100A16', 'S100A10', 'CXCL3', 'TRMT6', 'PBDC1', 'SLC27A2', 'RPF2', 'PA2G4', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'INSL4', 'CCT4', 'PRDX1', 'SOX4', 'ITGA3', 'CLSPN', 'EMP3', 'YPEL5', 'TMEM54', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'SLC4A7', 'SMIM14', 'TMPO', 'PAQR5', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'C1orf56', 'DKC1', 'HSPE1', 'CTTN', 'TNFRSF12A', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'PAQR5', 'AKR1C1', 'RQCD1', 'LIPH', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'TFF1', 'GAL', 'PA2G4', 'TM4SF1', 'TUBA1A', 'TP53I3', 'PIR', 'TMEM205', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'CD70', 'CDC42', 'MMD', 'GRPEL1', 'MDK', 'NFKBIA', 'DNAJC12', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'DCBLD2', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'RSPO3', 'ALDH7A1', 'HES4', 'SQSTM1', 'TRIML2', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'EPHX1', 'EIF1AY', 'RPS27L', 'TAGLN2', 'EPS8', 'NINJ1', 'EIF3D', 'COL5A2', 'ANKRD40', 'PHLDA1', 'SNRPF', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'CKS2', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SAT1', 'SEMA4B', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'EMP3', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'KCNMA1', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'ADAMTS12', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RBCK1', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'IGFBP6', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'TMEM54', 'VAMP8', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'CXCL3', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'SLC7A5', 'LXN', 'GPRC5A', 'TGFBR2', 'PCSK1N', 'PMP22', 'CKB', 'DDX10', 'ODC1', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'COX17', 'DHRS7', 'CD24', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'INSL4', 'PTGES3', 'BZW1', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'PHLDA2', 'C16orf74', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'FEZ2', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'SCD', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'EMC7', 'LAPTM4A', 'SET', 'CUTC', 'CXCL5', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'TM4SF4', 'NCL', 'PLAUR', 'ETFB', 'RPL27', 'DNAJC22', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'CCL2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'PBDC1', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'SLC16A5', 'EFHD2', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'SLC4A7', 'PAPPA', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'PTPRF', 'CRIP2', 'SSB', 'TYMP', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'UPK1B', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'MKI67', 'ELF3', 'B4GALT4', 'MMP7', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'HPCAL1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'INPP1', 'KRT18', 'TOR1AIP2', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IEA'], ['IPI'], ['IPI'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IC', 'IEA'], ['IPI'], ['IDA', 'IPI', 'NAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'HDA', 'IBA'], ['IPI', 'ISS', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI', 'HDA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IMP'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA'], ['IPI', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IMP', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IC', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI'], ['EXP', 'IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA'], ['IPI'], ['TAS'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'TAS'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IGI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'HDA', 'IEA'], ['HDA', 'IEA'], ['IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'ISS'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'NAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'NAS'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IC'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IBA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['HDA'], ['IPI'], ['IPI', 'ISS'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI'], ['IDA', 'IEA'], ['IPI', 'ISS'], ['IPI'], ['IPI'], ['IPI', 'ISS'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'TAS', 'NAS'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IBA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'TAS'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['ISS'], ['IPI', 'NAS'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'TAS'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI']]</t>
+          <t>[['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'NAS'], ['IPI', 'HDA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'ISS'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'ISS'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI', 'HDA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'TAS'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IC'], ['IDA', 'IPI'], ['IPI', 'TAS'], ['IPI'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IEA'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['ISS', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IEA'], ['IPI', 'ISS', 'IBA', 'IC'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['TAS'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IEA'], ['IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'HDA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['ISS'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['TAS'], ['IDA', 'IPI', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'NAS'], ['IPI', 'HDA', 'IEA'], ['IPI', 'IBA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IGI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IC'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IBA', 'TAS'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'ISS'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'TAS', 'NAS'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['HDA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'TAS'], ['IPI', 'IMP'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IDA'], ['IPI'], ['IPI', 'ISS', 'TAS'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'NAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IBA'], ['IPI', 'IBA', 'NAS'], ['IBA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'ISS'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI'], ['EXP', 'IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'HDA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'HDA', 'TAS'], ['IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IMP', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GO:MF</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GO:0005488</t>
+          <t>GO:0110165</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>cellular anatomical structure</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.04503248185867344</v>
+        <v>0.0184115895617477</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>"The selective, non-covalent, often stoichiometric, interaction of a molecule with one or more specific sites on another molecule." [GOC:ceb, GOC:mah, ISBN:0198506732]</t>
+          <t>"A part of a cellular organism consisting of a material entity with granularity above the level of a protein complex but below that of an anatomical system. Note that cellular organisms exclude viruses." [GOC:kmv]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2388</v>
+        <v>2507</v>
       </c>
       <c r="H21" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I21" t="n">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="J21" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9471544715447154</v>
+        <v>0.9797160243407708</v>
       </c>
       <c r="L21" t="n">
-        <v>0.195142378559464</v>
+        <v>0.1926605504587156</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>['GO:0003674']</t>
+          <t>['GO:0005575']</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>['HSP90AB1', 'PAK1IP1', 'ACTG1', 'RPL35', 'MUC5AC', 'ANXA7', 'GPX1', 'ADM', 'ARL6IP1', 'DNAJC22', 'AXL', 'S100A13', 'PROCR', 'ADAMTS12', 'AIMP1', 'CTSB', 'GLRX', 'HSPD1', 'EIF4A1', 'APOE', 'TM4SF1', 'RABAC1', 'CKS2', 'S100A3', 'FDFT1', 'NUDC', 'PPIB', 'HSPA8', 'RTN4RL2', 'G0S2', 'EIF2S3', 'PMEPA1', 'DKC1', 'TOP2A', 'CDA', 'GAL', 'TMSB4X', 'PCDH9', 'RQCD1', 'SPCS2', 'NFKBIA', 'EMC7', 'DDX21', 'SUCLG1', 'FEZ2', 'UPK1B', 'SCD', 'HSPA2', 'MARCKSL1', 'SERPINE2', 'PSAT1', 'MARCKS', 'CCND3', 'INPP1', 'TSPYL1', 'HPCAL1', 'TRIML2', 'RPL37A', 'NUDT19', 'DDIT4', 'KMT5A', 'TRIB3', 'TDG', 'ALG8', 'KRT8', 'ATP1B1', 'CNIH4', 'CEBPB', 'PHLDA2', 'DEGS1', 'LMNA', 'RBCK1', 'PKM', 'HSPG2', 'CTNNB1', 'EBNA1BP2', 'SQSTM1', 'DHRS7', 'SSB', 'S100A11', 'PGK1', 'INA', 'PHKG1', 'ALDH3A1', 'TGFBI', 'RRS1', 'LGALS1', 'GINS2', 'COTL1', 'CDK6', 'UTP18', 'FABP5', 'TUBB', 'FBXO2', 'RNF121', 'PLEK2', 'LETM1', 'PTRH2', 'SLC12A2', 'SLC16A3', 'ZC3H4', 'TUBA1B', 'TNNT1', 'KRT81', 'GLRX3', 'GLA', 'SDC4', 'FN1', 'RAP2B', 'MGST3', 'PDHA1', 'ANP32A', 'COX7B', 'MGST1', 'GRPEL1', 'CPNE7', 'ID3', 'PKMYT1', 'CDK1', 'PMP22', 'RPL26', 'ANKRD28', 'DDX10', 'PRSS3', 'AKAP12', 'RPL41', 'LGALS3BP', 'UBE2S', 'TOB1', 'PLPP5', 'DKK1', 'EZR', 'RHOF', 'ILF2', 'TOR1AIP2', 'UMPS', 'CD44', 'CCL2', 'CCNB2', 'PSMD14', 'OAS1', 'SLC3A2', 'EMP2', 'TPPP3', 'PSMC2', 'SMAGP', 'RPS27L', 'CTSL', 'NUP37', 'EXOSC9', 'GTPBP4', 'PGD', 'CYB5A', 'TAGLN2', 'KRT18', 'TYMP', 'CUTC', 'PHACTR2', 'HLA-A', 'TMEM205', 'IGFBP4', 'NDUFAF4', 'SNW1', 'DUSP1', 'TP53I3', 'PTPRF', 'NQO1', 'CDCA4', 'AKR1B10', 'GPRC5A', 'PLAU', 'KPNA2', 'PDLIM1', 'LBH', 'ANXA2', 'EIF4EBP1', 'TMEM120B', 'AKR1B1', 'HEXA', 'PCNA', 'RPL34', 'PPA1', 'DCBLD2', 'CAV1', 'FGD6', 'AP1M2', 'ANTXR1', 'NT5E', 'ZFP36L1', 'IGFBP3', 'MTHFD2', 'YWHAE', 'TXN', 'PPP3CA', 'S100A6', 'ALDH1A1', 'APOBEC3C', 'DCAF13', 'ENO1', 'EIF6', 'PCSK1N', 'PLAUR', 'C1orf56', 'PPP1R7', 'RND3', 'LIPH', 'MYC', 'MKI67', 'EPS8', 'MGST2', 'CAV2', 'RPS28', 'ASF1A', 'CDKN1A', 'RNF212', 'IDI1', 'BLVRB', 'MCL1', 'RAD51AP1', 'HSPA5', 'PPP1CB', 'MDK', 'TRAM1', 'FDPS', 'ODC1', 'SLC2A1', 'CCT5', 'ARL1', 'YARS', 'AKR1C2', 'EVA1C', 'TXNRD1', 'CENPA', 'EGR1', 'AP3S1', 'SULT2B1', 'TNFRSF12A', 'SLC35F6', 'HNRNPH1', 'TCEAL8', 'CAMK1', 'GCNT2', 'MDM4', 'AKR1C1', 'RPS17', 'B4GALT4', 'MMP7', 'HMGB2', 'AGR2', 'DOCK5', 'SFRP1', 'EIF1AY', 'SLC7A5', 'LGALS3', 'PARD3', 'ALDH7A1', 'RAN', 'RPL39', 'BZW1', 'COL5A2', 'HMGA1', 'NCL', 'CKB', 'MYL6', 'UBE2C', 'CXCL5', 'MMD', 'GMPS', 'CD70', 'B4GALT1', 'BCL2L1', 'UBE2T', 'FOSL1', 'PRKCA', 'SPP1', 'NINJ1', 'CD63', 'PAPPA', 'S100A4', 'RPS15A', 'PFDN2', 'IGFBP7', 'CRIP2', 'ETFB', 'B4GALT5', 'FOXM1', 'ACTB', 'CKS1B', 'PSMD1', 'KRT80', 'NPM1', 'SAT1', 'COX14', 'TM4SF4', 'HES4', 'GCHFR', 'TIMP1', 'COX17', 'MYL12B', 'MCM3', 'SYNGR2', 'CDKN3', 'CNN2', 'F12', 'CRELD2', 'RBFOX3', 'ERGIC1', 'PHLDA1', 'AMIGO2', 'CAPG', 'MT2A', 'RPL27', 'ATF4', 'LXN', 'IK', 'ANXA5', 'ECH1', 'RAI14', 'KNSTRN', 'MKNK2', 'HELLS', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'PDLIM7', 'HSPE1', 'RPL28', 'SNRPF', 'CTTN', 'KIF3A', 'OPTN', 'SPTSSA', 'CES1', 'PDLIM5', 'SEMA4B', 'MRPS30', 'EIF3D', 'KCNMA1', 'LAPTM4A', 'SFR1', 'TFF1', 'EFHD2', 'TNRC6B', 'AMOTL2', 'GSTO1', 'CST3', 'SFN', 'VAMP8', 'MYL12A', 'ELF3', 'ADI1', 'UCHL1', 'PHGDH', 'TUBA1C', 'ARPC3', 'SLPI', 'MRPL13', 'CDT1', 'FGFR1', 'CAPZA1', 'CHP1', 'NTS', 'CTNNAL1', 'HM13', 'PTTG1', 'RSL1D1', 'TOMM7', 'UQCRB', 'STC2', 'TESC', 'VIM', 'RPS29', 'KRT7', 'EGLN1', 'CBX6', 'EPHX1', 'PSMC4', 'TRA2A', 'TPM1', 'SLC16A5', 'XRCC5', 'BASP1', 'CPLX2', 'PRMT1', 'ANXA3', 'TUBB4B', 'SET', 'RPL31', 'KYNU', 'MAGED2', 'RSPO3', 'HOXB8', 'FGB', 'CD24', 'TSC22D1', 'ANXA1', 'DDX39A', 'PSMA3', 'RAB11FIP1', 'MORC4', 'LDHB', 'ANXA4', 'RIN2', 'KRT19', 'TGFBR2', 'KIF23', 'PTPRS', 'CLU', 'ABCG2', 'RPS18', 'NEU1', 'BIRC5', 'NIP7', 'PTGES3', 'INO80C', 'ANKRD40', 'IGFBP6', 'C16orf74', 'DNAJC12', 'S100A16', 'IRF2BP2', 'S100A10', 'CXCL3', 'TRMT6', 'PBDC1', 'SLC27A2', 'RPF2', 'PA2G4', 'NT5DC3', 'CCT7', 'B2M', 'CCND1', 'DRAM1', 'INSL4', 'CCT4', 'PRDX1', 'SOX4', 'ITGA3', 'CLSPN', 'EMP3', 'YPEL5', 'TMEM54', 'PIR', 'DYNLL1', 'RPS24', 'BTG1', 'HMGB3', 'TM4SF20', 'LITAF', 'HACD3', 'EEF1A1', 'CCDC85B', 'SH3KBP1', 'PHLDA3', 'SLC4A7', 'SMIM14', 'TMPO', 'PAQR5', 'DDB2', 'FSCN1', 'CCNB1', 'JUNB', 'PTP4A1', 'CDC42', 'RIPK2']</t>
+          <t>['ALDH3A1', 'HM13', 'C1orf56', 'DKC1', 'HSPE1', 'CTTN', 'TNFRSF12A', 'CALM2', 'XRCC5', 'MYL12B', 'B2M', 'TRAM1', 'RRS1', 'PKMYT1', 'CHP1', 'IGFBP7', 'PAQR5', 'AKR1C1', 'RQCD1', 'LIPH', 'DDIT4', 'KPNA2', 'RIPK2', 'PRKCA', 'ADI1', 'SPCS2', 'AP3S1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'EXOSC9', 'HSPG2', 'PPP1R7', 'LGALS1', 'SLC16A3', 'TFF1', 'GCNT3', 'GAL', 'PA2G4', 'FKBP11', 'TM4SF1', 'RBFOX3', 'TUBA1A', 'TP53I3', 'PIR', 'TMEM205', 'COX7B', 'PFDN2', 'CNN2', 'MORC4', 'LRRC75A', 'SLC27A2', 'CCT7', 'CDCA4', 'TXN', 'TESC', 'ID3', 'JUNB', 'MKNK2', 'GINS2', 'DDB2', 'SUCLG1', 'CLSPN', 'CD70', 'PLEK2', 'CDC42', 'MMD', 'GRPEL1', 'MDK', 'NFKBIA', 'DNAJC12', 'B4GALT1', 'NEU1', 'HSPA8', 'CEBPB', 'CCT4', 'CPNE7', 'RPS15A', 'DCBLD2', 'UQCRB', 'FGFR1', 'MYC', 'LGALS3', 'EIF2S3', 'CTSB', 'PSMA3', 'ANXA2', 'LMNA', 'RSPO3', 'ALDH7A1', 'MUC12', 'HES4', 'SQSTM1', 'TRIML2', 'PHLDA3', 'ARL6IP1', 'ZC3H4', 'TNRC6B', 'UMPS', 'UTP18', 'TDG', 'SFN', 'G0S2', 'NANS', 'EPHX1', 'EIF1AY', 'RPS27L', 'TAGLN2', 'EPS8', 'NINJ1', 'EIF3D', 'COL5A2', 'PHLDA1', 'SNRPF', 'RPL35', 'SERPINE2', 'DKK1', 'NTS', 'GLRX', 'CENPA', 'PDHA1', 'AKAP12', 'RPS18', 'APOBEC3C', 'ANXA1', 'SAT1', 'SEMA4B', 'SDC4', 'EMP2', 'FOXM1', 'INO80C', 'CRELD2', 'EMP3', 'TGFBI', 'ARL1', 'EIF6', 'B4GALT5', 'SFRP1', 'SLC35F6', 'HERC4', 'KCNMA1', 'RND3', 'SYNGR2', 'KRT80', 'TM4SF20', 'RPL28', 'ADAMTS12', 'CFD', 'ANP32A', 'PDLIM5', 'FGB', 'RABAC1', 'AP1M2', 'RPL39', 'RBCK1', 'F12', 'FABP5', 'YARS', 'EBNA1BP2', 'IGFBP6', 'CDA', 'PHKG1', 'RPL41', 'ACTG1', 'PARD3', 'TMEM54', 'NT5DC3', 'VAMP8', 'NEAT1', 'CDKN3', 'CTSL', 'MCM3', 'MARCKSL1', 'S100A6', 'SULT2B1', 'CXCL3', 'BASP1', 'CKS1B', 'TMEM92', 'GCHFR', 'KMT5A', 'NPM1', 'OAS1', 'CDKN1A', 'MGST3', 'CDK6', 'DUSP1', 'CCNB1', 'RNF212', 'GTPBP4', 'PHGDH', 'ANTXR1', 'S100A16', 'MRPS30', 'HOXB8', 'SMAGP', 'TCEAL8', 'KIF23', 'TMEM120B', 'CLU', 'ITGA3', 'RTN4RL2', 'HSPD1', 'ZFAS1', 'IFI27L2', 'SLC7A5', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'TGFBR2', 'PCSK1N', 'PMP22', 'CKB', 'DDX10', 'ODC1', 'MUC5AC', 'CAV1', 'NQO1', 'PRMT1', 'RSL1D1', 'NUDT19', 'COX17', 'DHRS7', 'SMIM6', 'CD24', 'PCDH9', 'PDLIM7', 'RAB11FIP1', 'IK', 'TPM1', 'GOLIM4', 'MT2A', 'CCND1', 'UBE2T', 'ANXA7', 'RPS24', 'UCHL1', 'LITAF', 'S100A4', 'TOMM7', 'EEF1A1', 'TRA2A', 'VIM', 'INSL4', 'PTGES3', 'BZW1', 'PAK1IP1', 'TMSB4X', 'FDFT1', 'PHLDA2', 'SFR1', 'DDX21', 'TIMP1', 'TXNRD1', 'RIN2', 'HSPA5', 'PKM', 'S100A13', 'SPTSSA', 'UBE2C', 'FEZ2', 'ILF2', 'CBX6', 'BTG1', 'PRDX1', 'DYNLL1', 'ATP1B1', 'MRPL13', 'CCDC85B', 'KRT81', 'HMGB2', 'MYL6', 'SLPI', 'PPP1CB', 'TRIB3', 'PTPRS', 'EGR1', 'MGST2', 'PPA1', 'CES1', 'YPEL5', 'FBXO2', 'CAMK1', 'EZR', 'PTTG1', 'DRAM1', 'ANKRD28', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'AMOTL2', 'S100A10', 'HLA-A', 'IDI1', 'KYNU', 'ADM', 'COX14', 'FDPS', 'BCL2L1', 'RPL34', 'MCL1', 'AKR1C2', 'SCD', 'GMPS', 'GPX1', 'PROCR', 'SLC12A2', 'CD63', 'CAPG', 'SMIM14', 'SLC35F3', 'EMC7', 'LAPTM4A', 'RPS17', 'SET', 'CUTC', 'C19orf33', 'CXCL5', 'GLRX3', 'ANXA3', 'CDK1', 'DOCK5', 'UBE2S', 'TPPP3', 'SH3KBP1', 'RPS28', 'AIMP1', 'KNSTRN', 'PSMC2', 'COTL1', 'TSPYL1', 'RPF2', 'AKR1B1', 'TM4SF4', 'OCIAD2', 'NCL', 'PLAUR', 'ETFB', 'GPX2', 'RPL27', 'DNAJC22', 'TUBB', 'CCT5', 'RAN', 'CAV2', 'PHACTR2', 'FOSL1', 'MAGED2', 'CDT1', 'CCL2', 'AXL', 'LGALS3BP', 'PCNA', 'FSCN1', 'OPTN', 'INA', 'AMIGO2', 'EIF4A1', 'FGD6', 'SLC2A1', 'HSP90AA1', 'PGK1', 'TUBB4B', 'NIP7', 'DCAF13', 'GCNT2', 'PLAU', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'PSMD1', 'NT5E', 'BLVRB', 'TRMT6', 'MARCKS', 'RAD51AP1', 'MDM4', 'AKR1B10', 'TUBA1C', 'GSTO1', 'CTNNB1', 'FN1', 'CCNB2', 'SLC16A5', 'EFHD2', 'ALDH1A1', 'PLPP5', 'IGFBP4', 'MGST1', 'PDLIM1', 'SPP1', 'HNRNPH1', 'PTRH2', 'SLC4A7', 'PAPPA', 'ABCG2', 'RPL31', 'DDX39A', 'HELLS', 'PTPRF', 'CRIP2', 'SSB', 'PGD', 'TYMP', 'KRT7', 'BIRC5', 'TOP2A', 'CAPZA1', 'PMEPA1', 'UPK1B', 'EIF4EBP1', 'CNIH4', 'RAP2B', 'EVA1C', 'STC2', 'PSAT1', 'PPIB', 'AGR2', 'SLC3A2', 'GLA', 'ASF1A', 'S100A3', 'LDHB', 'MTHFD2', 'ARPC3', 'RNF121', 'MKI67', 'NNMT', 'ELF3', 'B4GALT4', 'MMP7', 'ATF4', 'CST3', 'APOE', 'PTP4A1', 'NDUFAF4', 'LBH', 'HMGA1', 'HPCAL1', 'RPL26', 'DEGS1', 'PRSS3', 'CCND3', 'PSMC4', 'NUDC', 'ACTB', 'RHOF', 'RAI14', 'HACD3', 'EGLN1', 'CTNNAL1', 'LDHA', 'HEXA', 'ANXA5', 'ERGIC1', 'YWHAE', 'RPS29', 'SNW1', 'PPP3CA', 'ALG8', 'LETM1', 'TOB1', 'HMGB3', 'IGFBP3', 'INPP1', 'KRT18', 'TOR1AIP2', 'MUC3A', 'KIF3A', 'SOX4', 'ECH1', 'TMPO', 'MYL12A', 'S100A11', 'TNNT1', 'TUBA1B', 'TSC22D1', 'ZFP36L1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IEA'], ['ISS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISS', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'HDA', 'ISS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IEA'], ['IPI', 'TAS', 'IC', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IEA'], ['IEA'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IMP', 'IBA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IC', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'TAS'], ['IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA'], ['EXP', 'IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['TAS'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'IMP'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['HDA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IMP', 'HDA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'IEA'], ['IEA'], ['EXP', 'IDA', 'IPI', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'TAS', 'IEA'], ['EXP', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'NAS'], ['IDA', 'IPI', 'NAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IC', 'IEA'], ['IPI', 'IEA'], ['IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HDA', 'TAS'], ['IPI', 'IMP', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'ISS'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI', 'HDA', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA'], ['IPI'], ['IPI'], ['IDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'TAS'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA'], ['ISS', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['HDA', 'ISS'], ['IPI', 'NAS'], ['IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA']]</t>
+          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HTP', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.525139541036839e-12</v>
+        <v>7.604002055465932e-13</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -2844,22 +2844,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H2" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2033898305084746</v>
+        <v>0.2067669172932331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4119850187265918</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['RBM8A', 'NUCKS1', 'TSFM', 'DKC1', 'TOP2A', 'TMSB4X', 'DDX21', 'NOC3L', 'PKM', 'LGALS1', 'EIF3E', 'UTP18', 'PSMC1', 'SMC1A', 'TUBA1B', 'RPS27', 'SLC3A2', 'UNC50', 'NOL7', 'KRT18', 'HLA-A', 'NOL11', 'KPNA2', 'RPL21', 'YWHAE', 'DCAF13', 'ENO1', 'HMGB2', 'EIF1AY', 'LGALS3', 'RPL39', 'UBC', 'NPM1', 'AHNAK', 'SNRPF', 'TNRC6B', 'SRP54', 'SLPI', 'ZNF622', 'CBX6', 'XRCC5', 'TUBB4B', 'RPL31', 'RPS18', 'LACTB2', 'PA2G4', 'CCT3', 'CCT4', 'HMGB3', 'EEF1A1', 'RPS12', 'FSCN1', 'HSP90AB1', 'HSPA1A', 'HSPD1', 'HSPA8', 'EIF2S3', 'RAD21', 'SUCLG1', 'RPL37A', 'CSRP1', 'PUS1', 'EBNA1BP2', 'SSB', 'RRS1', 'SLC16A3', 'NOLC1', 'GLRX3', 'ZFP36', 'ANP32A', 'DDX10', 'RPL41', 'OAS1', 'NAA15', 'GTPBP4', 'NQO1', 'ANXA2', 'ZFP36L1', 'TXN', 'APOBEC3C', 'MKI67', 'RPL38', 'RPS28', 'YARS', 'CCT5', 'SLBP', 'HNRNPH1', 'RAN', 'NCL', 'HMGA1', 'S100A4', 'HSP90B1', 'EIF4A3', 'HSP90AA1', 'HSPE1', 'RPL28', 'SPATS2', 'EIF3D', 'UTP6', 'RPS29', 'VIM', 'PRMT1', 'DDX39A', 'ISG20', 'S100A16', 'ZFP36L2', 'PRDX1', 'RPS24']</t>
+          <t>['DKC1', 'XRCC5', 'PPP1R7', 'UNC50', 'SUCLG1', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'TNRC6B', 'UTP18', 'EIF1AY', 'EIF3D', 'ANP32A', 'RPL39', 'YARS', 'RPL41', 'NPM1', 'RBM8A', 'S100A16', 'HSPD1', 'DDX10', 'NQO1', 'PRMT1', 'EIF4A3', 'EEF1A1', 'VIM', 'TMSB4X', 'DDX21', 'PKM', 'CBX6', 'CCT3', 'CCT5', 'RAN', 'UTP6', 'FSCN1', 'PSMC1', 'DCAF13', 'NOLC1', 'SLBP', 'ZNF622', 'ZFP36L2', 'DDX39A', 'SSB', 'TOP2A', 'RPS27', 'PUS1', 'YWHAE', 'RPS29', 'LACTB2', 'ZFP36L1', 'HSPE1', 'RRS1', 'KPNA2', 'NOC3L', 'LGALS1', 'SLC16A3', 'PA2G4', 'TXN', 'ZFP36', 'NAA15', 'HSPA8', 'SPATS2', 'SNRPF', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'RPL28', 'EBNA1BP2', 'RPS12', 'ISG20', 'NEAT1', 'OAS1', 'GTPBP4', 'RPL21', 'NOL11', 'RPL38', 'RPS24', 'SMC1A', 'S100A4', 'PRDX1', 'HMGB2', 'SLPI', 'EIF3E', 'NOL7', 'ENO1', 'HLA-A', 'UBC', 'GLRX3', 'TSFM', 'RPS28', 'NCL', 'HSP90AA1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'HNRNPH1', 'RPL31', 'NUCKS1', 'SLC3A2', 'MKI67', 'HMGA1', 'RAD21', 'HSPA1A', 'HMGB3', 'KRT18', 'TUBA1B', 'RPL37A']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[['HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IPI', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA', 'IBA'], ['IDA', 'HDA'], ['ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['HDA'], ['IEA'], ['IDA', 'HDA'], ['IDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA']]</t>
+          <t>[['IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IEA'], ['ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IEA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA'], ['IDA', 'HDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['IPI'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7.061987813430453e-12</v>
+        <v>5.067865201541748e-11</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -2910,22 +2910,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="H3" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J3" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5141242937853108</v>
+        <v>0.5150375939849624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2837837837837838</v>
+        <v>0.2807377049180328</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['ACTG1', 'GPX1', 'RBM8A', 'GLRX', 'GSN', 'AKR1C3', 'S100A3', 'TMSB4X', 'FBXO5', 'MAP1B', 'DDX21', 'MCM7', 'HSPA2', 'CCND3', 'DDIT4', 'TRIB3', 'MZT1', 'PKM', 'SQSTM1', 'ARHGAP11A', 'PGK1', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'NANS', 'SMC1A', 'PRDX4', 'CDCA3', 'TPX2', 'GAMT', 'RAP2B', 'PKMYT1', 'RRM2', 'EIF3M', 'AKAP12', 'UBE2S', 'TK1', 'NRDC', 'RPS27', 'CCNB2', 'UBB', 'JADE1', 'KLF6', 'PSMC2', 'SGOL1', 'CYB5A', 'PGD', 'KRT18', 'TAGLN2', 'TP53I3', 'AKR1B10', 'KPNA2', 'RMI2', 'CACYBP', 'RPL21', 'YWHAE', 'S100A6', 'ALDH1A1', 'DCAF13', 'DNAJC3', 'ENO1', 'TUBA4A', 'BLVRB', 'CALB2', 'ODC1', 'AKR1C2', 'TXNRD1', 'ORC5', 'NFKBIE', 'SULT2B1', 'SLC35F6', 'SFRP1', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'SAT1', 'AHNAK', 'MYL12B', 'PSMD7', 'MT2A', 'RAI14', 'HMGCS1', 'PDLIM7', 'MGLL', 'SNRPF', 'CTTN', 'CES1', 'PDLIM5', 'TNRC6B', 'GSTO1', 'VAMP8', 'SRP54', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'KRT7', 'ZNF622', 'PSMC4', 'NDUFA12', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOMER3', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'KIF23', 'PTPRS', 'RPS18', 'CDKN2D', 'PPID', 'NDRG1', 'CAPN2', 'CCT7', 'CCT3', 'CCND1', 'HILPDA', 'CCT4', 'DYNLL1', 'TALDO1', 'EEF1A1', 'MAP1LC3B', 'RPS12', 'FSCN1', 'CCNB1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ARL6IP1', 'S100A13', 'CDCA5', 'HSPA1A', 'HSPD1', 'HSPA8', 'EIF2S3', 'RAD21', 'SERPINE2', 'INPP1', 'FOS', 'AIMP2', 'RPL37A', 'NUDT19', 'HMOX1', 'KRT8', 'GPX2', 'LMNA', 'CTNNB1', 'SSB', 'CTSH', 'ALDH3A1', 'CCT2', 'CDC20', 'TUBB', 'CENPF', 'KRT81', 'GLRX3', 'ZFP36', 'CDK1', 'AURKA', 'RPL41', 'PPP1R14A', 'CD44', 'PSMD14', 'OAS1', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'ARHGAP29', 'NQO1', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'PRPS2', 'DNMBP', 'RND3', 'RPL38', 'RPS28', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'SLC7A5', 'RAN', 'HMGA1', 'GIGYF1', 'LMO7', 'BCL2L1', 'CDC42EP1', 'S100A4', 'UBR4', 'NAMPT', 'CCT8', 'HSP90B1', 'AP1S2', 'ATF4', 'EIF4A3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'RPL28', 'SPATS2', 'EIF3D', 'RAD51C', 'PYCARD', 'SFN', 'MYL12A', 'ELF3', 'STMN1', 'PHGDH', 'UCHL1', 'ADA', 'TRAPPC6A', 'CTNNAL1', 'PTTG1', 'RAP1GAP', 'TESC', 'AHNAK2', 'RPS29', 'VIM', 'DOK4', 'HMMR', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'S100A16', 'ACAT2', 'SLC27A2', 'B2M', 'GCLC', 'ATXN10', 'PRDX1', 'NNMT', 'PLK2', 'PIR', 'RPS24', 'CDC42']</t>
+          <t>['ALDH3A1', 'BIRC3', 'NFKBIE', 'CALM2', 'XRCC5', 'MYL12B', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'TKT', 'TUBA1A', 'TP53I3', 'LMO7', 'AIMP2', 'CCT7', 'ATXN10', 'NDRG1', 'CDC42', 'CCT4', 'HMMR', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'LMNA', 'ARL6IP1', 'TNRC6B', 'SFN', 'EIF3D', 'PLK2', 'GLRX', 'AKR1C3', 'CTNNBL1', 'AKAP12', 'ANXA1', 'TUBA4A', 'SFRP1', 'RND3', 'HMOX1', 'JADE1', 'MZT1', 'FOS', 'RPL39', 'NRDC', 'YARS', 'RPL41', 'MAP1LC3B', 'S100A6', 'CAPN2', 'GIGYF1', 'NPM1', 'RBM8A', 'MGLL', 'PHGDH', 'HILPDA', 'S100A16', 'UBR4', 'HSPD1', 'SMOX', 'PPP1R14A', 'DOK4', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'SH3BGRL3', 'PDLIM7', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'EEF1A1', 'VIM', 'TMSB4X', 'DDX21', 'EIF3M', 'PKM', 'S100A13', 'UBE2C', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'RAB10', 'KYNU', 'AKR1C2', 'GSN', 'HOMER3', 'CCT3', 'NAMPT', 'AURKB', 'GPX2', 'TUBB', 'CCT5', 'RAN', 'PPP1R15A', 'FSCN1', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'CTSH', 'PRPS2', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'TRAPPC6A', 'ALDH1A1', 'ZNF622', 'PTRH2', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'EIF4EBP1', 'RAP2B', 'RPS27', 'PPID', 'S100A3', 'LDHB', 'CDC25B', 'RAD51C', 'ARHGAP29', 'ACTB', 'RAI14', 'CTNNAL1', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'SGOL1', 'MAP1B', 'PLK1', 'CDC42EP1', 'ZFP36L1', 'DNMBP', 'CTTN', 'B2M', 'ACAT2', 'PKMYT1', 'KPNA2', 'RIPK2', 'LGALS1', 'MNS1', 'PIR', 'SLC27A2', 'TXN', 'TESC', 'AURKA', 'ZFP36', 'NAA15', 'CDKN2D', 'HSPA8', 'PSMA3', 'RAP1GAP', 'SPATS2', 'RMI2', 'SQSTM1', 'AHNAK2', 'ANKRD1', 'NANS', 'TAGLN2', 'SNRPF', 'RRM2', 'SERPINE2', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'RPS18', 'SRP54', 'SAT1', 'NUF2', 'INO80C', 'SLC35F6', 'DNAJC3', 'RPL28', 'PDLIM5', 'GCLC', 'RHOD', 'ACTG1', 'RPS12', 'VAMP8', 'CDCA3', 'SULT2B1', 'OAS1', 'CCNB1', 'GTPBP4', 'RPL21', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'SLC7A5', 'ODC1', 'PDXK', 'RPL38', 'MT2A', 'HMGCS1', 'RPS24', 'SMC1A', 'S100A4', 'CCT8', 'RIN2', 'TXNRD1', 'HSPA5', 'DYNLL1', 'PRDX1', 'KRT81', 'MYL6', 'PSMA4', 'MSH6', 'EIF3E', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'SET', 'GLRX3', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'ADA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'CYB5A', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'GSTO1', 'CCNB2', 'CENPF', 'HNRNPH1', 'RPL31', 'BIRC5', 'TALDO1', 'CACYBP', 'NNMT', 'ELF3', 'ATF4', 'HMGA1', 'RAD21', 'CCND3', 'PSMC4', 'HSPA1A', 'TK1', 'PPP3CA', 'CDC20', 'INPP1', 'KLF6', 'KRT18', 'ECH1', 'MYL12A', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA'], ['IDA'], ['IMP', 'IBA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['ISS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'ISS', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA'], ['IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'TAS', 'NAS'], ['TAS', 'IEA']]</t>
+          <t>[['IDA', 'ISS', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IBA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['TAS', 'NAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IBA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['ISS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IMP', 'IBA'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS'], ['IDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.381222434930374e-10</v>
+        <v>3.015270831406966e-10</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -2979,16 +2979,16 @@
         <v>485</v>
       </c>
       <c r="H4" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I4" t="n">
         <v>161</v>
       </c>
       <c r="J4" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3032015065913371</v>
+        <v>0.3026315789473684</v>
       </c>
       <c r="L4" t="n">
         <v>0.3319587628865979</v>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'RARRES1', 'CD55', 'UBB', 'SLC3A2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'ITGB5', 'ALDH2', 'CACYBP', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DNAJC3', 'ENO1', 'PPP1R7', 'TUBA4A', 'BLVRB', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'RAB3B', 'SFRP1', 'LGALS3', 'MYL6', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'ACAT1', 'SERPINB1', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'KRT7', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCT4', 'ITGA3', 'TALDO1', 'EEF1A1', 'FSCN1', 'HSP90AB1', 'SH3BGRL3', 'ITGB1', 'AXL', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'HSPA8', 'EIF2S3', 'UPK1B', 'PRSS23', 'RPL37A', 'CSRP1', 'KRT8', 'CTNNB1', 'CTSH', 'CCT2', 'TUBB', 'SLC12A2', 'ATP1B3', 'FN1', 'CDK1', 'CD44', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'TKT', 'TXN', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'CCT5', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CD70', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'NAMPT', 'CCT8', 'HSP90B1', 'F12', 'CAPG', 'GCNT3', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'CHP1', 'RPS29', 'VIM', 'PSMA3', 'LDHB', 'KRT19', 'CLU', 'S100A16', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'PRDX1', 'CDC42']</t>
+          <t>['MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'NDRG1', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SFN', 'GLRX', 'AKR1C3', 'ANXA1', 'TUBA4A', 'SFRP1', 'F12', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'S100A16', 'ITGA3', 'HSPD1', 'GPRC5A', 'SH3BGRL3', 'GPX3', 'EEF1A1', 'VIM', 'TIMP1', 'PKM', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'SLC12A2', 'CAPG', 'GSN', 'CCT3', 'NAMPT', 'LGMN', 'TUBB', 'CCT5', 'RAN', 'NPC2', 'FSCN1', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'ALDH2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'PRSS23', 'HSPE1', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'ACAT1', 'LGALS1', 'PA2G4', 'SLC27A2', 'TXN', 'CD70', 'CD9', 'ATP1B3', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'CLU', 'SLC7A5', 'MUC5AC', 'PDXK', 'S100A4', 'SLC26A2', 'CCT8', 'TXNRD1', 'CD55', 'HSPA5', 'PRDX1', 'ATP1B1', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'HLA-A', 'UBB', 'UBC', 'CD63', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'GSTO1', 'RPL31', 'UPK1B', 'TALDO1', 'SLC3A2', 'CACYBP', 'ITGB1', 'HSPA1A', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.896812141313427e-10</v>
+        <v>3.670445989762018e-10</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -3045,16 +3045,16 @@
         <v>490</v>
       </c>
       <c r="H5" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I5" t="n">
         <v>162</v>
       </c>
       <c r="J5" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3050847457627119</v>
+        <v>0.3045112781954887</v>
       </c>
       <c r="L5" t="n">
         <v>0.3306122448979592</v>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'RARRES1', 'CD55', 'UBB', 'SLC3A2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'ITGB5', 'ALDH2', 'CACYBP', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DNAJC3', 'ENO1', 'PPP1R7', 'TUBA4A', 'BLVRB', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'RAB3B', 'SFRP1', 'LGALS3', 'MYL6', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'ACAT1', 'SERPINB1', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'KRT7', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCT4', 'ITGA3', 'TALDO1', 'EEF1A1', 'FSCN1', 'HSP90AB1', 'SH3BGRL3', 'ITGB1', 'AXL', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'HSPA8', 'EIF2S3', 'UPK1B', 'PRSS23', 'SERPINE2', 'RPL37A', 'CSRP1', 'KRT8', 'CTNNB1', 'CTSH', 'CCT2', 'TUBB', 'SLC12A2', 'ATP1B3', 'FN1', 'CDK1', 'CD44', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'TKT', 'TXN', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'CCT5', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CD70', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'NAMPT', 'CCT8', 'HSP90B1', 'F12', 'CAPG', 'GCNT3', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'CHP1', 'RPS29', 'VIM', 'PSMA3', 'LDHB', 'KRT19', 'CLU', 'S100A16', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'PRDX1', 'CDC42']</t>
+          <t>['MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'NDRG1', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SFN', 'GLRX', 'AKR1C3', 'ANXA1', 'TUBA4A', 'SFRP1', 'F12', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'S100A16', 'ITGA3', 'HSPD1', 'GPRC5A', 'SH3BGRL3', 'GPX3', 'EEF1A1', 'VIM', 'TIMP1', 'PKM', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'SLC12A2', 'CAPG', 'GSN', 'CCT3', 'NAMPT', 'LGMN', 'TUBB', 'CCT5', 'RAN', 'NPC2', 'FSCN1', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'ALDH2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'PRSS23', 'HSPE1', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'ACAT1', 'LGALS1', 'PA2G4', 'SLC27A2', 'TXN', 'CD70', 'CD9', 'ATP1B3', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'SERPINE2', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'CLU', 'SLC7A5', 'MUC5AC', 'PDXK', 'S100A4', 'SLC26A2', 'CCT8', 'TXNRD1', 'CD55', 'HSPA5', 'PRDX1', 'ATP1B1', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'HLA-A', 'UBB', 'UBC', 'CD63', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'GSTO1', 'RPL31', 'UPK1B', 'TALDO1', 'SLC3A2', 'CACYBP', 'ITGB1', 'HSPA1A', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3088,39 +3088,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GO:1903561</t>
+          <t>GO:0065010</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>extracellular vesicle</t>
+          <t>extracellular membrane-bounded organelle</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.896812141313427e-10</v>
+        <v>3.670445989762018e-10</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
+          <t>"Organized structure of distinctive morphology and function, bounded by a lipid bilayer membrane and occurring outside the cell." [GOC:isa_complete]</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>490</v>
       </c>
       <c r="H6" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I6" t="n">
         <v>162</v>
       </c>
       <c r="J6" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3050847457627119</v>
+        <v>0.3045112781954887</v>
       </c>
       <c r="L6" t="n">
         <v>0.3306122448979592</v>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>['GO:0031982', 'GO:0065010']</t>
+          <t>['GO:0043227', 'GO:0043230']</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'RARRES1', 'CD55', 'UBB', 'SLC3A2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'ITGB5', 'ALDH2', 'CACYBP', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DNAJC3', 'ENO1', 'PPP1R7', 'TUBA4A', 'BLVRB', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'RAB3B', 'SFRP1', 'LGALS3', 'MYL6', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'ACAT1', 'SERPINB1', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'KRT7', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCT4', 'ITGA3', 'TALDO1', 'EEF1A1', 'FSCN1', 'HSP90AB1', 'SH3BGRL3', 'ITGB1', 'AXL', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'HSPA8', 'EIF2S3', 'UPK1B', 'PRSS23', 'SERPINE2', 'RPL37A', 'CSRP1', 'KRT8', 'CTNNB1', 'CTSH', 'CCT2', 'TUBB', 'SLC12A2', 'ATP1B3', 'FN1', 'CDK1', 'CD44', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'TKT', 'TXN', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'CCT5', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CD70', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'NAMPT', 'CCT8', 'HSP90B1', 'F12', 'CAPG', 'GCNT3', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'CHP1', 'RPS29', 'VIM', 'PSMA3', 'LDHB', 'KRT19', 'CLU', 'S100A16', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'PRDX1', 'CDC42']</t>
+          <t>['MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'NDRG1', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SFN', 'GLRX', 'AKR1C3', 'ANXA1', 'TUBA4A', 'SFRP1', 'F12', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'S100A16', 'ITGA3', 'HSPD1', 'GPRC5A', 'SH3BGRL3', 'GPX3', 'EEF1A1', 'VIM', 'TIMP1', 'PKM', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'SLC12A2', 'CAPG', 'GSN', 'CCT3', 'NAMPT', 'LGMN', 'TUBB', 'CCT5', 'RAN', 'NPC2', 'FSCN1', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'ALDH2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'PRSS23', 'HSPE1', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'ACAT1', 'LGALS1', 'PA2G4', 'SLC27A2', 'TXN', 'CD70', 'CD9', 'ATP1B3', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'SERPINE2', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'CLU', 'SLC7A5', 'MUC5AC', 'PDXK', 'S100A4', 'SLC26A2', 'CCT8', 'TXNRD1', 'CD55', 'HSPA5', 'PRDX1', 'ATP1B1', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'HLA-A', 'UBB', 'UBC', 'CD63', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'GSTO1', 'RPL31', 'UPK1B', 'TALDO1', 'SLC3A2', 'CACYBP', 'ITGB1', 'HSPA1A', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3154,39 +3154,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GO:0065010</t>
+          <t>GO:1903561</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>extracellular membrane-bounded organelle</t>
+          <t>extracellular vesicle</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.896812141313427e-10</v>
+        <v>3.670445989762018e-10</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, bounded by a lipid bilayer membrane and occurring outside the cell." [GOC:isa_complete]</t>
+          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>490</v>
       </c>
       <c r="H7" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I7" t="n">
         <v>162</v>
       </c>
       <c r="J7" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3050847457627119</v>
+        <v>0.3045112781954887</v>
       </c>
       <c r="L7" t="n">
         <v>0.3306122448979592</v>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>['GO:0043227', 'GO:0043230']</t>
+          <t>['GO:0031982', 'GO:0065010']</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'RARRES1', 'CD55', 'UBB', 'SLC3A2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'ITGB5', 'ALDH2', 'CACYBP', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DNAJC3', 'ENO1', 'PPP1R7', 'TUBA4A', 'BLVRB', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'RAB3B', 'SFRP1', 'LGALS3', 'MYL6', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'ACAT1', 'SERPINB1', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'KRT7', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCT4', 'ITGA3', 'TALDO1', 'EEF1A1', 'FSCN1', 'HSP90AB1', 'SH3BGRL3', 'ITGB1', 'AXL', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'HSPA8', 'EIF2S3', 'UPK1B', 'PRSS23', 'SERPINE2', 'RPL37A', 'CSRP1', 'KRT8', 'CTNNB1', 'CTSH', 'CCT2', 'TUBB', 'SLC12A2', 'ATP1B3', 'FN1', 'CDK1', 'CD44', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'TKT', 'TXN', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'CCT5', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CD70', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'NAMPT', 'CCT8', 'HSP90B1', 'F12', 'CAPG', 'GCNT3', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'CHP1', 'RPS29', 'VIM', 'PSMA3', 'LDHB', 'KRT19', 'CLU', 'S100A16', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'PRDX1', 'CDC42']</t>
+          <t>['MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'NDRG1', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'ANXA2', 'SFN', 'GLRX', 'AKR1C3', 'ANXA1', 'TUBA4A', 'SFRP1', 'F12', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'S100A16', 'ITGA3', 'HSPD1', 'GPRC5A', 'SH3BGRL3', 'GPX3', 'EEF1A1', 'VIM', 'TIMP1', 'PKM', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'SLC12A2', 'CAPG', 'GSN', 'CCT3', 'NAMPT', 'LGMN', 'TUBB', 'CCT5', 'RAN', 'NPC2', 'FSCN1', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'ALDH2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'PRSS23', 'HSPE1', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'ACAT1', 'LGALS1', 'PA2G4', 'SLC27A2', 'TXN', 'CD70', 'CD9', 'ATP1B3', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'SERPINE2', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'CLU', 'SLC7A5', 'MUC5AC', 'PDXK', 'S100A4', 'SLC26A2', 'CCT8', 'TXNRD1', 'CD55', 'HSPA5', 'PRDX1', 'ATP1B1', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'HLA-A', 'UBB', 'UBC', 'CD63', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'GSTO1', 'RPL31', 'UPK1B', 'TALDO1', 'SLC3A2', 'CACYBP', 'ITGB1', 'HSPA1A', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.082800422067861e-08</v>
+        <v>3.892604050353685e-08</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -3240,22 +3240,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1931</v>
+        <v>1942</v>
       </c>
       <c r="H8" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I8" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J8" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K8" t="n">
-        <v>0.839924670433145</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2309684101501812</v>
+        <v>0.2306900102986612</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'TMSB10', 'GPX1', 'RBM8A', 'NUCKS1', 'GLRX', 'GSN', 'AKR1C3', 'TSFM', 'CA8', 'CYB5B', 'S100A3', 'DKC1', 'TOP2A', 'GAL', 'TMSB4X', 'FBXO5', 'EMC7', 'MAP1B', 'DDX21', 'NOC3L', 'EREG', 'MARCKSL1', 'MCM7', 'HSPA2', 'CCND3', 'ID1', 'DDIT4', 'TRIB3', 'MZT1', 'CNIH4', 'PHLDA2', 'PKM', 'SQSTM1', 'DHRS7', 'S100A11', 'ARHGAP11A', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'DHRS3', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'NANS', 'SMC1A', 'PRDX4', 'CDCA3', 'SERPINE1', 'TUBA1B', 'TPX2', 'GAMT', 'RAP2B', 'ID3', 'PKMYT1', 'RRM2', 'NDUFA9', 'EIF3M', 'CYP1B1', 'PRSS3', 'AKAP12', 'INSIG1', 'UBE2S', 'TOB1', 'GOLIM4', 'TK1', 'NRDC', 'TOR1AIP2', 'CD55', 'RPS27', 'NUPR1', 'CCNB2', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'KANK1', 'UNC50', 'PSMC2', 'SGOL1', 'CTSL', 'CYB5A', 'PGD', 'NOL7', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'IGFBP4', 'DUSP1', 'TP53I3', 'ITGB5', 'AKR1B10', 'ALDH2', 'KPNA2', 'RMI2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'RPL21', 'YWHAE', 'CDC123', 'LGMN', 'S100A6', 'ALDH1A1', 'DCAF13', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'CAV2', 'BLVRB', 'TRAM1', 'CALB2', 'ODC1', 'ZFAS1', 'AKR1C2', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SULT2B1', 'LRRC75A', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'BIRC3', 'EIF1AY', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'MMD', 'B4GALT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'SAT1', 'AHNAK', 'TIMP1', 'MYL12B', 'PSMD7', 'MT2A', 'LXN', 'ACAT1', 'NPTX1', 'SERPINB1', 'RAI14', 'PIF1', 'HMGCS1', 'PDLIM7', 'MGLL', 'SNRPF', 'CTTN', 'CES1', 'PDLIM5', 'UQCRQ', 'LAPTM4A', 'TNRC6B', 'GSTO1', 'VAMP8', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'ZNF622', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOMER3', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'ANXA4', 'KIF23', 'PTPRS', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'NDRG1', 'IRF2BP2', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'ITGA3', 'REEP5', 'NDUFC2', 'PDHB', 'DYNLL1', 'LITAF', 'HMGB3', 'BTG1', 'TALDO1', 'EEF1A1', 'HACD3', 'MAP1LC3B', 'RPS12', 'SMIM14', 'TMPO', 'FSCN1', 'CCNB1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ADM', 'ITGB1', 'ARL6IP1', 'UCP2', 'S100A13', 'CDCA5', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'TSPAN14', 'LOXL2', 'HSPA8', 'EIF2S3', 'PMEPA1', 'RAD21', 'CD68', 'SUCLG1', 'PRSS23', 'SERPINE2', 'INPP1', 'GADD45B', 'FOS', 'AIMP2', 'RPL37A', 'CSRP1', 'NUDT19', 'HMOX1', 'FKBP11', 'ALG8', 'KRT8', 'CEBPB', 'GPX2', 'LMNA', 'CTNNB1', 'PUS1', 'SSB', 'INA', 'CTSH', 'REEP4', 'ALDH3A1', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'TUBB', 'CENPF', 'INHBB', 'SLC12A2', 'TEAD4', 'NOLC1', 'ATP1B3', 'KRT81', 'GLRX3', 'FN1', 'DUSP5', 'ZFP36', 'ANP32A', 'COX7B', 'CDK1', 'FEN1', 'AURKA', 'RPL41', 'UQCR11', 'PPP1R14A', 'CD44', 'PSMD14', 'GAL3ST1', 'OAS1', 'LY6K', 'REXO2', 'TPPP3', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'ARHGAP29', 'PHACTR2', 'CRIP1', 'UQCRC2', 'PTPRF', 'NQO1', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'ANTXR1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'APOBEC3C', 'PLAUR', 'PRPS2', 'DNMBP', 'RND3', 'RPL38', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'GIGYF1', 'LMO7', 'BCL2L1', 'STC2', 'CDC42EP1', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'CRIP2', 'MUC3A', 'IMMP2L', 'NAMPT', 'ORMDL2', 'CCT8', 'HSP90B1', 'MFSD12', 'F12', 'AP1S2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'GCNT3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'SPATS2', 'EIF3D', 'RAD51C', 'MNS1', 'PYCARD', 'SFN', 'ASPM', 'MYL12A', 'ELF3', 'STMN1', 'PHGDH', 'UCHL1', 'TUBA1C', 'ADA', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'CTNNAL1', 'PTTG1', 'RAP1GAP', 'TESC', 'AHNAK2', 'PPA2', 'RPS29', 'VIM', 'DOK4', 'HMMR', 'CNFN', 'FA2H', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'DDX39A', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'ZFP36L2', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'GCLC', 'MRPS22', 'ATXN10', 'PRDX1', 'NNMT', 'PLK2', 'PIR', 'RPS24', 'CDC42']</t>
+          <t>['ALDH3A1', 'BIRC3', 'DKC1', 'NFKBIE', 'CALM2', 'XRCC5', 'MYL12B', 'TRAM1', 'CHP1', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'TKT', 'GCNT3', 'GAL', 'FKBP11', 'TUBA1A', 'TP53I3', 'LMO7', 'AIMP2', 'VDAC3', 'CCT7', 'ID3', 'RAB3B', 'ATXN10', 'UNC50', 'LOXL2', 'NDUFC2', 'SUCLG1', 'NDRG1', 'CDC42', 'CCT4', 'HMMR', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EIF2S3', 'EREG', 'ANXA2', 'LMNA', 'ARL6IP1', 'TNRC6B', 'SFN', 'EIF1AY', 'COL5A2', 'EIF3D', 'PLK2', 'NTS', 'GLRX', 'AKR1C3', 'CA8', 'CTNNBL1', 'AKAP12', 'ANXA1', 'SKIL', 'TUBA4A', 'NPTX1', 'MFSD12', 'DUSP5', 'SFRP1', 'DHRS3', 'RND3', 'HMOX1', 'JADE1', 'MZT1', 'ASPM', 'ANP32A', 'FOS', 'GAL3ST1', 'RPL39', 'F12', 'NRDC', 'YARS', 'FSTL3', 'RPL41', 'MAP1LC3B', 'MARCKSL1', 'S100A6', 'CAPN2', 'GIGYF1', 'NPM1', 'TMSB10', 'RBM8A', 'REXO2', 'DUSP1', 'REEP5', 'MGLL', 'PHGDH', 'ANTXR1', 'HILPDA', 'S100A16', 'ID1', 'UBR4', 'ITGA3', 'HSPD1', 'ZFAS1', 'SMOX', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'PCSK1N', 'DOK4', 'CDC123', 'DDX10', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'DHRS7', 'SMIM6', 'SH3BGRL3', 'PDLIM7', 'TSPAN14', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'EIF3M', 'PKM', 'S100A13', 'UBE2C', 'BTG1', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'CNFN', 'KANK1', 'S100A10', 'RAB10', 'KYNU', 'AKR1C2', 'SLC12A2', 'CAPG', 'SMIM14', 'EMC7', 'GSN', 'HOMER3', 'CCT3', 'NAMPT', 'TPPP3', 'AURKB', 'PLAUR', 'LGMN', 'GPX2', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'NPC2', 'PHACTR2', 'PPP1R15A', 'FSCN1', 'INA', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'PLAU', 'CTSH', 'PRPS2', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'ALDH1A1', 'ITGB5', 'ZNF622', 'PTRH2', 'SPP1', 'ZFP36L2', 'DDX39A', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'TOP2A', 'EIF4EBP1', 'RAP2B', 'ALDH2', 'RPS27', 'AGR2', 'PPID', 'S100A3', 'LDHB', 'PUS1', 'CDC25B', 'RAD51C', 'LBH', 'ARHGAP29', 'ACTB', 'RAI14', 'CTNNAL1', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'SGOL1', 'ALG8', 'MAP1B', 'TOB1', 'SDHB', 'LACTB2', 'TOR1AIP2', 'INSIG1', 'NUPR1', 'TMPO', 'NDUFA12', 'PLK1', 'CDC42EP1', 'ZFP36L1', 'PRSS23', 'DNMBP', 'HSPE1', 'CTTN', 'B2M', 'RRS1', 'ACAT2', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'RIPK2', 'ACAT1', 'NOC3L', 'TIMP2', 'UQCRQ', 'LGALS1', 'MNS1', 'PA2G4', 'PIR', 'CD68', 'CYP1B1', 'COX7B', 'LRRC75A', 'SLC27A2', 'TXN', 'TESC', 'CYBA', 'AURKA', 'ZFP36', 'REEP4', 'CD9', 'ATP1B3', 'MMD', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RAP1GAP', 'CYB5B', 'SPATS2', 'RMI2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'ANKRD1', 'NANS', 'TAGLN2', 'FA2H', 'SNRPF', 'RRM2', 'SERPINE2', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'SAT1', 'NUF2', 'INO80C', 'TGFBI', 'SLC35F6', 'DNAJC3', 'IMMP2L', 'RPL28', 'PDLIM5', 'GCLC', 'RHOD', 'NDUFA9', 'SERPINE1', 'ACTG1', 'RPS12', 'ISG20', 'VAMP8', 'CTSL', 'CDCA3', 'BASP1', 'SULT2B1', 'TEAD4', 'OAS1', 'DPM1', 'CCNB1', 'GTPBP4', 'RPL21', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'SLC7A5', 'RILP', 'INHBB', 'MUC5AC', 'ODC1', 'CAV1', 'CRIP1', 'PDXK', 'PPA2', 'RPL38', 'MT2A', 'GOLIM4', 'HMGCS1', 'RPS24', 'SMC1A', 'S100A4', 'GADD45B', 'PHLDA2', 'PRAME', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'LAPTM4A', 'SET', 'GLRX3', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'COX7C', 'PIF1', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'TUBA1C', 'GSTO1', 'CCNB2', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'RPL31', 'CRIP2', 'BIRC5', 'NUCKS1', 'PMEPA1', 'CNIH4', 'TALDO1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'NNMT', 'ELF3', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'UCP2', 'HSPA1A', 'HACD3', 'TK1', 'PPP3CA', 'FHL2', 'IGFBP3', 'HMGB3', 'CDC20', 'INPP1', 'KLF6', 'KRT18', 'MUC3A', 'ORMDL2', 'ECH1', 'MYL12A', 'S100A11', 'FEN1', 'TUBA1B', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['TAS'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IMP'], ['TAS'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'HTP', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['IDA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'ISS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.012241021157112e-06</v>
+        <v>3.842159995987439e-06</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -3309,19 +3309,19 @@
         <v>687</v>
       </c>
       <c r="H9" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J9" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3672316384180791</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2838427947598253</v>
+        <v>0.2852983988355167</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'GAL', 'EREG', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'PRSS3', 'RARRES1', 'CD55', 'UBB', 'SLC3A2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'IGFBP4', 'ITGB5', 'ALDH2', 'CACYBP', 'IGFBP3', 'MTHFD2', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'BLVRB', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'LGALS3', 'RPL39', 'MYL6', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'LXN', 'ACAT1', 'SERPINB1', 'FGFBP1', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'KRT7', 'BASP1', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'HILPDA', 'CCT4', 'ITGA3', 'TALDO1', 'EEF1A1', 'FSCN1', 'HSP90AB1', 'SH3BGRL3', 'ADM', 'METRN', 'ITGB1', 'AXL', 'S100A13', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'LOXL2', 'HSPA8', 'EIF2S3', 'UPK1B', 'PRSS23', 'SERPINE2', 'RPL37A', 'CSRP1', 'HMOX1', 'KRT8', 'CTNNB1', 'INA', 'CTSH', 'ALDH3A1', 'CCT2', 'TUBB', 'INHBB', 'SLC12A2', 'ATP1B3', 'KRT81', 'FN1', 'CDK1', 'CD44', 'CCL2', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'TKT', 'TXN', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CXCL5', 'CD70', 'STC2', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'NAMPT', 'CCT8', 'HSP90B1', 'F12', 'CAPG', 'GCNT3', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'CHP1', 'RPS29', 'VIM', 'PSMA3', 'LDHB', 'KRT19', 'CLU', 'IGFBP6', 'S100A16', 'S100A10', 'ACAT2', 'CXCL3', 'NPC2', 'SLC27A2', 'B2M', 'INSL4', 'ATXN10', 'PRDX1', 'CDC42']</t>
+          <t>['ALDH3A1', 'MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'GAL', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'ATXN10', 'LOXL2', 'NDRG1', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'EREG', 'ANXA2', 'RSPO3', 'SFN', 'COL5A2', 'GLRX', 'AKR1C3', 'ANXA1', 'TUBA4A', 'SFRP1', 'HMOX1', 'RPL39', 'F12', 'YARS', 'FSTL3', 'IGFBP6', 'CXCL3', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'HILPDA', 'S100A16', 'ITGA3', 'HSPD1', 'LXN', 'GPRC5A', 'PCSK1N', 'SH3BGRL3', 'GPX3', 'EEF1A1', 'VIM', 'TIMP1', 'PKM', 'S100A13', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'SLC12A2', 'CAPG', 'GSN', 'CXCL5', 'CCT3', 'NAMPT', 'LGMN', 'TUBB', 'CCT5', 'RAN', 'NPC2', 'FSCN1', 'FGFBP1', 'INA', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'ALDH2', 'AGR2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'PRSS23', 'HSPE1', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'ACAT1', 'TIMP2', 'LGALS1', 'PA2G4', 'SLC27A2', 'TXN', 'CD70', 'CD9', 'ATP1B3', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'SERPINE2', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'CLU', 'SLC7A5', 'INHBB', 'METRN', 'MUC5AC', 'PDXK', 'S100A4', 'INSL4', 'SLC26A2', 'CCT8', 'TXNRD1', 'CD55', 'HSPA5', 'PRDX1', 'ATP1B1', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'HLA-A', 'ADM', 'UBB', 'UBC', 'CD63', 'CDK1', 'RPS28', 'COTL1', 'AKR1B1', 'NCL', 'CCL2', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'GSTO1', 'IGFBP4', 'RPL31', 'UPK1B', 'TALDO1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'PRSS3', 'ITGB1', 'HSPA1A', 'IGFBP3', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IBA'], ['HDA', 'TAS'], ['IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['IBA'], ['HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['IBA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.474513332740603e-05</v>
+        <v>6.579396423768348e-05</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -3372,22 +3372,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H10" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J10" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3898305084745763</v>
+        <v>0.3909774436090225</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2723684210526316</v>
+        <v>0.2733245729303548</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'GAL', 'TMSB4X', 'EREG', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'CNIH4', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'PRSS3', 'RARRES1', 'GOLIM4', 'CD55', 'UBB', 'SLC3A2', 'PSMC2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'ITGB5', 'ALDH2', 'CAV1', 'CACYBP', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'CAV2', 'BLVRB', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'RAB3B', 'SFRP1', 'LGALS3', 'MYL6', 'MMD', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'ACAT1', 'NPTX1', 'SERPINB1', 'CTTN', 'LAPTM4A', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'BASP1', 'XRCC5', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'HILPDA', 'CCT4', 'ITGA3', 'NDUFC2', 'DYNLL1', 'LITAF', 'TALDO1', 'EEF1A1', 'MAP1LC3B', 'FSCN1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'ITGB1', 'AXL', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'TSPAN14', 'HSPA8', 'EIF2S3', 'PMEPA1', 'CD68', 'UPK1B', 'PRSS23', 'SERPINE2', 'RPL37A', 'CSRP1', 'KRT8', 'CTNNB1', 'CTSH', 'CCT2', 'CYBA', 'TUBB', 'SLC12A2', 'ATP1B3', 'FN1', 'CDK1', 'CD44', 'PSMD14', 'LY6K', 'PHACTR2', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'ANTXR1', 'TKT', 'TXN', 'PLAUR', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'CCT5', 'SLC7A5', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CD70', 'BCL2L1', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'NAMPT', 'CCT8', 'HSP90B1', 'MFSD12', 'F12', 'AP1S2', 'CAPG', 'RILP', 'GCNT3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'PYCARD', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'TUBA1C', 'ADA', 'CHP1', 'RAP1GAP', 'RPS29', 'VIM', 'PSMA3', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'S100A16', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'PRDX1', 'CDC42']</t>
+          <t>['CALM2', 'XRCC5', 'MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'GAL', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'NDUFC2', 'NDRG1', 'CDC42', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'EREG', 'ANXA2', 'SFN', 'NTS', 'GLRX', 'AKR1C3', 'ANXA1', 'SKIL', 'TUBA4A', 'NPTX1', 'MFSD12', 'SFRP1', 'F12', 'MAP1LC3B', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'ANTXR1', 'HILPDA', 'S100A16', 'UBR4', 'ITGA3', 'HSPD1', 'GPRC5A', 'LY6K', 'PCSK1N', 'SH3BGRL3', 'TSPAN14', 'LITAF', 'GPX3', 'EEF1A1', 'VIM', 'TMSB4X', 'TIMP1', 'PKM', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'SLC12A2', 'CAPG', 'GSN', 'CCT3', 'NAMPT', 'PLAUR', 'LGMN', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'NPC2', 'PHACTR2', 'FSCN1', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'ALDH2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'PRSS23', 'HSPE1', 'CTTN', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'RIPK2', 'ACAT1', 'TIMP2', 'LGALS1', 'PA2G4', 'CD68', 'SLC27A2', 'TXN', 'CYBA', 'CD70', 'CD9', 'ATP1B3', 'MMD', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'SERPINE2', 'PYCARD', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'RHOD', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'CLU', 'SLC7A5', 'RILP', 'MUC5AC', 'CAV1', 'PDXK', 'GOLIM4', 'S100A4', 'SLC26A2', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'ATP1B1', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'PSMD14', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'CD63', 'LAPTM4A', 'CDK1', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'AP1S2', 'HSP90B1', 'TUBA1C', 'GSTO1', 'RPL31', 'PMEPA1', 'UPK1B', 'CNIH4', 'TALDO1', 'SLC3A2', 'CACYBP', 'PTP4A1', 'PRSS3', 'ITGB1', 'HSPA1A', 'KRT18', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['TAS'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['IBA'], ['IDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['HDA'], ['IEA'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'ISS'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'IEA']]</t>
+          <t>[['HDA', 'ISS', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA'], ['HDA'], ['ISS', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IBA'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.271336068321521e-05</v>
+        <v>0.0001035092029252626</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -3438,22 +3438,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H11" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I11" t="n">
         <v>214</v>
       </c>
       <c r="J11" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4030131826741996</v>
+        <v>0.4022556390977444</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2698612862547289</v>
+        <v>0.2702020202020202</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GLRX', 'GSN', 'AKR1C3', 'GAL', 'TMSB4X', 'EREG', 'MARCKSL1', 'HSPA2', 'ATP1B1', 'PKM', 'SQSTM1', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'NANS', 'PRDX4', 'SERPINE1', 'RAP2B', 'PRSS3', 'RARRES1', 'CD55', 'UBB', 'SLC3A2', 'PSMC2', 'CTSL', 'PGD', 'KRT18', 'TAGLN2', 'HLA-A', 'IGFBP4', 'ITGB5', 'AKR1B10', 'ALDH2', 'CACYBP', 'IGFBP3', 'MTHFD2', 'YWHAE', 'LGMN', 'CCDC80', 'S100A6', 'ALDH1A1', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'BLVRB', 'MDK', 'TXNRD1', 'SULT2B1', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'LGALS3', 'RPL39', 'MYL6', 'B4GALT1', 'UBC', 'ACTB', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'LXN', 'ACAT1', 'NPTX1', 'SERPINB1', 'FGFBP1', 'GSTO1', 'VAMP8', 'SLPI', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'BASP1', 'XRCC5', 'TUBB4B', 'RPL31', 'RAB10', 'ANXA1', 'ANXA4', 'PTPRS', 'RPS18', 'NDRG1', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'HILPDA', 'CCT4', 'ITGA3', 'CRIM1', 'TALDO1', 'EEF1A1', 'FSCN1', 'HSP90AB1', 'SH3BGRL3', 'ADM', 'METRN', 'ITGB1', 'AXL', 'S100A13', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'LOXL2', 'HSPA8', 'EIF2S3', 'UPK1B', 'PRSS23', 'SERPINE2', 'RPL37A', 'CSRP1', 'HMOX1', 'KRT8', 'CTNNB1', 'INA', 'CTSH', 'ALDH3A1', 'CCT2', 'TUBB', 'INHBB', 'SLC12A2', 'ATP1B3', 'KRT81', 'FN1', 'CDK1', 'CD44', 'CCL2', 'PSMD14', 'OAS1', 'LY6K', 'PTPRF', 'GPRC5A', 'PLAU', 'ANXA2', 'AKR1B1', 'PCNA', 'TKT', 'TXN', 'PLAUR', 'C1orf56', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'EVA1C', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'GPX3', 'CXCL5', 'CD70', 'STC2', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'MUC3A', 'NAMPT', 'CCT8', 'HSP90B1', 'F12', 'CAPG', 'GCNT3', 'ECH1', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'PYCARD', 'SFN', 'MYL12A', 'STMN1', 'PHGDH', 'CHP1', 'RPS29', 'VIM', 'NRP2', 'RSPO3', 'PSMA3', 'LDHB', 'KRT19', 'CLU', 'IGFBP6', 'S100A16', 'S100A10', 'ACAT2', 'CXCL3', 'NPC2', 'SLC27A2', 'B2M', 'INSL4', 'ATXN10', 'PRDX1', 'CDC42']</t>
+          <t>['ALDH3A1', 'XRCC5', 'MYL12B', 'CHP1', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'GAL', 'TUBA1A', 'VDAC3', 'CCT7', 'RAB3B', 'ATXN10', 'LOXL2', 'NDRG1', 'CDC42', 'MDK', 'CCT4', 'AHNAK', 'LGALS3', 'EIF2S3', 'EREG', 'ANXA2', 'RSPO3', 'SFN', 'COL5A2', 'NTS', 'GLRX', 'AKR1C3', 'ANXA1', 'TUBA4A', 'NPTX1', 'SFRP1', 'HMOX1', 'RPL39', 'F12', 'YARS', 'FSTL3', 'IGFBP6', 'CXCL3', 'MARCKSL1', 'S100A6', 'CAPN2', 'PHGDH', 'HILPDA', 'S100A16', 'ITGA3', 'HSPD1', 'LXN', 'GPRC5A', 'LY6K', 'PCSK1N', 'SH3BGRL3', 'GPX3', 'EEF1A1', 'VIM', 'TMSB4X', 'TIMP1', 'PKM', 'S100A13', 'PPP1CB', 'PTPRS', 'S100A10', 'RAB10', 'CRIM1', 'SLC12A2', 'CAPG', 'GSN', 'CXCL5', 'CCT3', 'NAMPT', 'PLAUR', 'LGMN', 'TUBB', 'CCT5', 'RAN', 'NPC2', 'FSCN1', 'FGFBP1', 'INA', 'STMN1', 'CCT2', 'PRDX4', 'PLAU', 'CTSH', 'BLVRB', 'AKR1B10', 'CTNNB1', 'FN1', 'ALDH1A1', 'ITGB5', 'SPP1', 'PTPRF', 'PGD', 'KRT7', 'CAPZA1', 'RAP2B', 'EVA1C', 'ALDH2', 'AGR2', 'LDHB', 'ACTB', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'NRP2', 'C1orf56', 'PRSS23', 'HSPE1', 'B2M', 'ACAT2', 'MFGE8', 'IGFBP7', 'ACAT1', 'TIMP2', 'LGALS1', 'PA2G4', 'SLC27A2', 'TXN', 'CD70', 'CD9', 'ATP1B3', 'B4GALT1', 'HSPA8', 'PSMA3', 'CTSB', 'SQSTM1', 'SERPINB1', 'NANS', 'TAGLN2', 'SERPINE2', 'PYCARD', 'CSRP1', 'RPS18', 'TGFBI', 'SLC35F6', 'DNAJC3', 'RPL28', 'SERPINE1', 'ACTG1', 'VAMP8', 'CTSL', 'BASP1', 'SULT2B1', 'OAS1', 'CLU', 'SLC7A5', 'INHBB', 'METRN', 'MUC5AC', 'PDXK', 'S100A4', 'INSL4', 'SLC26A2', 'CCT8', 'TXNRD1', 'CD55', 'HSPA5', 'PRDX1', 'ATP1B1', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'SLPI', 'EIF3E', 'HSPA2', 'ENO1', 'PSMD14', 'HLA-A', 'ADM', 'UBB', 'UBC', 'CD63', 'CDK1', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'CCL2', 'AXL', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'HSP90B1', 'GSTO1', 'IGFBP4', 'RPL31', 'UPK1B', 'TALDO1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'CCDC80', 'PRSS3', 'ITGB1', 'HSPA1A', 'IGFBP3', 'KRT18', 'MUC3A', 'ECH1', 'MYL12A', 'S100A11', 'RPL37A']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IBA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'IBA'], ['IDA', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['NAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['IBA'], ['HDA', 'IBA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA'], ['NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.00240184300592478</v>
+        <v>0.001005625010815894</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -3504,22 +3504,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="H12" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I12" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="J12" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4726930320150659</v>
+        <v>0.4830827067669173</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2522613065326633</v>
+        <v>0.2534516765285996</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['MUC5AC', 'GPX1', 'RBM8A', 'NUCKS1', 'GSN', 'TSFM', 'DKC1', 'TOP2A', 'TMSB4X', 'FBXO5', 'DDX21', 'NOC3L', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'TRIB3', 'PKM', 'SQSTM1', 'S100A11', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'UTP18', 'ID2', 'CCNA2', 'PSMC1', 'SMC1A', 'PRDX4', 'SERPINE1', 'TPX2', 'ID3', 'PKMYT1', 'NDUFA9', 'PRSS3', 'UBE2S', 'GOLIM4', 'NRDC', 'RPS27', 'NUPR1', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'PSMC2', 'SGOL1', 'CTSL', 'NOL7', 'KRT18', 'SKIL', 'IGFBP4', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'LGMN', 'DCAF13', 'DNAJC3', 'TIMP2', 'ASF1A', 'BLVRB', 'ZFAS1', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SLC35F6', 'HMGB2', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'FOSL1', 'NEAT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'TIMP1', 'PSMD7', 'ACAT1', 'SERPINB1', 'RAI14', 'PIF1', 'PDLIM7', 'SNRPF', 'CES1', 'TNRC6B', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'PDXK', 'ZNF622', 'CBX6', 'PSMC4', 'BASP1', 'XRCC5', 'TUBB4B', 'HOXB8', 'KYNU', 'ANXA1', 'MORC4', 'KIF23', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'IRF2BP2', 'PA2G4', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'PDHB', 'LITAF', 'BTG1', 'EEF1A1', 'RPS12', 'CCNB1', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'S100A13', 'CDCA5', 'FSTL3', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'RAD21', 'SUCLG1', 'PRSS23', 'FOS', 'NUDT19', 'HMOX1', 'KRT8', 'CEBPB', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'CTSH', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'GINS2', 'TUBB', 'CENPF', 'TEAD4', 'NOLC1', 'FN1', 'DUSP5', 'ANP32A', 'CDK1', 'FEN1', 'AURKA', 'PSMD14', 'OAS1', 'REXO2', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'UQCRC2', 'GPRC5A', 'ANXA2', 'AKR1B1', 'PCNA', 'GABRA5', 'TKT', 'TXN', 'PPP3CA', 'PLAUR', 'MKI67', 'RPS28', 'PPP1CB', 'HSPA5', 'YARS', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'BCL2L1', 'STC2', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'MUC3A', 'NAMPT', 'CKS1B', 'CCT8', 'HSP90B1', 'CAPG', 'ATF4', 'EIF4A3', 'ECH1', 'HSP90AA1', 'TMEM92', 'HSPE1', 'RAD51C', 'PYCARD', 'ELF3', 'UCHL1', 'UTP6', 'ADA', 'TESC', 'STK17A', 'PPA2', 'RPS29', 'VIM', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'DDX39A', 'PSMA3', 'CDC25B', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'S100A10', 'NPC2', 'SLC27A2', 'B2M', 'MRPS22', 'PIR', 'RPS24', 'UHRF1']</t>
+          <t>['BIRC3', 'DKC1', 'NFKBIE', 'XRCC5', 'CDCA5', 'KRT8', 'TKT', 'MORC4', 'ID3', 'LOXL2', 'SUCLG1', 'CCT4', 'LGALS3', 'PDHB', 'ANXA2', 'LMNA', 'TNRC6B', 'UTP18', 'COL5A2', 'CTNNBL1', 'ANXA1', 'SKIL', 'DUSP5', 'HMOX1', 'JADE1', 'FAM64A', 'ANP32A', 'FOS', 'RPL39', 'NRDC', 'YARS', 'FSTL3', 'CKS1B', 'TMEM92', 'NPM1', 'RBM8A', 'REXO2', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'HSPD1', 'ZFAS1', 'SMOX', 'GPRC5A', 'DDX10', 'PRMT1', 'NUDT19', 'EIF4A3', 'SH3BGRL3', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'PPP1CB', 'TRIB3', 'CES1', 'S100A10', 'KYNU', 'CAPG', 'GSN', 'NAMPT', 'AURKB', 'PLAUR', 'LGMN', 'TUBB', 'RAN', 'FOSL1', 'NPC2', 'UTP6', 'PSMC1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'CTSH', 'BLVRB', 'SLBP', 'CTNNB1', 'FN1', 'ZNF622', 'SPP1', 'DDX39A', 'TOP2A', 'ALDH2', 'RPS27', 'PPID', 'ASF1A', 'PUS1', 'CDC25B', 'RAD51C', 'ACTB', 'RAI14', 'ORC5', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'SDHB', 'LACTB2', 'NUPR1', 'PLK1', 'PRSS23', 'DNMBP', 'HSPE1', 'B2M', 'RRS1', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'ACAT1', 'NOC3L', 'TIMP2', 'LGALS1', 'MNS1', 'PA2G4', 'PIR', 'SLC27A2', 'TXN', 'TESC', 'GINS2', 'AURKA', 'NAA15', 'CDKN2D', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RMI2', 'SQSTM1', 'SERPINB1', 'STK17A', 'ANKRD1', 'SNRPF', 'RRM2', 'CENPA', 'PYCARD', 'CCNA2', 'RPS18', 'SRP54', 'NUF2', 'INO80C', 'SLC35F6', 'DNAJC3', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'RPS12', 'ISG20', 'NEAT1', 'CTSL', 'BASP1', 'TEAD4', 'OAS1', 'CCNB1', 'GTPBP4', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'MUC5AC', 'PDXK', 'PPA2', 'GOLIM4', 'RPS24', 'SMC1A', 'S100A4', 'PRAME', 'CCT8', 'TXNRD1', 'HSPA5', 'HMGB2', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'HSPA2', 'NUP37', 'PSMD14', 'MRPS22', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'SET', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'PIF1', 'GABRA5', 'HSP90B1', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'BIRC5', 'NUCKS1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'MKI67', 'ELF3', 'ATF4', 'HMGA1', 'PRSS3', 'RAD21', 'CCND3', 'PSMC4', 'HSPA1A', 'PPP3CA', 'FHL2', 'IGFBP3', 'CDC20', 'KLF6', 'KRT18', 'MUC3A', 'ECH1', 'S100A11', 'FEN1']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IEA'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IBA'], ['IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['NAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['NAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['TAS'], ['TAS'], ['IPI', 'ISS', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3550,42 +3550,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GO:0031974</t>
+          <t>GO:0070013</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>membrane-enclosed lumen</t>
+          <t>intracellular organelle lumen</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.00240184300592478</v>
+        <v>0.001005625010815894</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>"The enclosed volume within a sealed membrane or between two sealed membranes. Encompasses the volume enclosed by the membranes of a particular organelle, e.g. endoplasmic reticulum lumen, or the space between the two lipid bilayers of a double membrane surrounding an organelle, e.g. nuclear envelope lumen." [GOC:add, GOC:mah]</t>
+          <t>"An organelle lumen that is part of an intracellular organelle." [GOC:mah]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="H13" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I13" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="J13" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4726930320150659</v>
+        <v>0.4830827067669173</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2522613065326633</v>
+        <v>0.2534516765285996</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0043229', 'GO:0043233']</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['MUC5AC', 'GPX1', 'RBM8A', 'NUCKS1', 'GSN', 'TSFM', 'DKC1', 'TOP2A', 'TMSB4X', 'FBXO5', 'DDX21', 'NOC3L', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'TRIB3', 'PKM', 'SQSTM1', 'S100A11', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'UTP18', 'ID2', 'CCNA2', 'PSMC1', 'SMC1A', 'PRDX4', 'SERPINE1', 'TPX2', 'ID3', 'PKMYT1', 'NDUFA9', 'PRSS3', 'UBE2S', 'GOLIM4', 'NRDC', 'RPS27', 'NUPR1', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'PSMC2', 'SGOL1', 'CTSL', 'NOL7', 'KRT18', 'SKIL', 'IGFBP4', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'LGMN', 'DCAF13', 'DNAJC3', 'TIMP2', 'ASF1A', 'BLVRB', 'ZFAS1', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SLC35F6', 'HMGB2', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'FOSL1', 'NEAT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'TIMP1', 'PSMD7', 'ACAT1', 'SERPINB1', 'RAI14', 'PIF1', 'PDLIM7', 'SNRPF', 'CES1', 'TNRC6B', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'PDXK', 'ZNF622', 'CBX6', 'PSMC4', 'BASP1', 'XRCC5', 'TUBB4B', 'HOXB8', 'KYNU', 'ANXA1', 'MORC4', 'KIF23', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'IRF2BP2', 'PA2G4', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'PDHB', 'LITAF', 'BTG1', 'EEF1A1', 'RPS12', 'CCNB1', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'S100A13', 'CDCA5', 'FSTL3', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'RAD21', 'SUCLG1', 'PRSS23', 'FOS', 'NUDT19', 'HMOX1', 'KRT8', 'CEBPB', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'CTSH', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'GINS2', 'TUBB', 'CENPF', 'TEAD4', 'NOLC1', 'FN1', 'DUSP5', 'ANP32A', 'CDK1', 'FEN1', 'AURKA', 'PSMD14', 'OAS1', 'REXO2', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'UQCRC2', 'GPRC5A', 'ANXA2', 'AKR1B1', 'PCNA', 'GABRA5', 'TKT', 'TXN', 'PPP3CA', 'PLAUR', 'MKI67', 'RPS28', 'PPP1CB', 'HSPA5', 'YARS', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'BCL2L1', 'STC2', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'MUC3A', 'NAMPT', 'CKS1B', 'CCT8', 'HSP90B1', 'CAPG', 'ATF4', 'EIF4A3', 'ECH1', 'HSP90AA1', 'TMEM92', 'HSPE1', 'RAD51C', 'PYCARD', 'ELF3', 'UCHL1', 'UTP6', 'ADA', 'TESC', 'STK17A', 'PPA2', 'RPS29', 'VIM', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'DDX39A', 'PSMA3', 'CDC25B', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'S100A10', 'NPC2', 'SLC27A2', 'B2M', 'MRPS22', 'PIR', 'RPS24', 'UHRF1']</t>
+          <t>['BIRC3', 'DKC1', 'NFKBIE', 'XRCC5', 'CDCA5', 'KRT8', 'TKT', 'MORC4', 'ID3', 'LOXL2', 'SUCLG1', 'CCT4', 'LGALS3', 'PDHB', 'ANXA2', 'LMNA', 'TNRC6B', 'UTP18', 'COL5A2', 'CTNNBL1', 'ANXA1', 'SKIL', 'DUSP5', 'HMOX1', 'JADE1', 'FAM64A', 'ANP32A', 'FOS', 'RPL39', 'NRDC', 'YARS', 'FSTL3', 'CKS1B', 'TMEM92', 'NPM1', 'RBM8A', 'REXO2', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'HSPD1', 'ZFAS1', 'SMOX', 'GPRC5A', 'DDX10', 'PRMT1', 'NUDT19', 'EIF4A3', 'SH3BGRL3', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'PPP1CB', 'TRIB3', 'CES1', 'S100A10', 'KYNU', 'CAPG', 'GSN', 'NAMPT', 'AURKB', 'PLAUR', 'LGMN', 'TUBB', 'RAN', 'FOSL1', 'NPC2', 'UTP6', 'PSMC1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'CTSH', 'BLVRB', 'SLBP', 'CTNNB1', 'FN1', 'ZNF622', 'SPP1', 'DDX39A', 'TOP2A', 'ALDH2', 'RPS27', 'PPID', 'ASF1A', 'PUS1', 'CDC25B', 'RAD51C', 'ACTB', 'RAI14', 'ORC5', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'SDHB', 'LACTB2', 'NUPR1', 'PLK1', 'PRSS23', 'DNMBP', 'HSPE1', 'B2M', 'RRS1', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'ACAT1', 'NOC3L', 'TIMP2', 'LGALS1', 'MNS1', 'PA2G4', 'PIR', 'SLC27A2', 'TXN', 'TESC', 'GINS2', 'AURKA', 'NAA15', 'CDKN2D', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RMI2', 'SQSTM1', 'SERPINB1', 'STK17A', 'ANKRD1', 'SNRPF', 'RRM2', 'CENPA', 'PYCARD', 'CCNA2', 'RPS18', 'SRP54', 'NUF2', 'INO80C', 'SLC35F6', 'DNAJC3', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'RPS12', 'ISG20', 'NEAT1', 'CTSL', 'BASP1', 'TEAD4', 'OAS1', 'CCNB1', 'GTPBP4', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'MUC5AC', 'PDXK', 'PPA2', 'GOLIM4', 'RPS24', 'SMC1A', 'S100A4', 'PRAME', 'CCT8', 'TXNRD1', 'HSPA5', 'HMGB2', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'HSPA2', 'NUP37', 'PSMD14', 'MRPS22', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'SET', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'PIF1', 'GABRA5', 'HSP90B1', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'BIRC5', 'NUCKS1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'MKI67', 'ELF3', 'ATF4', 'HMGA1', 'PRSS3', 'RAD21', 'CCND3', 'PSMC4', 'HSPA1A', 'PPP3CA', 'FHL2', 'IGFBP3', 'CDC20', 'KLF6', 'KRT18', 'MUC3A', 'ECH1', 'S100A11', 'FEN1']</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IEA'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IBA'], ['IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['NAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['NAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['TAS'], ['TAS'], ['IPI', 'ISS', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3616,42 +3616,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GO:0070013</t>
+          <t>GO:0031974</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>intracellular organelle lumen</t>
+          <t>membrane-enclosed lumen</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.00240184300592478</v>
+        <v>0.001005625010815894</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>"An organelle lumen that is part of an intracellular organelle." [GOC:mah]</t>
+          <t>"The enclosed volume within a sealed membrane or between two sealed membranes. Encompasses the volume enclosed by the membranes of a particular organelle, e.g. endoplasmic reticulum lumen, or the space between the two lipid bilayers of a double membrane surrounding an organelle, e.g. nuclear envelope lumen." [GOC:add, GOC:mah]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="H14" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I14" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="J14" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4726930320150659</v>
+        <v>0.4830827067669173</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2522613065326633</v>
+        <v>0.2534516765285996</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3660,64 +3660,64 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>['GO:0043229', 'GO:0043233']</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>['MUC5AC', 'GPX1', 'RBM8A', 'NUCKS1', 'GSN', 'TSFM', 'DKC1', 'TOP2A', 'TMSB4X', 'FBXO5', 'DDX21', 'NOC3L', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'TRIB3', 'PKM', 'SQSTM1', 'S100A11', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'UTP18', 'ID2', 'CCNA2', 'PSMC1', 'SMC1A', 'PRDX4', 'SERPINE1', 'TPX2', 'ID3', 'PKMYT1', 'NDUFA9', 'PRSS3', 'UBE2S', 'GOLIM4', 'NRDC', 'RPS27', 'NUPR1', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'PSMC2', 'SGOL1', 'CTSL', 'NOL7', 'KRT18', 'SKIL', 'IGFBP4', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'LGMN', 'DCAF13', 'DNAJC3', 'TIMP2', 'ASF1A', 'BLVRB', 'ZFAS1', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SLC35F6', 'HMGB2', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'FOSL1', 'NEAT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'TIMP1', 'PSMD7', 'ACAT1', 'SERPINB1', 'RAI14', 'PIF1', 'PDLIM7', 'SNRPF', 'CES1', 'TNRC6B', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'PDXK', 'ZNF622', 'CBX6', 'PSMC4', 'BASP1', 'XRCC5', 'TUBB4B', 'HOXB8', 'KYNU', 'ANXA1', 'MORC4', 'KIF23', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'IRF2BP2', 'PA2G4', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'PDHB', 'LITAF', 'BTG1', 'EEF1A1', 'RPS12', 'CCNB1', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'S100A13', 'CDCA5', 'FSTL3', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'RAD21', 'SUCLG1', 'PRSS23', 'FOS', 'NUDT19', 'HMOX1', 'KRT8', 'CEBPB', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'CTSH', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'GINS2', 'TUBB', 'CENPF', 'TEAD4', 'NOLC1', 'FN1', 'DUSP5', 'ANP32A', 'CDK1', 'FEN1', 'AURKA', 'PSMD14', 'OAS1', 'REXO2', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'UQCRC2', 'GPRC5A', 'ANXA2', 'AKR1B1', 'PCNA', 'GABRA5', 'TKT', 'TXN', 'PPP3CA', 'PLAUR', 'MKI67', 'RPS28', 'PPP1CB', 'HSPA5', 'YARS', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'BCL2L1', 'STC2', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'MUC3A', 'NAMPT', 'CKS1B', 'CCT8', 'HSP90B1', 'CAPG', 'ATF4', 'EIF4A3', 'ECH1', 'HSP90AA1', 'TMEM92', 'HSPE1', 'RAD51C', 'PYCARD', 'ELF3', 'UCHL1', 'UTP6', 'ADA', 'TESC', 'STK17A', 'PPA2', 'RPS29', 'VIM', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'DDX39A', 'PSMA3', 'CDC25B', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'S100A10', 'NPC2', 'SLC27A2', 'B2M', 'MRPS22', 'PIR', 'RPS24', 'UHRF1']</t>
+          <t>['BIRC3', 'DKC1', 'NFKBIE', 'XRCC5', 'CDCA5', 'KRT8', 'TKT', 'MORC4', 'ID3', 'LOXL2', 'SUCLG1', 'CCT4', 'LGALS3', 'PDHB', 'ANXA2', 'LMNA', 'TNRC6B', 'UTP18', 'COL5A2', 'CTNNBL1', 'ANXA1', 'SKIL', 'DUSP5', 'HMOX1', 'JADE1', 'FAM64A', 'ANP32A', 'FOS', 'RPL39', 'NRDC', 'YARS', 'FSTL3', 'CKS1B', 'TMEM92', 'NPM1', 'RBM8A', 'REXO2', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'HSPD1', 'ZFAS1', 'SMOX', 'GPRC5A', 'DDX10', 'PRMT1', 'NUDT19', 'EIF4A3', 'SH3BGRL3', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'PPP1CB', 'TRIB3', 'CES1', 'S100A10', 'KYNU', 'CAPG', 'GSN', 'NAMPT', 'AURKB', 'PLAUR', 'LGMN', 'TUBB', 'RAN', 'FOSL1', 'NPC2', 'UTP6', 'PSMC1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'CTSH', 'BLVRB', 'SLBP', 'CTNNB1', 'FN1', 'ZNF622', 'SPP1', 'DDX39A', 'TOP2A', 'ALDH2', 'RPS27', 'PPID', 'ASF1A', 'PUS1', 'CDC25B', 'RAD51C', 'ACTB', 'RAI14', 'ORC5', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'SDHB', 'LACTB2', 'NUPR1', 'PLK1', 'PRSS23', 'DNMBP', 'HSPE1', 'B2M', 'RRS1', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'ACAT1', 'NOC3L', 'TIMP2', 'LGALS1', 'MNS1', 'PA2G4', 'PIR', 'SLC27A2', 'TXN', 'TESC', 'GINS2', 'AURKA', 'NAA15', 'CDKN2D', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RMI2', 'SQSTM1', 'SERPINB1', 'STK17A', 'ANKRD1', 'SNRPF', 'RRM2', 'CENPA', 'PYCARD', 'CCNA2', 'RPS18', 'SRP54', 'NUF2', 'INO80C', 'SLC35F6', 'DNAJC3', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'RPS12', 'ISG20', 'NEAT1', 'CTSL', 'BASP1', 'TEAD4', 'OAS1', 'CCNB1', 'GTPBP4', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'MUC5AC', 'PDXK', 'PPA2', 'GOLIM4', 'RPS24', 'SMC1A', 'S100A4', 'PRAME', 'CCT8', 'TXNRD1', 'HSPA5', 'HMGB2', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'HSPA2', 'NUP37', 'PSMD14', 'MRPS22', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'SET', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'PCNA', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'PIF1', 'GABRA5', 'HSP90B1', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'BIRC5', 'NUCKS1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'MKI67', 'ELF3', 'ATF4', 'HMGA1', 'PRSS3', 'RAD21', 'CCND3', 'PSMC4', 'HSPA1A', 'PPP3CA', 'FHL2', 'IGFBP3', 'CDC20', 'KLF6', 'KRT18', 'MUC3A', 'ECH1', 'S100A11', 'FEN1']</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IEA'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IBA'], ['IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['NAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['NAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'NAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['TAS'], ['TAS'], ['IPI', 'ISS', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:MF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GO:0006259</t>
+          <t>GO:0003674</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNA metabolic process</t>
+          <t>molecular_function</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.004756999490414171</v>
+        <v>0.002076081669167949</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>"Any cellular metabolic process involving deoxyribonucleic acid. This is one of the two main types of nucleic acid, consisting of a long, unbranched macromolecule formed from one, or more commonly, two, strands of linked deoxyribonucleotides." [ISBN:0198506732]</t>
+          <t>"A molecular process that can be carried out by the action of a single macromolecular machine, usually via direct physical interactions with other molecular entities. Function in this sense denotes an action, or activity, that a gene product (or a complex) performs." [GOC:pdt]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>173</v>
+        <v>2484</v>
       </c>
       <c r="H15" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I15" t="n">
-        <v>63</v>
+        <v>519</v>
       </c>
       <c r="J15" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1186440677966102</v>
+        <v>0.9755639097744361</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3641618497109826</v>
+        <v>0.2089371980676329</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3726,17 +3726,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>['GO:0090304']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>['NUCKS1', 'DKC1', 'TOP2A', 'FBXO5', 'NOC3L', 'EREG', 'MCM7', 'S100A11', 'CCNA2', 'SMC1A', 'ID3', 'CYP1B1', 'TK1', 'JADE1', 'KPNA2', 'RMI2', 'TERF1', 'ASF1A', 'ORC5', 'HMGB2', 'ACTB', 'NPM1', 'PIF1', 'ANKRD1', 'XRCC5', 'CDKN2D', 'INO80C', 'CCT7', 'CCT3', 'CCT4', 'DYNLL1', 'HMGB3', 'HSP90AB1', 'PLK1', 'CDCA5', 'HSPD1', 'RAD21', 'LMNA', 'CTNNB1', 'CCT2', 'GINS2', 'CENPF', 'CDK1', 'FEN1', 'PSMD14', 'REXO2', 'GTPBP4', 'PCNA', 'APOBEC3C', 'CCT5', 'RAN', 'HMGA1', 'CCT8', 'HSP90AA1', 'RAD51C', 'PTTG1', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'ISG20', 'CDC42', 'UHRF1']</t>
+          <t>['ALDH3A1', 'BIRC3', 'DKC1', 'NFKBIE', 'TNFRSF12A', 'CALM2', 'XRCC5', 'MYL12B', 'TRAM1', 'CHP1', 'PAQR5', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'GAL', 'FKBP11', 'TM4SF1', 'TUBA1A', 'TP53I3', 'LMO7', 'AIMP2', 'MORC4', 'VDAC3', 'CCT7', 'ID3', 'DEPDC1B', 'RAB3B', 'ATXN10', 'UNC50', 'LOXL2', 'NDUFC2', 'SUCLG1', 'NDRG1', 'CDC42', 'MDK', 'CCT4', 'HMMR', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EIF2S3', 'EREG', 'ANXA2', 'LMNA', 'RSPO3', 'ARL6IP1', 'TNRC6B', 'UTP18', 'SFN', 'EIF1AY', 'COL5A2', 'EIF3D', 'PLK2', 'NTS', 'GLRX', 'AKR1C3', 'CKS2', 'CA8', 'CTNNBL1', 'AKAP12', 'ANXA1', 'EMP3', 'SKIL', 'TUBA4A', 'NPTX1', 'MFSD12', 'DUSP5', 'SFRP1', 'DHRS3', 'KCNMA1', 'RND3', 'HMOX1', 'JADE1', 'MZT1', 'ASPM', 'FAM64A', 'ANP32A', 'FOS', 'GAL3ST1', 'RPL39', 'F12', 'NRDC', 'YARS', 'FSTL3', 'IGFBP6', 'RPL41', 'TMEM54', 'MAP1LC3B', 'CXCL3', 'MARCKSL1', 'CKS1B', 'S100A6', 'MESP1', 'TMEM92', 'CAPN2', 'GIGYF1', 'NPM1', 'TMSB10', 'RBM8A', 'REXO2', 'DUSP1', 'REEP5', 'MGLL', 'PHGDH', 'ANTXR1', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'ITGA3', 'HSPD1', 'SMOX', 'LXN', 'GPRC5A', 'PPP1R14A', 'PCSK1N', 'PMP22', 'DOK4', 'CDC123', 'DDX10', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'DHRS7', 'SH3BGRL3', 'CD24', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'GPX3', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'EIF3M', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'S100A2', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'CNFN', 'KANK1', 'S100A10', 'RAB10', 'KYNU', 'CRIM1', 'AKR1C2', 'SLC12A2', 'CAPG', 'SMIM14', 'EMC7', 'PCED1B', 'GSN', 'HOMER3', 'CXCL5', 'CCDC34', 'CCT3', 'NAMPT', 'TPPP3', 'AURKB', 'TM4SF4', 'PLAUR', 'LGMN', 'GPX2', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'FOSL1', 'NPC2', 'PHACTR2', 'UTP6', 'PPP1R15A', 'FSCN1', 'FGFBP1', 'INA', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'PLAU', 'PBDC1', 'CTSH', 'PRPS2', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'EFHD2', 'ALDH1A1', 'ITGB5', 'ZNF622', 'SLC4A7', 'PTRH2', 'SPP1', 'ZFP36L2', 'EPHA2', 'DDX39A', 'PTPRF', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'TOP2A', 'EIF4EBP1', 'RAP2B', 'EVA1C', 'ALDH2', 'RPS27', 'AGR2', 'PPID', 'ASF1A', 'S100A3', 'LDHB', 'PUS1', 'CDC25B', 'RAD51C', 'LBH', 'ARHGAP29', 'ACTB', 'RAI14', 'CTNNAL1', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'ALG8', 'MAP1B', 'TOB1', 'NRP2', 'SDHB', 'LACTB2', 'TOR1AIP2', 'INSIG1', 'NUPR1', 'TMPO', 'NDUFA12', 'PLK1', 'CDC42EP1', 'ZFP36L1', 'C1orf56', 'PRSS23', 'DNMBP', 'HSPE1', 'CTTN', 'B2M', 'RRS1', 'ACAT2', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'RIPK2', 'ACAT1', 'NOC3L', 'TIMP2', 'LGALS1', 'MNS1', 'SLC16A3', 'PA2G4', 'PIR', 'CD68', 'CYP1B1', 'COX7B', 'LRRC75A', 'SLC27A2', 'TXN', 'TESC', 'CYBA', 'GINS2', 'AURKA', 'CD70', 'ZFP36', 'REEP4', 'CD9', 'ATP1B3', 'MMD', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'DCBLD2', 'PSMA3', 'CTSB', 'RAP1GAP', 'CYB5B', 'SPATS2', 'HES4', 'RMI2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'STK17A', 'ANKRD1', 'NANS', 'TAGLN2', 'ANKRD40', 'FA2H', 'SNRPF', 'RRM2', 'SERPINE2', 'SLC20A1', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'SAT1', 'NUF2', 'INO80C', 'TGFBI', 'SLC35F6', 'DNAJC3', 'IMMP2L', 'RPL28', 'PDLIM5', 'GCLC', 'RHOD', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'ACTG1', 'RPS12', 'ISG20', 'VAMP8', 'NEAT1', 'CTSL', 'CDCA3', 'BASP1', 'SULT2B1', 'TEAD4', 'OAS1', 'DPM1', 'CCNB1', 'GTPBP4', 'RPL21', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'SLC7A5', 'RILP', 'CA12', 'INHBB', 'METRN', 'MUC5AC', 'ODC1', 'CAV1', 'CRIP1', 'PDXK', 'PCDH9', 'PPA2', 'RPL38', 'MT2A', 'HMGCS1', 'RPS24', 'SMC1A', 'S100A4', 'INSL4', 'GADD45B', 'PHLDA2', 'PRAME', 'SLC26A2', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'ATP1B1', 'KRT81', 'HMGB2', 'MYL6', 'CHORDC1', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'LAPTM4A', 'SET', 'GLRX3', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AVPI1', 'AKR1B1', 'NCL', 'ADA', 'CCL2', 'AXL', 'PCNA', 'AMIGO2', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'COX7C', 'PIF1', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'TUBA1C', 'GSTO1', 'CCNB2', 'IGFBP4', 'CENPF', 'HNRNPH1', 'OSGIN1', 'ABCG2', 'RPL31', 'CRIP2', 'BIRC5', 'NUCKS1', 'PMEPA1', 'GNG11', 'UPK1B', 'CNIH4', 'TALDO1', 'STC2', 'SLC3A2', 'CACNG6', 'MTHFD2', 'CACYBP', 'MKI67', 'NNMT', 'CCDC80', 'ELF3', 'ATF4', 'PTP4A1', 'OSGIN2', 'HMGA1', 'HPCAL1', 'PRSS3', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'UCP2', 'HSPA1A', 'HACD3', 'TK1', 'PPP3CA', 'FHL2', 'IGFBP3', 'HMGB3', 'CDC20', 'INPP1', 'KLF6', 'KRT18', 'MUC3A', 'ORMDL2', 'ECH1', 'MYL12A', 'S100A11', 'FEN1', 'TUBA1B', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP'], ['IBA'], ['IDA', 'ISS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IMP', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'NAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IMP', 'ISO', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IDA'], ['ISS'], ['IDA'], ['IDA'], ['IMP', 'IBA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IMP'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IMP'], ['TAS'], ['IDA'], ['IMP'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IMP'], ['IDA', 'IBA'], ['IEA'], ['TAS', 'IEA']]</t>
+          <t>[['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'TAS'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IMP', 'TAS', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'NAS'], ['IPI', 'HDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['TAS'], ['IPI', 'HDA', 'ISS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['HDA', 'IBA', 'RCA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IC', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IC', 'IEA'], ['IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['ISS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'NAS'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IMP', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'TAS', 'IEA'], ['IPI'], ['IPI', 'TAS', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEP', 'ISS', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'RCA', 'NAS', 'IEA'], ['IPI'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'TAS', 'NAS', 'IEA'], ['IPI', 'IMP', 'IBA', 'IEA'], ['EXP', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'IGI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IMP', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'ISS', 'IEA'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IPI', 'NAS'], ['EXP', 'IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'RCA', 'IEA'], ['IDA', 'IPI', 'RCA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'TAS'], ['IBA'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'TAS', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'IMP', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IGI', 'IBA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IBA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IPI', 'ISA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'ND', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI', 'IMP', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IMP', 'IBA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'RCA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'NAS'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IC', 'IEA'], ['IPI', 'HDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['EXP', 'IPI', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['EXP', 'IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'NAS'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IGI', 'HDA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IBA'], ['EXP', 'IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['NAS'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP'], ['IDA', 'IPI', 'HDA', 'NAS', 'IEA'], ['IPI', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.004906432509758105</v>
+        <v>0.002326066256702582</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -3768,22 +3768,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H16" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I16" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J16" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4218455743879473</v>
+        <v>0.424812030075188</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2568807339449541</v>
+        <v>0.2588774341351661</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3797,59 +3797,59 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>['ACTG1', 'RBM8A', 'CYB5B', 'CKS2', 'DKC1', 'TOP2A', 'EMC7', 'MAP1B', 'DDX21', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'MZT1', 'ATP1B1', 'LGALS1', 'EIF3E', 'PSMA4', 'UTP18', 'ID2', 'CCNA2', 'PSMC1', 'SMC1A', 'SERPINE1', 'EPHA2', 'RRM2', 'NDUFA9', 'EIF3M', 'INSIG1', 'UBE2S', 'TOB1', 'RPS27', 'NUPR1', 'CCNB2', 'JADE1', 'SLC3A2', 'PSMC2', 'NOL7', 'HLA-A', 'SKIL', 'ITGB5', 'NOL11', 'KPNA2', 'RMI2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'RPL21', 'DCAF13', 'ENO1', 'CAV2', 'ASF1A', 'ORC5', 'HMGB2', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'B4GALT1', 'FOSL1', 'ACTB', 'NPM1', 'AHNAK', 'TIMP1', 'MYL12B', 'PSMD7', 'PDLIM7', 'SNRPF', 'CTTN', 'PDLIM5', 'UQCRQ', 'VAMP8', 'SRP54', 'ANKRD1', 'MYBL2', 'CAPZA1', 'ZNF622', 'CBX6', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'RPL31', 'RAB10', 'KIF23', 'RPS18', 'CDKN2D', 'INO80C', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'CCT4', 'ITGA3', 'NDUFC2', 'PDHB', 'DYNLL1', 'EEF1A1', 'RPS12', 'CCNB1', 'RIPK2', 'HSP90AB1', 'PLK1', 'ITGB1', 'ARL6IP1', 'AXL', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'HSPA8', 'EIF2S3', 'RAD21', 'SUCLG1', 'FOS', 'AIMP2', 'RPL37A', 'KRT8', 'CEBPB', 'CTNNB1', 'EBNA1BP2', 'SSB', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'GINS2', 'TUBB', 'CENPF', 'TEAD4', 'ATP1B3', 'GLRX3', 'FN1', 'ZFP36', 'COX7B', 'CDK1', 'FEN1', 'AURKA', 'RPL41', 'CD44', 'CACNG6', 'PSMD14', 'NAA15', 'NUP37', 'NUF2', 'PPP1R15A', 'ARHGAP29', 'UQCRC2', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'PCNA', 'GABRA5', 'ZFP36L1', 'PPP3CA', 'PLAUR', 'PRPS2', 'RPL38', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'CCT5', 'PRAME', 'CENPA', 'SLBP', 'HNRNPH1', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'HMGA1', 'GIGYF1', 'LMO7', 'BCL2L1', 'IMMP2L', 'ORMDL2', 'CKS1B', 'CCT8', 'HSP90B1', 'AP1S2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'HSP90AA1', 'LDHA', 'RPL28', 'GNG11', 'EIF3D', 'RAD51C', 'PYCARD', 'MYL12A', 'UTP6', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'RPS29', 'NRP2', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'PSMA3', 'LDHB', 'CLU', 'BIRC5', 'IGFBP6', 'ZFP36L2', 'S100A10', 'B2M', 'GCLC', 'MRPS22', 'RPS24', 'KCNMA1', 'CDC42']</t>
+          <t>['BIRC3', 'DKC1', 'CALM2', 'XRCC5', 'MYL12B', 'CHP1', 'CD44', 'LMO7', 'AIMP2', 'VDAC3', 'CCT7', 'NDUFC2', 'SUCLG1', 'CDC42', 'CCT4', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EIF2S3', 'ANXA2', 'ARL6IP1', 'UTP18', 'COL5A2', 'EIF3D', 'CKS2', 'CTNNBL1', 'SKIL', 'KCNMA1', 'JADE1', 'MZT1', 'FOS', 'RPL39', 'IGFBP6', 'RPL41', 'CKS1B', 'CAPN2', 'GIGYF1', 'NPM1', 'RBM8A', 'ITGA3', 'HSPD1', 'GPRC5A', 'PRMT1', 'EIF4A3', 'PDLIM7', 'PLRG1', 'CCND1', 'ID2', 'EEF1A1', 'TERF1', 'TIMP1', 'DDX21', 'EIF3M', 'UBE2C', 'CBX6', 'PPP1CB', 'S100A10', 'RAB10', 'CAPG', 'EMC7', 'CCT3', 'AURKB', 'PLAUR', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'FOSL1', 'UTP6', 'PPP1R15A', 'PSMC1', 'CCT2', 'DCAF13', 'PLAU', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'ITGB5', 'ZNF622', 'ZFP36L2', 'EPHA2', 'SSB', 'CAPZA1', 'TOP2A', 'RPS27', 'ASF1A', 'LDHB', 'RAD51C', 'LBH', 'ARHGAP29', 'ACTB', 'ORC5', 'LDHA', 'RPS29', 'PSMD7', 'MCM7', 'MAP1B', 'TOB1', 'NRP2', 'SDHB', 'INSIG1', 'NUPR1', 'NDUFA12', 'PLK1', 'ZFP36L1', 'CTTN', 'B2M', 'RRS1', 'KPNA2', 'RIPK2', 'UQCRQ', 'LGALS1', 'PA2G4', 'COX7B', 'LRRC75A', 'CYBA', 'GINS2', 'AURKA', 'ZFP36', 'CD9', 'ATP1B3', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'CYB5B', 'RMI2', 'ANKRD1', 'SNRPF', 'RRM2', 'CENPA', 'PYCARD', 'CCNA2', 'RPS18', 'SRP54', 'NUF2', 'INO80C', 'IMMP2L', 'RPL28', 'PDLIM5', 'GCLC', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'ACTG1', 'RPS12', 'VAMP8', 'NEAT1', 'BASP1', 'TEAD4', 'DPM1', 'CCNB1', 'RPL21', 'UQCRC2', 'KIF23', 'CLU', 'NOL11', 'SLC7A5', 'RILP', 'CAV1', 'RPL38', 'RPS24', 'SMC1A', 'PRAME', 'CCT8', 'HSPA5', 'DYNLL1', 'ATP1B1', 'HMGB2', 'MYL6', 'PSMA4', 'MSH6', 'EIF3E', 'NOL7', 'MYBL2', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'BCL2L1', 'SET', 'GLRX3', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'NCL', 'AXL', 'PCNA', 'HSP90AA1', 'HSP90AB1', 'COX7C', 'GABRA5', 'AP1S2', 'HSP90B1', 'CCNB2', 'CENPF', 'HNRNPH1', 'RPL31', 'BIRC5', 'GNG11', 'SLC3A2', 'CACNG6', 'CACYBP', 'ATF4', 'HMGA1', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'HSPA1A', 'PPP3CA', 'IGFBP3', 'CDC20', 'ORMDL2', 'MYL12A', 'FEN1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[['IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'ISS', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IGI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['ISS'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI'], ['IBA'], ['IPI', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA'], ['IPI'], ['IPI'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IC'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IPI'], ['IDA', 'HDA', 'IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IPI'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'IPI', 'ISS', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA'], ['IDA'], ['IPI'], ['IDA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'IBA', 'NAS'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA'], ['EXP', 'IPI', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'ISS', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IMP', 'NAS', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'IEA'], ['IBA'], ['IPI', 'IEA'], ['IDA'], ['EXP', 'IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IBA'], ['ISS', 'TAS'], ['IDA'], ['NAS'], ['IDA', 'IPI', 'IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI', 'ISS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IPI'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['NAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'ISS'], ['IDA'], ['IPI'], ['IMP'], ['IEA'], ['EXP', 'IDA', 'IPI', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP']]</t>
+          <t>[['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['NAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IPI', 'IBA', 'NAS'], ['IDA', 'IMP'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA'], ['IDA', 'IPI', 'IBA'], ['EXP', 'IDA', 'IPI', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IBA'], ['IPI'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['ISS'], ['TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['EXP', 'IDA', 'IPI', 'IEA'], ['ISS'], ['TAS'], ['IDA', 'IPI', 'ISS', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'NAS'], ['IPI'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI'], ['IBA', 'NAS'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IBA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IPI', 'ISS'], ['IDA', 'IBA'], ['IDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'NAS'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['NAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IPI'], ['IDA', 'IMP'], ['IBA', 'IEA'], ['IPI'], ['IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IPI', 'ISS', 'IBA'], ['IBA'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IEA'], ['IEA'], ['EXP', 'IPI', 'NAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI'], ['IDA'], ['IPI'], ['IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IPI'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'ISO', 'IBA', 'NAS', 'IEA'], ['ISS', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IC'], ['IDA', 'IPI', 'IBA', 'NAS'], ['IBA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO:MF</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GO:0045296</t>
+          <t>GO:0008150</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cadherin binding</t>
+          <t>biological_process</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.007966019594229165</v>
+        <v>0.00397214054444167</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>"Binding to cadherin, a type I membrane protein involved in cell adhesion." [GOC:bf]</t>
+          <t>"A biological process is the execution of a genetically-encoded biological module or program. It consists of all the steps required to achieve the specific biological objective of the module. A biological process is accomplished by a particular set of molecular functions carried out by specific gene products (or macromolecular complexes), often in a highly regulated manner and in a particular temporal sequence." [GOC:pdt]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>83</v>
+        <v>2414</v>
       </c>
       <c r="H17" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I17" t="n">
-        <v>37</v>
+        <v>509</v>
       </c>
       <c r="J17" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0696798493408663</v>
+        <v>0.956766917293233</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4457831325301205</v>
+        <v>0.2108533554266777</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3858,64 +3858,64 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>['GO:0050839']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['PKM', 'S100A11', 'EIF3E', 'EPHA2', 'CCNB2', 'SLC3A2', 'KRT18', 'TAGLN2', 'YWHAE', 'ENO1', 'AHNAK', 'CTTN', 'PDLIM5', 'CAPZA1', 'RAB10', 'ANXA1', 'NDRG1', 'TMPO', 'FSCN1', 'HSP90AB1', 'ITGB1', 'HSPA1A', 'HSPA8', 'EIF2S3', 'CTNNB1', 'GPRC5A', 'ANXA2', 'HSPA5', 'RAN', 'CDC42EP1', 'CCT8', 'CAPG', 'LDHA', 'EFHD2', 'SFN', 'CTNNAL1', 'PRDX1']</t>
+          <t>['ALDH3A1', 'BIRC3', 'DKC1', 'NFKBIE', 'TNFRSF12A', 'CALM2', 'XRCC5', 'MYL12B', 'TRAM1', 'CHP1', 'PAQR5', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'GAL', 'FKBP11', 'TM4SF1', 'TUBA1A', 'TP53I3', 'LMO7', 'AIMP2', 'VDAC3', 'CCT7', 'ID3', 'DEPDC1B', 'RAB3B', 'ATXN10', 'UNC50', 'LOXL2', 'NDUFC2', 'SUCLG1', 'NDRG1', 'CDC42', 'MDK', 'CCT4', 'HMMR', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EIF2S3', 'EREG', 'ANXA2', 'LMNA', 'RSPO3', 'ARL6IP1', 'TNRC6B', 'UTP18', 'SFN', 'EIF1AY', 'COL5A2', 'EIF3D', 'PLK2', 'NTS', 'GLRX', 'AKR1C3', 'CKS2', 'CA8', 'CTNNBL1', 'AKAP12', 'ANXA1', 'EMP3', 'SKIL', 'MALAT1', 'TUBA4A', 'NPTX1', 'MFSD12', 'DUSP5', 'SFRP1', 'DHRS3', 'KCNMA1', 'RND3', 'HMOX1', 'JADE1', 'MZT1', 'ASPM', 'FAM64A', 'ANP32A', 'FOS', 'GAL3ST1', 'RPL39', 'F12', 'NRDC', 'YARS', 'FSTL3', 'IGFBP6', 'RPL41', 'MAP1LC3B', 'CXCL3', 'MARCKSL1', 'CKS1B', 'S100A6', 'MESP1', 'CAPN2', 'GIGYF1', 'NPM1', 'TMSB10', 'RBM8A', 'REXO2', 'DUSP1', 'REEP5', 'MGLL', 'PHGDH', 'ANTXR1', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'ITGA3', 'HSPD1', 'ZFAS1', 'SMOX', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'PCSK1N', 'PMP22', 'DOK4', 'CDC123', 'DDX10', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'DHRS7', 'SH3BGRL3', 'CD24', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'GPX3', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'EIF3M', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'S100A2', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'CNFN', 'KANK1', 'S100A10', 'RAB10', 'KYNU', 'CRIM1', 'AKR1C2', 'SLC12A2', 'CAPG', 'SMIM14', 'EMC7', 'GSN', 'HOMER3', 'CXCL5', 'CCDC34', 'CCT3', 'NAMPT', 'TPPP3', 'AURKB', 'TM4SF4', 'PLAUR', 'LGMN', 'GPX2', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'FOSL1', 'NPC2', 'PHACTR2', 'UTP6', 'PPP1R15A', 'FSCN1', 'FGFBP1', 'INA', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'PLAU', 'CTSH', 'PRPS2', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'ALDH1A1', 'ITGB5', 'ZNF622', 'SLC4A7', 'PTRH2', 'SPP1', 'ZFP36L2', 'EPHA2', 'DDX39A', 'PTPRF', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'TOP2A', 'EIF4EBP1', 'RAP2B', 'ALDH2', 'RPS27', 'AGR2', 'PPID', 'ASF1A', 'LDHB', 'PUS1', 'CDC25B', 'RAD51C', 'LBH', 'ARHGAP29', 'ACTB', 'RAI14', 'CTNNAL1', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'ALG8', 'MAP1B', 'TOB1', 'NRP2', 'SDHB', 'TOR1AIP2', 'INSIG1', 'NUPR1', 'NDUFA12', 'PLK1', 'CDC42EP1', 'ZFP36L1', 'C1orf56', 'PRSS23', 'DNMBP', 'HSPE1', 'CTTN', 'B2M', 'RRS1', 'ACAT2', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'RIPK2', 'ACAT1', 'NOC3L', 'TIMP2', 'UQCRQ', 'LGALS1', 'MNS1', 'SLC16A3', 'PA2G4', 'PIR', 'CD68', 'CYP1B1', 'COX7B', 'LRRC75A', 'SLC27A2', 'TXN', 'TESC', 'CYBA', 'GINS2', 'AURKA', 'CD70', 'ZFP36', 'REEP4', 'CD9', 'ATP1B3', 'MMD', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'DCBLD2', 'PSMA3', 'CTSB', 'RAP1GAP', 'CYB5B', 'HES4', 'RMI2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'STK17A', 'ANKRD1', 'NANS', 'TAGLN2', 'ANKRD40', 'FA2H', 'SNRPF', 'RRM2', 'SERPINE2', 'SLC20A1', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'SAT1', 'NUF2', 'INO80C', 'TGFBI', 'SLC35F6', 'DNAJC3', 'IMMP2L', 'RPL28', 'PDLIM5', 'GCLC', 'RHOD', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'ACTG1', 'RPS12', 'ISG20', 'VAMP8', 'NEAT1', 'CTSL', 'CDCA3', 'BASP1', 'SULT2B1', 'TEAD4', 'OAS1', 'DPM1', 'CCNB1', 'GTPBP4', 'RPL21', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'SLC7A5', 'RILP', 'CA12', 'INHBB', 'METRN', 'ODC1', 'CAV1', 'CRIP1', 'PDXK', 'PCDH9', 'PPA2', 'RPL38', 'MT2A', 'HMGCS1', 'RPS24', 'SMC1A', 'S100A4', 'INSL4', 'GADD45B', 'PHLDA2', 'PRAME', 'SLC26A2', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'ATP1B1', 'KRT81', 'HMGB2', 'MYL6', 'CHORDC1', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'SET', 'GLRX3', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AVPI1', 'AKR1B1', 'NCL', 'ADA', 'CCL2', 'AXL', 'PCNA', 'AMIGO2', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'COX7C', 'PIF1', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'TUBA1C', 'GSTO1', 'CCNB2', 'IGFBP4', 'CENPF', 'HNRNPH1', 'OSGIN1', 'ABCG2', 'RPL31', 'CRIP2', 'BIRC5', 'NUCKS1', 'PMEPA1', 'GNG11', 'UPK1B', 'CNIH4', 'TALDO1', 'STC2', 'SLC3A2', 'CACNG6', 'MTHFD2', 'CACYBP', 'MKI67', 'NNMT', 'CCDC80', 'ELF3', 'ATF4', 'PTP4A1', 'OSGIN2', 'HMGA1', 'HPCAL1', 'PRSS3', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'UCP2', 'HSPA1A', 'HACD3', 'TK1', 'PPP3CA', 'FHL2', 'IGFBP3', 'HMGB3', 'CDC20', 'INPP1', 'KLF6', 'KRT18', 'ORMDL2', 'ECH1', 'MYL12A', 'S100A11', 'FEN1', 'TUBA1B', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'NAS', 'IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['ISS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IEA'], ['IMP'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'HMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HEP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'NAS'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IMP', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IC', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IBA'], ['ND'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['HMP', 'IBA'], ['NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'NAS', 'IC'], ['IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IEP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IPI', 'IEP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'IC', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HEP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['NAS'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IGI', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IC'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['HMP'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['NAS', 'IC', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GO:0006278</t>
+          <t>GO:0043227</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RNA-templated DNA biosynthetic process</t>
+          <t>membrane-bounded organelle</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.009707115335170343</v>
+        <v>0.006619966935758699</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>"A DNA biosynthetic process that uses RNA as a template for RNA-dependent DNA polymerases (e.g. reverse transcriptase) that synthesize the new strand." [GOC:mah, ISBN:0198506732]</t>
+          <t>"Organized structure of distinctive morphology and function, bounded by a single or double lipid bilayer membrane. Includes the nucleus, mitochondria, plastids, vacuoles, and vesicles. Excludes the plasma membrane." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>2007</v>
       </c>
       <c r="H18" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>443</v>
       </c>
       <c r="J18" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02448210922787194</v>
+        <v>0.8327067669172933</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8125</v>
+        <v>0.2207274539113104</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3924,64 +3924,64 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>['GO:0071897']</t>
+          <t>['GO:0043226']</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['DKC1', 'TERF1', 'PIF1', 'XRCC5', 'CCT7', 'CCT3', 'CCT4', 'HSP90AB1', 'CTNNB1', 'CCT2', 'CCT5', 'CCT8', 'HSP90AA1']</t>
+          <t>['ALDH3A1', 'BIRC3', 'DKC1', 'NFKBIE', 'CALM2', 'XRCC5', 'MYL12B', 'TRAM1', 'CHP1', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'RARRES1', 'TKT', 'GCNT3', 'GAL', 'FKBP11', 'TUBA1A', 'LMO7', 'AIMP2', 'MORC4', 'VDAC3', 'CCT7', 'ID3', 'RAB3B', 'ATXN10', 'UNC50', 'LOXL2', 'NDUFC2', 'SUCLG1', 'NDRG1', 'CDC42', 'CCT4', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EIF2S3', 'EREG', 'ANXA2', 'LMNA', 'ARL6IP1', 'TNRC6B', 'UTP18', 'SFN', 'COL5A2', 'PLK2', 'NTS', 'GLRX', 'AKR1C3', 'CTNNBL1', 'ANXA1', 'SKIL', 'TUBA4A', 'NPTX1', 'MFSD12', 'DUSP5', 'SFRP1', 'DHRS3', 'RND3', 'HMOX1', 'JADE1', 'ASPM', 'FAM64A', 'ANP32A', 'FOS', 'GAL3ST1', 'RPL39', 'F12', 'NRDC', 'YARS', 'FSTL3', 'RPL41', 'MAP1LC3B', 'MARCKSL1', 'CKS1B', 'S100A6', 'MESP1', 'TMEM92', 'CAPN2', 'NPM1', 'RBM8A', 'REXO2', 'DUSP1', 'REEP5', 'MGLL', 'PHGDH', 'ANTXR1', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'ITGA3', 'HSPD1', 'ZFAS1', 'SMOX', 'GPRC5A', 'LY6K', 'PCSK1N', 'DDX10', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'DHRS7', 'SMIM6', 'SH3BGRL3', 'CD24', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'GPX3', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'KANK1', 'S100A10', 'RAB10', 'KYNU', 'SLC12A2', 'CAPG', 'SMIM14', 'EMC7', 'GSN', 'CCDC34', 'CCT3', 'NAMPT', 'AURKB', 'PLAUR', 'LGMN', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'FOSL1', 'NPC2', 'PHACTR2', 'UTP6', 'PPP1R15A', 'FSCN1', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'PLAU', 'CTSH', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'ALDH1A1', 'ITGB5', 'ZNF622', 'PTRH2', 'SPP1', 'ZFP36L2', 'DDX39A', 'PTPRF', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'TOP2A', 'EIF4EBP1', 'RAP2B', 'ALDH2', 'RPS27', 'AGR2', 'PPID', 'ASF1A', 'S100A3', 'LDHB', 'PUS1', 'CDC25B', 'RAD51C', 'LBH', 'ACTB', 'RAI14', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'ALG8', 'MAP1B', 'TOB1', 'SDHB', 'LACTB2', 'TOR1AIP2', 'INSIG1', 'NUPR1', 'TMPO', 'NDUFA12', 'PLK1', 'ZFP36L1', 'PRSS23', 'DNMBP', 'HSPE1', 'CTTN', 'B2M', 'RRS1', 'ACAT2', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'RIPK2', 'ACAT1', 'NOC3L', 'TIMP2', 'UQCRQ', 'LGALS1', 'MNS1', 'SLC16A3', 'PA2G4', 'PIR', 'CD68', 'CYP1B1', 'COX7B', 'SLC27A2', 'TXN', 'TESC', 'CYBA', 'GINS2', 'AURKA', 'CD70', 'ZFP36', 'REEP4', 'CD9', 'ATP1B3', 'MMD', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RAP1GAP', 'CYB5B', 'HES4', 'RMI2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'STK17A', 'ANKRD1', 'NANS', 'TAGLN2', 'FA2H', 'SNRPF', 'RRM2', 'SERPINE2', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'NUF2', 'INO80C', 'TGFBI', 'SLC35F6', 'DNAJC3', 'IMMP2L', 'RPL28', 'GCLC', 'RHOD', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'ACTG1', 'RPS12', 'ISG20', 'VAMP8', 'NEAT1', 'CTSL', 'BASP1', 'SULT2B1', 'TEAD4', 'OAS1', 'DPM1', 'CCNB1', 'GTPBP4', 'RPL21', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'SLC7A5', 'RILP', 'MUC5AC', 'CAV1', 'PDXK', 'PPA2', 'MT2A', 'GOLIM4', 'RPS24', 'SMC1A', 'S100A4', 'GADD45B', 'PRAME', 'SLC26A2', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'ATP1B1', 'HMGB2', 'MYL6', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'LAPTM4A', 'SET', 'GLRX3', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'AXL', 'PCNA', 'AMIGO2', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'COX7C', 'PIF1', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'TUBA1C', 'GSTO1', 'CCNB2', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'RPL31', 'BIRC5', 'NUCKS1', 'PMEPA1', 'UPK1B', 'CNIH4', 'TALDO1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'MKI67', 'ELF3', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'UCP2', 'HSPA1A', 'HACD3', 'TK1', 'PPP3CA', 'FHL2', 'IGFBP3', 'HMGB3', 'CDC20', 'KLF6', 'KRT18', 'MUC3A', 'ORMDL2', 'ECH1', 'MYL12A', 'S100A11', 'FEN1', 'TUBA1B', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IMP'], ['IDA'], ['ISS', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IDA', 'TAS']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HTP', 'TAS'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'IC', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['HDA'], ['TAS'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HTP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IC', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IBA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IEA']]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:MF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GO:0007004</t>
+          <t>GO:0019899</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>telomere maintenance via telomerase</t>
+          <t>enzyme binding</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.009707115335170343</v>
+        <v>0.007045072396085521</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>"The maintenance of proper telomeric length by the addition of telomeric repeats by telomerase." [GOC:elh]</t>
+          <t>"Binding to an enzyme, a protein with catalytic activity." [GOC:jl]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>370</v>
       </c>
       <c r="H19" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="J19" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02448210922787194</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8125</v>
+        <v>0.3027027027027027</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3990,64 +3990,64 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>['GO:0006278', 'GO:0010833']</t>
+          <t>['GO:0005515']</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['DKC1', 'TERF1', 'PIF1', 'XRCC5', 'CCT7', 'CCT3', 'CCT4', 'HSP90AB1', 'CTNNB1', 'CCT2', 'CCT5', 'CCT8', 'HSP90AA1']</t>
+          <t>['CALM2', 'XRCC5', 'CHP1', 'NDRG1', 'CDC42', 'LGALS3', 'ANXA2', 'SFN', 'CKS2', 'CTNNBL1', 'AKAP12', 'TUBA4A', 'RND3', 'HMOX1', 'MAP1LC3B', 'CKS1B', 'CAPN2', 'NPM1', 'DUSP1', 'ITGA3', 'HSPD1', 'PRMT1', 'CD24', 'TSPAN14', 'CCND1', 'UCHL1', 'EEF1A1', 'TMSB4X', 'TIMP1', 'UBE2C', 'BTG1', 'PPP1CB', 'TRIB3', 'SLC12A2', 'GSN', 'AURKB', 'PLAUR', 'TUBB', 'CAV2', 'NPC2', 'PPP1R15A', 'CCT2', 'CTNNB1', 'FN1', 'TOP2A', 'LDHB', 'CDC25B', 'ACTB', 'YWHAE', 'SGOL1', 'TOB1', 'TOR1AIP2', 'PLK1', 'CDC42EP1', 'KPNA2', 'RIPK2', 'ACAT1', 'TIMP2', 'PA2G4', 'SLC27A2', 'AURKA', 'ZFP36', 'ATP1B3', 'CDKN2D', 'CEBPB', 'HSPA8', 'PSMA3', 'RAP1GAP', 'SQSTM1', 'ANKRD1', 'PYCARD', 'CCNA2', 'DNAJC3', 'PDLIM5', 'SERPINE1', 'ACTG1', 'CCNB1', 'FBXO5', 'CLU', 'TPX2', 'RILP', 'CAV1', 'RIN2', 'HSPA5', 'ATP1B1', 'SLPI', 'MSH6', 'EGR1', 'HSPA2', 'ENO1', 'UBB', 'UBC', 'BCL2L1', 'GLRX3', 'COTL1', 'NCL', 'PCNA', 'HSP90AA1', 'HSP90AB1', 'CYB5A', 'HSP90B1', 'BIRC5', 'STC2', 'CACYBP', 'ATF4', 'HMGA1', 'ITGB1', 'CCND3', 'HSPA1A', 'HACD3', 'PPP3CA', 'TUBA1B']</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IMP'], ['IDA'], ['ISS', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IDA', 'TAS']]</t>
+          <t>[['IPI'], ['IPI'], ['ISS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IBA', 'IEA'], ['IBA'], ['IPI'], ['IPI'], ['IPI'], ['IBA'], ['ISS'], ['IPI', 'IBA'], ['IBA'], ['IEA'], ['IPI'], ['ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'NAS'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IBA', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['EXP', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IDA'], ['IDA'], ['IPI'], ['IPI'], ['IBA'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'ISS'], ['IPI'], ['IPI', 'IEA'], ['IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['ISS', 'IEA'], ['ISS'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IDA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'TAS'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IBA'], ['IBA'], ['IPI'], ['IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IDA'], ['IPI'], ['IDA'], ['IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IDA'], ['IDA', 'IPI'], ['IPI']]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:MF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GO:0043227</t>
+          <t>GO:0045296</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>membrane-bounded organelle</t>
+          <t>cadherin binding</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01119436063474374</v>
+        <v>0.00847065951593513</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, bounded by a single or double lipid bilayer membrane. Includes the nucleus, mitochondria, plastids, vacuoles, and vesicles. Excludes the plasma membrane." [GOC:go_curators]</t>
+          <t>"Binding to cadherin, a type I membrane protein involved in cell adhesion." [GOC:bf]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1994</v>
+        <v>83</v>
       </c>
       <c r="H20" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I20" t="n">
-        <v>439</v>
+        <v>37</v>
       </c>
       <c r="J20" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8267419962335216</v>
+        <v>0.06954887218045112</v>
       </c>
       <c r="L20" t="n">
-        <v>0.220160481444333</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -4056,64 +4056,64 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>['GO:0043226']</t>
+          <t>['GO:0050839']</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'GPX1', 'RBM8A', 'NUCKS1', 'GLRX', 'GSN', 'AKR1C3', 'TSFM', 'CYB5B', 'S100A3', 'DKC1', 'TOP2A', 'GAL', 'TMSB4X', 'FBXO5', 'EMC7', 'MAP1B', 'DDX21', 'NOC3L', 'EREG', 'MARCKSL1', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'DDIT4', 'TRIB3', 'ATP1B1', 'CNIH4', 'PKM', 'SQSTM1', 'DHRS7', 'S100A11', 'ARHGAP11A', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'DHRS3', 'UTP18', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'NANS', 'SMC1A', 'PRDX4', 'SERPINE1', 'TPX2', 'GAMT', 'RAP2B', 'ID3', 'PKMYT1', 'RRM2', 'NDUFA9', 'CYP1B1', 'PRSS3', 'INSIG1', 'UBE2S', 'TOB1', 'RARRES1', 'GOLIM4', 'TK1', 'NRDC', 'TOR1AIP2', 'CD55', 'RPS27', 'NUPR1', 'CCNB2', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'KANK1', 'UNC50', 'PSMC2', 'SGOL1', 'CTSL', 'CYB5A', 'PGD', 'NOL7', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'IGFBP4', 'DUSP1', 'ITGB5', 'AKR1B10', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'RPL21', 'YWHAE', 'LGMN', 'S100A6', 'ALDH1A1', 'DCAF13', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'CAV2', 'ASF1A', 'BLVRB', 'TRAM1', 'CALB2', 'ZFAS1', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SULT2B1', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'MMD', 'B4GALT1', 'FOSL1', 'NEAT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'MT2A', 'ACAT1', 'NPTX1', 'SERPINB1', 'RAI14', 'PIF1', 'CCDC34', 'PDLIM7', 'MGLL', 'SNRPF', 'CTTN', 'CES1', 'UQCRQ', 'LAPTM4A', 'TNRC6B', 'GSTO1', 'VAMP8', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'ZNF622', 'CBX6', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOXB8', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'MORC4', 'ANXA4', 'KIF23', 'PTPRS', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'NDRG1', 'IRF2BP2', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'ITGA3', 'REEP5', 'NDUFC2', 'PDHB', 'DYNLL1', 'LITAF', 'HMGB3', 'BTG1', 'TALDO1', 'EEF1A1', 'MESP1', 'HACD3', 'MAP1LC3B', 'RPS12', 'SMIM14', 'TMPO', 'FSCN1', 'CCNB1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ITGB1', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CDCA5', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'EIF2S3', 'PMEPA1', 'RAD21', 'CD68', 'SUCLG1', 'UPK1B', 'PRSS23', 'SERPINE2', 'GADD45B', 'FOS', 'AIMP2', 'RPL37A', 'CSRP1', 'NUDT19', 'HMOX1', 'FKBP11', 'ALG8', 'KRT8', 'CEBPB', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'SSB', 'CTSH', 'REEP4', 'ALDH3A1', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'GINS2', 'TUBB', 'CENPF', 'SLC12A2', 'SLC16A3', 'TEAD4', 'NOLC1', 'ATP1B3', 'GLRX3', 'FN1', 'DUSP5', 'ZFP36', 'ANP32A', 'COX7B', 'CDK1', 'FEN1', 'DDX10', 'AURKA', 'RPL41', 'UQCR11', 'CD44', 'PSMD14', 'GAL3ST1', 'OAS1', 'LY6K', 'REXO2', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'PHACTR2', 'UQCRC2', 'PTPRF', 'NQO1', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'PCNA', 'ANTXR1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'APOBEC3C', 'PLAUR', 'DNMBP', 'RND3', 'MKI67', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'GPX3', 'LMO7', 'CD70', 'BCL2L1', 'STC2', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'MUC3A', 'IMMP2L', 'NAMPT', 'ORMDL2', 'CKS1B', 'CCT8', 'HSP90B1', 'HES4', 'MFSD12', 'F12', 'AP1S2', 'AMIGO2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'GCNT3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'HSPE1', 'RPL28', 'RAD51C', 'MNS1', 'PYCARD', 'SFN', 'ASPM', 'MYL12A', 'ELF3', 'STMN1', 'PHGDH', 'UCHL1', 'TUBA1C', 'UTP6', 'ADA', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'PTTG1', 'RAP1GAP', 'TESC', 'STK17A', 'AHNAK2', 'PPA2', 'RPS29', 'VIM', 'FA2H', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'CD24', 'DDX39A', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'ZFP36L2', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'GCLC', 'MRPS22', 'ATXN10', 'PRDX1', 'PLK2', 'PIR', 'RPS24', 'CDC42', 'UHRF1']</t>
+          <t>['NDRG1', 'AHNAK', 'EIF2S3', 'ANXA2', 'SFN', 'ANXA1', 'GPRC5A', 'PKM', 'RAB10', 'CAPG', 'RAN', 'FSCN1', 'CTNNB1', 'EFHD2', 'EPHA2', 'CAPZA1', 'CTNNAL1', 'LDHA', 'YWHAE', 'TMPO', 'CDC42EP1', 'CTTN', 'HSPA8', 'TAGLN2', 'PDLIM5', 'CCT8', 'HSPA5', 'PRDX1', 'EIF3E', 'ENO1', 'HSP90AB1', 'CCNB2', 'SLC3A2', 'ITGB1', 'HSPA1A', 'KRT18', 'S100A11']</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['ISS', 'IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IMP', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'NAS'], ['IDA', 'HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HTP', 'TAS'], ['HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA']]</t>
+          <t>[['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GO:0005622</t>
+          <t>GO:0006259</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>intracellular anatomical structure</t>
+          <t>DNA metabolic process</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01282105551677953</v>
+        <v>0.009602095942930133</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>"A component of a cell contained within (but not including) the plasma membrane. In eukaryotes it includes the nucleus and cytoplasm." [ISBN:0198506732]</t>
+          <t>"Any cellular metabolic process involving deoxyribonucleic acid. This is one of the two main types of nucleic acid, consisting of a long, unbranched macromolecule formed from one, or more commonly, two, strands of linked deoxyribonucleotides." [ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2196</v>
+        <v>168</v>
       </c>
       <c r="H21" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I21" t="n">
-        <v>473</v>
+        <v>61</v>
       </c>
       <c r="J21" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8907721280602636</v>
+        <v>0.1146616541353383</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2153916211293261</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -4122,64 +4122,64 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0090304']</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'TMSB10', 'GPX1', 'RBM8A', 'NUCKS1', 'GLRX', 'GSN', 'AKR1C3', 'TSFM', 'CA8', 'CYB5B', 'S100A3', 'DKC1', 'TOP2A', 'GAL', 'TMSB4X', 'FBXO5', 'EMC7', 'MAP1B', 'DDX21', 'NOC3L', 'EREG', 'MARCKSL1', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'DDIT4', 'TRIB3', 'MZT1', 'CNIH4', 'PHLDA2', 'PKM', 'SQSTM1', 'DHRS7', 'S100A11', 'ARHGAP11A', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'DHRS3', 'UTP18', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'NANS', 'SMC1A', 'PRDX4', 'CDCA3', 'SERPINE1', 'TUBA1B', 'TPX2', 'GAMT', 'RAP2B', 'ID3', 'PKMYT1', 'RRM2', 'NDUFA9', 'EIF3M', 'CYP1B1', 'PRSS3', 'AKAP12', 'INSIG1', 'UBE2S', 'TOB1', 'GOLIM4', 'TK1', 'NRDC', 'TOR1AIP2', 'CD55', 'RPS27', 'NUPR1', 'CCNB2', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'KANK1', 'UNC50', 'PSMC2', 'SGOL1', 'CTSL', 'CYB5A', 'PGD', 'NOL7', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'IGFBP4', 'DUSP1', 'TP53I3', 'ITGB5', 'AKR1B10', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'RPL21', 'YWHAE', 'CDC123', 'LGMN', 'S100A6', 'ALDH1A1', 'DCAF13', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'CAV2', 'ASF1A', 'BLVRB', 'TRAM1', 'CALB2', 'ODC1', 'ZFAS1', 'AKR1C2', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SULT2B1', 'LRRC75A', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'BIRC3', 'EIF1AY', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'MMD', 'B4GALT1', 'FOSL1', 'NEAT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'SAT1', 'AHNAK', 'TIMP1', 'MYL12B', 'PSMD7', 'MT2A', 'LXN', 'ACAT1', 'NPTX1', 'SERPINB1', 'RAI14', 'PIF1', 'HMGCS1', 'PDLIM7', 'MGLL', 'SNRPF', 'CTTN', 'CES1', 'PDLIM5', 'UQCRQ', 'LAPTM4A', 'TNRC6B', 'GSTO1', 'VAMP8', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'ZNF622', 'CBX6', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOMER3', 'HOXB8', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'MORC4', 'ANXA4', 'KIF23', 'PTPRS', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'NDRG1', 'IRF2BP2', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'ITGA3', 'REEP5', 'NDUFC2', 'PDHB', 'DYNLL1', 'LITAF', 'HMGB3', 'BTG1', 'TALDO1', 'EEF1A1', 'MESP1', 'HACD3', 'MAP1LC3B', 'RPS12', 'SMIM14', 'TMPO', 'FSCN1', 'CCNB1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ADM', 'ITGB1', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CDCA5', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'EIF2S3', 'PMEPA1', 'RAD21', 'CD68', 'SUCLG1', 'PRSS23', 'SERPINE2', 'INPP1', 'GADD45B', 'FOS', 'AIMP2', 'RPL37A', 'CSRP1', 'NUDT19', 'HMOX1', 'FKBP11', 'ALG8', 'KRT8', 'CEBPB', 'GPX2', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'SSB', 'INA', 'CTSH', 'REEP4', 'ALDH3A1', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'GINS2', 'TUBB', 'CENPF', 'INHBB', 'SLC12A2', 'SLC16A3', 'TEAD4', 'NOLC1', 'ATP1B3', 'KRT81', 'GLRX3', 'FN1', 'DUSP5', 'ZFP36', 'ANP32A', 'COX7B', 'CDK1', 'FEN1', 'DDX10', 'AURKA', 'RPL41', 'UQCR11', 'PPP1R14A', 'CD44', 'PSMD14', 'GAL3ST1', 'OAS1', 'LY6K', 'REXO2', 'TPPP3', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'ARHGAP29', 'PHACTR2', 'CRIP1', 'UQCRC2', 'PTPRF', 'NQO1', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'PCNA', 'ANTXR1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'APOBEC3C', 'PLAUR', 'PRPS2', 'DNMBP', 'RND3', 'MKI67', 'RPL38', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'GIGYF1', 'LMO7', 'BCL2L1', 'STC2', 'CDC42EP1', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'CRIP2', 'MUC3A', 'IMMP2L', 'NAMPT', 'ORMDL2', 'CKS1B', 'CCT8', 'HSP90B1', 'HES4', 'MFSD12', 'F12', 'AP1S2', 'AMIGO2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'GCNT3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'HSPE1', 'RPL28', 'SPATS2', 'EIF3D', 'RAD51C', 'MNS1', 'PYCARD', 'SFN', 'ASPM', 'MYL12A', 'ELF3', 'STMN1', 'PHGDH', 'UCHL1', 'TUBA1C', 'UTP6', 'ADA', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'CTNNAL1', 'PTTG1', 'RAP1GAP', 'TESC', 'STK17A', 'AHNAK2', 'PPA2', 'RPS29', 'VIM', 'DOK4', 'HMMR', 'CNFN', 'FA2H', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'CD24', 'DDX39A', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'ZFP36L2', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'GCLC', 'MRPS22', 'ATXN10', 'PRDX1', 'NNMT', 'PLK2', 'PIR', 'RPS24', 'CDC42', 'UHRF1']</t>
+          <t>['DKC1', 'XRCC5', 'CDCA5', 'CCT7', 'ID3', 'CCT4', 'EREG', 'LMNA', 'JADE1', 'NPM1', 'REXO2', 'HSPD1', 'PRMT1', 'UHRF1', 'TERF1', 'CCT3', 'AURKB', 'CCT5', 'RAN', 'CCT2', 'CTNNB1', 'TOP2A', 'ASF1A', 'RAD51C', 'ACTB', 'ORC5', 'MCM7', 'PLK1', 'KPNA2', 'NOC3L', 'GINS2', 'CDKN2D', 'RMI2', 'ANKRD1', 'CCNA2', 'APOBEC3C', 'INO80C', 'ISG20', 'GTPBP4', 'FBXO5', 'SMC1A', 'CCT8', 'DYNLL1', 'HMGB2', 'MSH6', 'PTTG1', 'PSMD14', 'SET', 'CDK1', 'PCNA', 'HSP90AA1', 'HSP90AB1', 'PIF1', 'CENPF', 'NUCKS1', 'HMGA1', 'RAD21', 'TK1', 'HMGB3', 'S100A11', 'FEN1']</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HTP', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['EXP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IC', 'IEA']]</t>
+          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA'], ['IMP', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IMP'], ['IDA'], ['IDA'], ['IEA'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['IMP', 'IEA'], ['TAS'], ['IMP'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'NAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IBA'], ['IBA', 'IEA'], ['IMP'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['IMP', 'IEA'], ['IBA'], ['IMP', 'ISO', 'IEA'], ['IDA', 'IBA'], ['IMP'], ['IMP'], ['TAS', 'IEA'], ['IMP'], ['IDA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS'], ['TAS'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GO:MF</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GO:0019899</t>
+          <t>GO:0007004</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>enzyme binding</t>
+          <t>telomere maintenance via telomerase</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01333123415102858</v>
+        <v>0.009983531492636749</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>"Binding to an enzyme, a protein with catalytic activity." [GOC:jl]</t>
+          <t>"The maintenance of proper telomeric length by the addition of telomeric repeats by telomerase." [GOC:elh]</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>379</v>
+        <v>16</v>
       </c>
       <c r="H22" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I22" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2128060263653484</v>
+        <v>0.02443609022556391</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2981530343007915</v>
+        <v>0.8125</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -4188,64 +4188,64 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>['GO:0005515']</t>
+          <t>['GO:0006278', 'GO:0010833']</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>['ACTG1', 'GSN', 'CKS2', 'TOP2A', 'TMSB4X', 'FBXO5', 'HSPA2', 'CCND3', 'TRIB3', 'ATP1B1', 'SQSTM1', 'COTL1', 'CCNA2', 'SERPINE1', 'TUBA1B', 'TPX2', 'AKAP12', 'TOB1', 'TOR1AIP2', 'UBB', 'SGOL1', 'CYB5A', 'DUSP1', 'KPNA2', 'CAV1', 'CACYBP', 'YWHAE', 'DNAJC3', 'TIMP2', 'ENO1', 'TUBA4A', 'CAV2', 'EGR1', 'LGALS3', 'UBE2C', 'UBC', 'ACTB', 'NPM1', 'TIMP1', 'ACAT1', 'PDLIM5', 'SLPI', 'ANKRD1', 'XRCC5', 'CDKN2D', 'NDRG1', 'CAPN2', 'PA2G4', 'CCND1', 'ITGA3', 'DYNLL1', 'BTG1', 'EEF1A1', 'HACD3', 'MAP1LC3B', 'CCNB1', 'RIPK2', 'HSP90AB1', 'PLK1', 'ITGB1', 'HSPA1A', 'HSPD1', 'TSPAN14', 'HSPA8', 'HMOX1', 'CEBPB', 'CTNNB1', 'CCT2', 'TUBB', 'SLC12A2', 'ATP1B3', 'GLRX3', 'FN1', 'ZFP36', 'AURKA', 'PPP1R15A', 'ANXA2', 'PCNA', 'PPP3CA', 'PLAUR', 'RND3', 'PPP1CB', 'HSPA5', 'NCL', 'HMGA1', 'BCL2L1', 'STC2', 'CDC42EP1', 'CKS1B', 'HSP90B1', 'RILP', 'ATF4', 'RHOD', 'HSP90AA1', 'PYCARD', 'SFN', 'UCHL1', 'CHP1', 'RAP1GAP', 'PRMT1', 'MSH6', 'AURKB', 'CTNNBL1', 'CD24', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'CLU', 'BIRC5', 'NPC2', 'SLC27A2', 'CDC42']</t>
+          <t>['DKC1', 'XRCC5', 'CCT7', 'CCT4', 'TERF1', 'CCT3', 'CCT5', 'CCT2', 'CTNNB1', 'CCT8', 'HSP90AA1', 'HSP90AB1', 'PIF1']</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>[['IPI', 'IBA'], ['IPI', 'IEA'], ['IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA'], ['IPI'], ['IBA'], ['IDA'], ['IPI'], ['ISS', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IPI', 'IEA'], ['ISS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IBA'], ['IPI', 'IBA'], ['IPI'], ['IBA', 'IEA'], ['IEA'], ['ISS'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IEA'], ['IPI', 'NAS'], ['IPI'], ['IDA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['ISS'], ['IEA'], ['EXP', 'IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IBA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA'], ['IBA'], ['IBA', 'IEA'], ['IDA'], ['IPI', 'IBA', 'TAS'], ['IPI'], ['IBA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IBA', 'IEA'], ['IPI'], ['ISS'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IEA'], ['IBA'], ['IDA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA']]</t>
+          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IMP', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS'], ['IMP', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GO:MF</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GO:0140662</t>
+          <t>GO:0006278</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ATP-dependent protein folding chaperone</t>
+          <t>RNA-templated DNA biosynthetic process</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.02619524248060973</v>
+        <v>0.009983531492636749</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>"Binding to a protein or a protein-containing complex to assist the protein folding process, driven by ATP hydrolysis." [PMID:27365453]</t>
+          <t>"A DNA biosynthetic process that uses RNA as a template for RNA-dependent DNA polymerases (e.g. reverse transcriptase) that synthesize the new strand." [GOC:mah, ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K23" t="n">
-        <v>0.02636534839924671</v>
+        <v>0.02443609022556391</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.8125</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -4254,64 +4254,64 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>['GO:0044183', 'GO:0140657']</t>
+          <t>['GO:0071897']</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>['HSPA2', 'CCT7', 'CCT3', 'CCT4', 'HSP90AB1', 'HSPA1A', 'HSPD1', 'HSPA8', 'CCT2', 'HSPA5', 'CCT5', 'CCT8', 'HSP90B1', 'HSP90AA1']</t>
+          <t>['DKC1', 'XRCC5', 'CCT7', 'CCT4', 'TERF1', 'CCT3', 'CCT5', 'CCT2', 'CTNNB1', 'CCT8', 'HSP90AA1', 'HSP90AB1', 'PIF1']</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA']]</t>
+          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IMP', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS'], ['IMP', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GO:0008150</t>
+          <t>GO:1990904</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>biological_process</t>
+          <t>ribonucleoprotein complex</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.03353565134380344</v>
+        <v>0.02166091446939803</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>"A biological process is the execution of a genetically-encoded biological module or program. It consists of all the steps required to achieve the specific biological objective of the module. A biological process is accomplished by a particular set of molecular functions carried out by specific gene products (or macromolecular complexes), often in a highly regulated manner and in a particular temporal sequence." [GOC:pdt]</t>
+          <t>"A macromolecular complex that contains both RNA and protein molecules." [GOC:krc, GOC:vesicles]</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2422</v>
+        <v>120</v>
       </c>
       <c r="H24" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I24" t="n">
-        <v>507</v>
+        <v>47</v>
       </c>
       <c r="J24" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9548022598870056</v>
+        <v>0.08834586466165413</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2093311312964492</v>
+        <v>0.3916666666666667</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -4320,64 +4320,64 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['GO:0032991']</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>['DEPDC1B', 'ACTG1', 'TMSB10', 'GPX1', 'RBM8A', 'NUCKS1', 'GLRX', 'GSN', 'AKR1C3', 'TSFM', 'CA8', 'TM4SF1', 'CYB5B', 'CKS2', 'DKC1', 'TOP2A', 'GAL', 'TMSB4X', 'FBXO5', 'EMC7', 'MAP1B', 'DDX21', 'NOC3L', 'EREG', 'MARCKSL1', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'DDIT4', 'TRIB3', 'MZT1', 'ATP1B1', 'CNIH4', 'PHLDA2', 'PKM', 'SQSTM1', 'DHRS7', 'S100A11', 'ARHGAP11A', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'DHRS3', 'UTP18', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'NANS', 'SMC1A', 'PRDX4', 'CDCA3', 'SERPINE1', 'TUBA1B', 'TPX2', 'EPHA2', 'GAMT', 'RAP2B', 'ID3', 'PKMYT1', 'RRM2', 'NDUFA9', 'EIF3M', 'CHORDC1', 'CYP1B1', 'PRSS3', 'AKAP12', 'INSIG1', 'UBE2S', 'TOB1', 'RARRES1', 'TK1', 'NRDC', 'TOR1AIP2', 'CD55', 'RPS27', 'NUPR1', 'OSGIN1', 'CCNB2', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'KANK1', 'UNC50', 'PSMC2', 'SGOL1', 'CTSL', 'CYB5A', 'PGD', 'NOL7', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'IGFBP4', 'DUSP1', 'TP53I3', 'ITGB5', 'AKR1B10', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'DCBLD2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'RPL21', 'YWHAE', 'CDC123', 'LGMN', 'CCDC80', 'S100A6', 'ALDH1A1', 'DCAF13', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'TUBA4A', 'CAV2', 'ASF1A', 'BLVRB', 'MDK', 'TRAM1', 'CALB2', 'ODC1', 'ZFAS1', 'AKR1C2', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SULT2B1', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'BIRC3', 'EIF1AY', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'MMD', 'B4GALT1', 'FOSL1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'SAT1', 'AHNAK', 'SLC26A2', 'TIMP1', 'MYL12B', 'PSMD7', 'MT2A', 'LXN', 'ACAT1', 'NPTX1', 'SERPINB1', 'RAI14', 'PIF1', 'CCDC34', 'HMGCS1', 'PDLIM7', 'MGLL', 'SNRPF', 'FGFBP1', 'CTTN', 'CES1', 'PDLIM5', 'UQCRQ', 'TNRC6B', 'GSTO1', 'VAMP8', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'ZNF622', 'CBX6', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOMER3', 'HOXB8', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'ANXA4', 'KIF23', 'PTPRS', 'ABCG2', 'RPS18', 'CDKN2D', 'PPID', 'INO80C', 'ANKRD40', 'NDRG1', 'IRF2BP2', 'CAPN2', 'PBDC1', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'ITGA3', 'EMP3', 'CRIM1', 'MALAT1', 'REEP5', 'NDUFC2', 'TMEM54', 'PDHB', 'DYNLL1', 'LITAF', 'HMGB3', 'BTG1', 'TALDO1', 'EEF1A1', 'MESP1', 'HACD3', 'MAP1LC3B', 'RPS12', 'SMIM14', 'PAQR5', 'FSCN1', 'CCNB1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ADM', 'METRN', 'ITGB1', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CDCA5', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'EIF2S3', 'OSGIN2', 'PMEPA1', 'RAD21', 'PCDH9', 'CD68', 'SUCLG1', 'UPK1B', 'PRSS23', 'SERPINE2', 'INPP1', 'GADD45B', 'FOS', 'AIMP2', 'RPL37A', 'CSRP1', 'NUDT19', 'HMOX1', 'FKBP11', 'ALG8', 'KRT8', 'CEBPB', 'GPX2', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'SSB', 'INA', 'CTSH', 'REEP4', 'ALDH3A1', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'GINS2', 'TUBB', 'CENPF', 'INHBB', 'SLC12A2', 'SLC16A3', 'TEAD4', 'NOLC1', 'ATP1B3', 'KRT81', 'GLRX3', 'FN1', 'DUSP5', 'ZFP36', 'ANP32A', 'COX7B', 'CDK1', 'FEN1', 'PMP22', 'DDX10', 'AURKA', 'RPL41', 'UQCR11', 'PPP1R14A', 'CD44', 'CCL2', 'CACNG6', 'PSMD14', 'GAL3ST1', 'OAS1', 'LY6K', 'REXO2', 'TPPP3', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'ARHGAP29', 'PHACTR2', 'CRIP1', 'UQCRC2', 'PTPRF', 'NQO1', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'PCNA', 'ANTXR1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'APOBEC3C', 'PLAUR', 'C1orf56', 'PRPS2', 'DNMBP', 'RND3', 'MKI67', 'RPL38', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'EVA1C', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'TNFRSF12A', 'HNRNPH1', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'GPX3', 'CXCL5', 'GIGYF1', 'LMO7', 'CD70', 'BCL2L1', 'STC2', 'CDC42EP1', 'SPP1', 'CD63', 'S100A4', 'S100A2', 'IGFBP7', 'UBR4', 'CRIP2', 'IMMP2L', 'NAMPT', 'ORMDL2', 'SLC20A1', 'CKS1B', 'CCT8', 'CA12', 'HSP90B1', 'TM4SF4', 'HES4', 'MFSD12', 'F12', 'AP1S2', 'AMIGO2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'GCNT3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'HSPE1', 'RPL28', 'GNG11', 'EIF3D', 'RAD51C', 'MNS1', 'PYCARD', 'SFN', 'ASPM', 'MYL12A', 'ELF3', 'STMN1', 'PHGDH', 'UCHL1', 'TUBA1C', 'UTP6', 'ADA', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'CTNNAL1', 'PTTG1', 'RAP1GAP', 'TESC', 'STK17A', 'AHNAK2', 'PPA2', 'RPS29', 'VIM', 'DOK4', 'NRP2', 'HMMR', 'CNFN', 'FA2H', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'RSPO3', 'CD24', 'AVPI1', 'DDX39A', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'IGFBP6', 'ISG20', 'S100A16', 'ZFP36L2', 'S100A10', 'ACAT2', 'CXCL3', 'NPC2', 'SLC27A2', 'B2M', 'GCLC', 'MRPS22', 'INSL4', 'ATXN10', 'PRDX1', 'NNMT', 'PLK2', 'PIR', 'RPS24', 'SLC4A7', 'KCNMA1', 'CDC42', 'UHRF1']</t>
+          <t>['DKC1', 'XRCC5', 'LGALS3', 'UTP18', 'EIF3D', 'CTNNBL1', 'RPL39', 'RPL41', 'NPM1', 'RBM8A', 'EIF4A3', 'PLRG1', 'EIF3M', 'UTP6', 'DCAF13', 'SLBP', 'ZNF622', 'ZFP36L2', 'SSB', 'TOP2A', 'RPS27', 'ACTB', 'RPS29', 'ZFP36L1', 'RRS1', 'PA2G4', 'ZFP36', 'HSPA8', 'SNRPF', 'RPS18', 'SRP54', 'RPL28', 'EBNA1BP2', 'RPS12', 'NEAT1', 'RPL21', 'RPL38', 'RPS24', 'EIF3E', 'NOL7', 'MRPS22', 'RPS28', 'NCL', 'HNRNPH1', 'RPL31', 'HSPA1A', 'RPL37A']</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[['IMP', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ND', 'IEA'], ['IDA', 'ISS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'ND', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ND', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'NAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IBA', 'NAS', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IBA', 'NAS'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IC', 'IEA'], ['IDA', 'IGI', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['ND'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ND'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IMP', 'TAS', 'IEA'], ['IEA'], ['ISS', 'ND'], ['IMP', 'NAS', 'IEA'], ['ND'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HEP', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'NAS', 'IC', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['NAS', 'IC', 'IEA'], ['HMP', 'IBA', 'IEA'], ['ISS', 'TAS', 'ND', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['HEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IEP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['IDA', 'IEP', 'IBA', 'TAS'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'HMP', 'IBA', 'IEA'], ['ND'], ['IDA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'ND', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'HMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['HMP'], ['IDA', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IGI', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'IEA'], ['IGI', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['NAS', 'ND'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'NAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GO:0010833</t>
+          <t>GO:0005622</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>telomere maintenance via telomere lengthening</t>
+          <t>intracellular anatomical structure</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.03384678944996753</v>
+        <v>0.02569065217551905</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>"Any process that contributes to the maintenance of proper telomeric length and structure by affecting and monitoring the activity of telomeric proteins and lengthening the telomeric DNA." [GOC:dph, GOC:tb]</t>
+          <t>"A component of a cell contained within (but not including) the plasma membrane. In eukaryotes it includes the nucleus and cytoplasm." [ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>2202</v>
       </c>
       <c r="H25" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>474</v>
       </c>
       <c r="J25" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02448210922787194</v>
+        <v>0.8909774436090225</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.215258855585831</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -4386,17 +4386,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>['GO:0000723']</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>['DKC1', 'TERF1', 'PIF1', 'XRCC5', 'CCT7', 'CCT3', 'CCT4', 'HSP90AB1', 'CTNNB1', 'CCT2', 'CCT5', 'CCT8', 'HSP90AA1']</t>
+          <t>['ALDH3A1', 'BIRC3', 'DKC1', 'NFKBIE', 'CALM2', 'XRCC5', 'MYL12B', 'TRAM1', 'CHP1', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'TKT', 'GCNT3', 'GAL', 'FKBP11', 'TUBA1A', 'TP53I3', 'LMO7', 'AIMP2', 'MORC4', 'VDAC3', 'CCT7', 'ID3', 'RAB3B', 'ATXN10', 'UNC50', 'LOXL2', 'NDUFC2', 'SUCLG1', 'NDRG1', 'CDC42', 'CCT4', 'HMMR', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EIF2S3', 'EREG', 'ANXA2', 'LMNA', 'ARL6IP1', 'TNRC6B', 'UTP18', 'SFN', 'EIF1AY', 'COL5A2', 'EIF3D', 'PLK2', 'NTS', 'GLRX', 'AKR1C3', 'CA8', 'CTNNBL1', 'AKAP12', 'ANXA1', 'SKIL', 'TUBA4A', 'NPTX1', 'MFSD12', 'DUSP5', 'SFRP1', 'DHRS3', 'RND3', 'HMOX1', 'JADE1', 'MZT1', 'ASPM', 'FAM64A', 'ANP32A', 'FOS', 'GAL3ST1', 'RPL39', 'F12', 'NRDC', 'YARS', 'FSTL3', 'RPL41', 'MAP1LC3B', 'MARCKSL1', 'CKS1B', 'S100A6', 'MESP1', 'TMEM92', 'CAPN2', 'GIGYF1', 'NPM1', 'TMSB10', 'RBM8A', 'REXO2', 'DUSP1', 'REEP5', 'MGLL', 'PHGDH', 'ANTXR1', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'ITGA3', 'HSPD1', 'ZFAS1', 'SMOX', 'LXN', 'GPRC5A', 'PPP1R14A', 'LY6K', 'PCSK1N', 'DOK4', 'CDC123', 'DDX10', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'DHRS7', 'SMIM6', 'SH3BGRL3', 'CD24', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'EIF3M', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'CNFN', 'KANK1', 'S100A10', 'RAB10', 'KYNU', 'AKR1C2', 'SLC12A2', 'CAPG', 'SMIM14', 'EMC7', 'GSN', 'HOMER3', 'CCT3', 'NAMPT', 'TPPP3', 'AURKB', 'PLAUR', 'LGMN', 'GPX2', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'FOSL1', 'NPC2', 'PHACTR2', 'UTP6', 'PPP1R15A', 'FSCN1', 'INA', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'PLAU', 'CTSH', 'PRPS2', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'ALDH1A1', 'ITGB5', 'ZNF622', 'PTRH2', 'SPP1', 'ZFP36L2', 'DDX39A', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'TOP2A', 'EIF4EBP1', 'RAP2B', 'ALDH2', 'RPS27', 'AGR2', 'PPID', 'ASF1A', 'S100A3', 'LDHB', 'PUS1', 'CDC25B', 'RAD51C', 'LBH', 'ARHGAP29', 'ACTB', 'RAI14', 'CTNNAL1', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'ALG8', 'MAP1B', 'TOB1', 'SDHB', 'LACTB2', 'TOR1AIP2', 'INSIG1', 'NUPR1', 'TMPO', 'NDUFA12', 'PLK1', 'CDC42EP1', 'ZFP36L1', 'PRSS23', 'DNMBP', 'HSPE1', 'CTTN', 'B2M', 'RRS1', 'ACAT2', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'RIPK2', 'ACAT1', 'NOC3L', 'TIMP2', 'UQCRQ', 'LGALS1', 'MNS1', 'SLC16A3', 'PA2G4', 'PIR', 'CD68', 'CYP1B1', 'COX7B', 'LRRC75A', 'SLC27A2', 'TXN', 'TESC', 'CYBA', 'GINS2', 'AURKA', 'ZFP36', 'REEP4', 'CD9', 'ATP1B3', 'MMD', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RAP1GAP', 'CYB5B', 'SPATS2', 'HES4', 'RMI2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'STK17A', 'ANKRD1', 'NANS', 'TAGLN2', 'FA2H', 'SNRPF', 'RRM2', 'SERPINE2', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'SAT1', 'NUF2', 'INO80C', 'TGFBI', 'SLC35F6', 'DNAJC3', 'IMMP2L', 'RPL28', 'PDLIM5', 'GCLC', 'RHOD', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'ACTG1', 'RPS12', 'ISG20', 'VAMP8', 'NEAT1', 'CTSL', 'CDCA3', 'BASP1', 'SULT2B1', 'TEAD4', 'OAS1', 'DPM1', 'CCNB1', 'GTPBP4', 'RPL21', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'SLC7A5', 'RILP', 'INHBB', 'MUC5AC', 'ODC1', 'CAV1', 'CRIP1', 'PDXK', 'PPA2', 'RPL38', 'MT2A', 'GOLIM4', 'HMGCS1', 'RPS24', 'SMC1A', 'S100A4', 'GADD45B', 'PHLDA2', 'PRAME', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'LAPTM4A', 'SET', 'GLRX3', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'AXL', 'PCNA', 'AMIGO2', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'COX7C', 'PIF1', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'TUBA1C', 'GSTO1', 'CCNB2', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'RPL31', 'CRIP2', 'BIRC5', 'NUCKS1', 'PMEPA1', 'CNIH4', 'TALDO1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'MKI67', 'NNMT', 'ELF3', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'UCP2', 'HSPA1A', 'HACD3', 'TK1', 'PPP3CA', 'FHL2', 'IGFBP3', 'HMGB3', 'CDC20', 'INPP1', 'KLF6', 'KRT18', 'MUC3A', 'ORMDL2', 'ECH1', 'MYL12A', 'S100A11', 'FEN1', 'TUBA1B', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IMP'], ['IDA'], ['ISS', 'IEA'], ['IMP'], ['IMP'], ['IMP'], ['IDA', 'TAS']]</t>
+          <t>[['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IC', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -4408,42 +4408,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GO:0005515</t>
+          <t>GO:0140662</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>protein binding</t>
+          <t>ATP-dependent protein folding chaperone</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.03749000350053195</v>
+        <v>0.02697572631055998</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>"Binding to a protein." [GOC:go_curators]</t>
+          <t>"Binding to a protein or a protein-containing complex to assist the protein folding process, driven by ATP hydrolysis." [PMID:27365453]</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2248</v>
+        <v>19</v>
       </c>
       <c r="H26" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I26" t="n">
-        <v>480</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K26" t="n">
-        <v>0.903954802259887</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2135231316725979</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -4452,17 +4452,17 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>['GO:0005488']</t>
+          <t>['GO:0044183', 'GO:0140657']</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'TMSB10', 'GPX1', 'RBM8A', 'NUCKS1', 'GLRX', 'GSN', 'AKR1C3', 'TSFM', 'CA8', 'TM4SF1', 'CYB5B', 'CKS2', 'S100A3', 'DKC1', 'TOP2A', 'GAL', 'TMSB4X', 'FBXO5', 'EMC7', 'MAP1B', 'DDX21', 'EREG', 'MARCKSL1', 'MCM7', 'HSPA2', 'CCND3', 'HPCAL1', 'PLRG1', 'ID1', 'DDIT4', 'TRIB3', 'MZT1', 'ATP1B1', 'CNIH4', 'PHLDA2', 'PKM', 'SQSTM1', 'DHRS7', 'S100A11', 'PGK1', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'UTP18', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'SMC1A', 'PRDX4', 'CDCA3', 'SERPINE1', 'TUBA1B', 'TPX2', 'EPHA2', 'GAMT', 'RAP2B', 'ID3', 'PKMYT1', 'RRM2', 'NDUFA9', 'EIF3M', 'CHORDC1', 'CYP1B1', 'PRSS3', 'AKAP12', 'INSIG1', 'UBE2S', 'TOB1', 'RARRES1', 'TK1', 'NRDC', 'TOR1AIP2', 'CD55', 'RPS27', 'NUPR1', 'OSGIN1', 'CCNB2', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'KANK1', 'UNC50', 'PSMC2', 'SGOL1', 'CTSL', 'CYB5A', 'NOL7', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'IGFBP4', 'DUSP1', 'TP53I3', 'ITGB5', 'AKR1B10', 'NOL11', 'KPNA2', 'RMI2', 'DCBLD2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'RPL21', 'YWHAE', 'CDC123', 'LGMN', 'CCDC80', 'S100A6', 'ALDH1A1', 'DCAF13', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'CAV2', 'ASF1A', 'BLVRB', 'MDK', 'TRAM1', 'ODC1', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SULT2B1', 'SLC35F6', 'HMGB2', 'RAB3B', 'SFRP1', 'BIRC3', 'EIF1AY', 'LGALS3', 'UBE2C', 'MYL6', 'MMD', 'B4GALT1', 'FOSL1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'SAT1', 'AHNAK', 'TIMP1', 'MYL12B', 'PSMD7', 'MT2A', 'LXN', 'ACAT1', 'SERPINB1', 'RAI14', 'CCDC34', 'HMGCS1', 'PDLIM7', 'MGLL', 'SNRPF', 'FGFBP1', 'CTTN', 'CES1', 'PDLIM5', 'LAPTM4A', 'TNRC6B', 'GSTO1', 'VAMP8', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'ZNF622', 'CBX6', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOMER3', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'MORC4', 'ANXA4', 'KIF23', 'PTPRS', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'ANKRD40', 'NDRG1', 'CAPN2', 'PBDC1', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'ITGA3', 'EMP3', 'CRIM1', 'REEP5', 'NDUFC2', 'TMEM54', 'PDHB', 'DYNLL1', 'LITAF', 'HMGB3', 'BTG1', 'TALDO1', 'EEF1A1', 'MESP1', 'HACD3', 'MAP1LC3B', 'RPS12', 'SMIM14', 'TMPO', 'PAQR5', 'FSCN1', 'CCNB1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ADM', 'METRN', 'ITGB1', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CDCA5', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'EIF2S3', 'OSGIN2', 'PMEPA1', 'RAD21', 'CD68', 'SUCLG1', 'UPK1B', 'PRSS23', 'SERPINE2', 'INPP1', 'GADD45B', 'FOS', 'AIMP2', 'RPL37A', 'CSRP1', 'HMOX1', 'ALG8', 'KRT8', 'CEBPB', 'LMNA', 'CTNNB1', 'EBNA1BP2', 'SSB', 'INA', 'CTSH', 'REEP4', 'ALDH3A1', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'GINS2', 'TUBB', 'CENPF', 'INHBB', 'SLC12A2', 'SLC16A3', 'TEAD4', 'NOLC1', 'ATP1B3', 'KRT81', 'GLRX3', 'FN1', 'DUSP5', 'ZFP36', 'ANP32A', 'COX7B', 'CDK1', 'FEN1', 'PMP22', 'DDX10', 'AURKA', 'RPL41', 'CD44', 'CCL2', 'PSMD14', 'OAS1', 'TPPP3', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'ARHGAP29', 'PHACTR2', 'UQCRC2', 'PTPRF', 'NQO1', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'PCNA', 'ANTXR1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'APOBEC3C', 'PLAUR', 'C1orf56', 'PRPS2', 'DNMBP', 'RND3', 'MKI67', 'RPL38', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'PRAME', 'CENPA', 'SLBP', 'TNFRSF12A', 'HNRNPH1', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'GPX3', 'CXCL5', 'GIGYF1', 'LMO7', 'CD70', 'BCL2L1', 'STC2', 'CDC42EP1', 'SPP1', 'CD63', 'S100A4', 'S100A2', 'IGFBP7', 'UBR4', 'CRIP2', 'IMMP2L', 'NAMPT', 'ORMDL2', 'CKS1B', 'CCT8', 'HSP90B1', 'TM4SF4', 'HES4', 'MFSD12', 'F12', 'AP1S2', 'AMIGO2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'HSPE1', 'RPL28', 'GNG11', 'SPATS2', 'EIF3D', 'RAD51C', 'EFHD2', 'MNS1', 'PYCARD', 'SFN', 'ASPM', 'MYL12A', 'ELF3', 'STMN1', 'PHGDH', 'UCHL1', 'TUBA1C', 'UTP6', 'ADA', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'CTNNAL1', 'PTTG1', 'RAP1GAP', 'TESC', 'AHNAK2', 'PPA2', 'VIM', 'DOK4', 'NRP2', 'HMMR', 'CNFN', 'FA2H', 'PRMT1', 'MSH6', 'SET', 'PCED1B', 'AURKB', 'CTNNBL1', 'RSPO3', 'CD24', 'AVPI1', 'DDX39A', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'IGFBP6', 'S100A16', 'ZFP36L2', 'S100A10', 'ACAT2', 'CXCL3', 'NPC2', 'SLC27A2', 'B2M', 'GCLC', 'MRPS22', 'INSL4', 'ATXN10', 'PRDX1', 'PLK2', 'PIR', 'RPS24', 'SLC4A7', 'KCNMA1', 'CDC42', 'UHRF1']</t>
+          <t>['CCT7', 'CCT4', 'HSPD1', 'CCT3', 'CCT5', 'CCT2', 'HSPA8', 'CCT8', 'HSPA5', 'HSPA2', 'HSP90AA1', 'HSP90AB1', 'HSP90B1', 'HSPA1A']</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>[['IDA', 'IPI', 'IBA'], ['IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IMP'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'TAS'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI', 'HDA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI'], ['IPI', 'HDA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IC', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['NAS'], ['IEA'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IPI', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IPI', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IGI', 'ISS', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IBA', 'NAS'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'TAS', 'NAS'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI'], ['IPI', 'HDA', 'IBA'], ['IDA', 'IPI'], ['IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'HDA'], ['IPI', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'NAS'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'TAS'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI'], ['IPI', 'IBA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI'], ['IPI', 'ISS', 'IBA', 'IC', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'HDA'], ['IBA'], ['IPI', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IEA'], ['IPI'], ['EXP', 'IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA'], ['IPI'], ['IPI', 'IBA', 'NAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IBA', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IMP'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'HDA'], ['IPI'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IDA', 'IPI'], ['IEA'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['EXP', 'IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'ISS'], ['IPI', 'IEA'], ['IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'TAS'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IEA'], ['IPI', 'HDA', 'IEA'], ['IPI', 'IEA'], ['IEA'], ['IDA', 'IPI'], ['IPI'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IDA', 'IPI', 'IMP', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IPI', 'HDA', 'IBA'], ['IPI', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'TAS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'IC'], ['IPI'], ['IPI', 'IEA'], ['IPI', 'HDA', 'IBA', 'IEA'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IEA'], ['IPI'], ['IPI'], ['IPI', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IPI', 'IEA'], ['IPI', 'HDA'], ['IPI'], ['IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI'], ['IPI', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI'], ['HDA'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI', 'ISS'], ['IPI', 'IEA'], ['IPI', 'IEA'], ['IPI'], ['IPI', 'ISS'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'TAS', 'NAS'], ['IPI'], ['IPI'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI'], ['IPI', 'IBA', 'TAS', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI', 'IEA'], ['IBA'], ['IPI'], ['IDA', 'IPI', 'IMP', 'ISS', 'IBA'], ['IPI', 'TAS'], ['IPI', 'IMP', 'IBA', 'TAS', 'IEA'], ['IPI', 'IBA', 'IEA'], ['IPI'], ['IDA', 'IPI', 'IBA'], ['IPI'], ['ISS', 'IBA', 'IEA'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['IPI'], ['TAS', 'IEA'], ['IPI'], ['IPI', 'HDA', 'IEA'], ['IDA', 'IPI', 'IEA'], ['IPI'], ['ISS'], ['IPI'], ['IDA', 'IPI'], ['IDA', 'IPI', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IEA']]</t>
+          <t>[['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
@@ -4474,42 +4474,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GO:0022414</t>
+          <t>GO:0010833</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>reproductive process</t>
+          <t>telomere maintenance via telomere lengthening</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.03783692678039494</v>
+        <v>0.03479310443781279</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>"A biological process that directly contributes to the process of producing new individuals by one or two organisms. The new individuals inherit some proportion of their genetic material from the parent or parents." [GOC:dph, GOC:isa_complete]</t>
+          <t>"Any process that contributes to the maintenance of proper telomeric length and structure by affecting and monitoring the activity of telomeric proteins and lengthening the telomeric DNA." [GOC:dph, GOC:tb]</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="H27" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I27" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1638418079096045</v>
+        <v>0.02443609022556391</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3140794223826715</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -4518,17 +4518,17 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>['GO:0008150']</t>
+          <t>['GO:0000723']</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>['AKR1C3', 'CKS2', 'TOP2A', 'FBXO5', 'EREG', 'HSPA2', 'SMC1A', 'PRDX4', 'GAMT', 'PKMYT1', 'CYP1B1', 'NUPR1', 'CCNB2', 'UBB', 'SGOL1', 'SKIL', 'DUSP1', 'TERF1', 'DCAF13', 'MDK', 'EGR1', 'HMGB2', 'SFRP1', 'BIRC3', 'B4GALT1', 'FOSL1', 'TIMP1', 'RAI14', 'CCDC34', 'BASP1', 'TUBB4B', 'ANXA1', 'CAPN2', 'CCT7', 'CCT3', 'CCT4', 'ITGA3', 'DYNLL1', 'PAQR5', 'PLK1', 'ADM', 'ITGB1', 'AXL', 'CD9', 'CTSB', 'HSPA8', 'OSGIN2', 'RAD21', 'SERPINE2', 'FOS', 'KRT8', 'CEBPB', 'CTNNB1', 'CCT2', 'CDC20', 'INHBB', 'TEAD4', 'CDK1', 'AURKA', 'GAL3ST1', 'LY6K', 'TPPP3', 'NUF2', 'CRIP1', 'PCNA', 'VDAC3', 'CCT5', 'RAN', 'MFGE8', 'BCL2L1', 'STC2', 'SPP1', 'IGFBP7', 'IMMP2L', 'CCT8', 'CA12', 'TUBA1A', 'RAD51C', 'MNS1', 'ASPM', 'UCHL1', 'ADA', 'PTTG1', 'MSH6', 'CDC25B', 'KRT19', 'BIRC5']</t>
+          <t>['DKC1', 'XRCC5', 'CCT7', 'CCT4', 'TERF1', 'CCT3', 'CCT5', 'CCT2', 'CTNNB1', 'CCT8', 'HSP90AA1', 'HSP90AB1', 'PIF1']</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[['IEP'], ['IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IBA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IMP', 'IEA'], ['IEA'], ['ISS'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IMP'], ['IEA'], ['IMP', 'IEA'], ['ISS'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IMP', 'NAS', 'IEA'], ['ISS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['IBA'], ['IMP', 'ISS', 'IEA'], ['IBA'], ['IEP'], ['IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IBA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IEA']]</t>
+          <t>[['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IMP', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS'], ['IMP', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.04053057620695748</v>
+        <v>0.03677620743434742</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -4560,22 +4560,22 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1989</v>
+        <v>2000</v>
       </c>
       <c r="H28" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I28" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J28" t="n">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8210922787193974</v>
+        <v>0.825187969924812</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2192056309703369</v>
+        <v>0.2195</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>['ACTG1', 'MUC5AC', 'TMSB10', 'GPX1', 'RBM8A', 'NUCKS1', 'GLRX', 'GSN', 'AKR1C3', 'TSFM', 'CYB5B', 'S100A3', 'DKC1', 'TOP2A', 'GAL', 'TMSB4X', 'FBXO5', 'EMC7', 'MAP1B', 'DDX21', 'NOC3L', 'EREG', 'MARCKSL1', 'MCM7', 'HSPA2', 'CCND3', 'PLRG1', 'ID1', 'DDIT4', 'TRIB3', 'MZT1', 'CNIH4', 'PKM', 'SQSTM1', 'DHRS7', 'S100A11', 'ARHGAP11A', 'TGFBI', 'LGALS1', 'EIF3E', 'PSMA4', 'COTL1', 'DHRS3', 'UTP18', 'ID2', 'CCNA2', 'PTRH2', 'PSMC1', 'SMC1A', 'PRDX4', 'SERPINE1', 'TUBA1B', 'TPX2', 'GAMT', 'RAP2B', 'ID3', 'PKMYT1', 'RRM2', 'NDUFA9', 'CYP1B1', 'PRSS3', 'AKAP12', 'INSIG1', 'UBE2S', 'TOB1', 'GOLIM4', 'TK1', 'NRDC', 'TOR1AIP2', 'CD55', 'RPS27', 'NUPR1', 'CCNB2', 'UBB', 'JADE1', 'SLC3A2', 'KLF6', 'KANK1', 'UNC50', 'PSMC2', 'SGOL1', 'CTSL', 'CYB5A', 'PGD', 'NOL7', 'KRT18', 'TAGLN2', 'HLA-A', 'SKIL', 'IGFBP4', 'DUSP1', 'ITGB5', 'AKR1B10', 'NOL11', 'ALDH2', 'KPNA2', 'RMI2', 'CAV1', 'CACYBP', 'TERF1', 'IGFBP3', 'MTHFD2', 'RPL21', 'YWHAE', 'LGMN', 'S100A6', 'DCAF13', 'DNAJC3', 'TIMP2', 'PCSK1N', 'ENO1', 'PPP1R7', 'TUBA4A', 'CAV2', 'ASF1A', 'BLVRB', 'TRAM1', 'CALB2', 'ZFAS1', 'TXNRD1', 'ORC5', 'EGR1', 'NFKBIE', 'SULT2B1', 'SLC35F6', 'HMGB2', 'RAB3B', 'BIRC3', 'LGALS3', 'RPL39', 'UBE2C', 'MYL6', 'MMD', 'B4GALT1', 'FOSL1', 'NEAT1', 'UBC', 'ACTB', 'UPP1', 'NPM1', 'AHNAK', 'TIMP1', 'MYL12B', 'PSMD7', 'MT2A', 'ACAT1', 'NPTX1', 'SERPINB1', 'RAI14', 'PIF1', 'PDLIM7', 'MGLL', 'SNRPF', 'CTTN', 'CES1', 'PDLIM5', 'UQCRQ', 'LAPTM4A', 'TNRC6B', 'VAMP8', 'SRP54', 'SLPI', 'ANKRD1', 'MYBL2', 'CAPZA1', 'PDXK', 'NTS', 'KRT7', 'ZNF622', 'CBX6', 'PSMC4', 'NDUFA12', 'BASP1', 'XRCC5', 'CPLX2', 'TUBB4B', 'RPL31', 'HOXB8', 'KYNU', 'RAB10', 'TSC22D1', 'ANXA1', 'MORC4', 'ANXA4', 'KIF23', 'PTPRS', 'ABCG2', 'RPS18', 'CDKN2D', 'LACTB2', 'PPID', 'INO80C', 'NDRG1', 'IRF2BP2', 'CAPN2', 'PA2G4', 'CCT7', 'CCT3', 'CCND1', 'FHL2', 'HILPDA', 'CCT4', 'REEP5', 'NDUFC2', 'PDHB', 'DYNLL1', 'LITAF', 'HMGB3', 'BTG1', 'TALDO1', 'EEF1A1', 'MESP1', 'HACD3', 'MAP1LC3B', 'RPS12', 'SMIM14', 'TMPO', 'FSCN1', 'CCNB1', 'PTP4A1', 'RIPK2', 'HSP90AB1', 'SH3BGRL3', 'PLK1', 'ITGB1', 'ARL6IP1', 'AXL', 'UCP2', 'S100A13', 'CDCA5', 'FSTL3', 'CD9', 'HSPA1A', 'CTSB', 'HSPD1', 'FAM64A', 'TSPAN14', 'LOXL2', 'HSPA8', 'PMEPA1', 'RAD21', 'CD68', 'SUCLG1', 'PRSS23', 'SERPINE2', 'GADD45B', 'FOS', 'AIMP2', 'RPL37A', 'CSRP1', 'NUDT19', 'HMOX1', 'FKBP11', 'ALG8', 'KRT8', 'CEBPB', 'GPX2', 'LMNA', 'CTNNB1', 'PUS1', 'EBNA1BP2', 'SSB', 'INA', 'CTSH', 'REEP4', 'ALDH3A1', 'CCT2', 'RRS1', 'SDHB', 'CDC20', 'CYBA', 'GINS2', 'TUBB', 'CENPF', 'SLC12A2', 'SLC16A3', 'TEAD4', 'NOLC1', 'ATP1B3', 'KRT81', 'GLRX3', 'FN1', 'DUSP5', 'ZFP36', 'ANP32A', 'COX7B', 'CDK1', 'FEN1', 'DDX10', 'AURKA', 'RPL41', 'UQCR11', 'CD44', 'PSMD14', 'GAL3ST1', 'OAS1', 'LY6K', 'REXO2', 'TPPP3', 'NAA15', 'NUP37', 'NUF2', 'GTPBP4', 'PPP1R15A', 'PHACTR2', 'UQCRC2', 'NQO1', 'GPRC5A', 'PLAU', 'LBH', 'ANXA2', 'EIF4EBP1', 'AKR1B1', 'PCNA', 'ANTXR1', 'GABRA5', 'ZFP36L1', 'TKT', 'TXN', 'PPP3CA', 'APOBEC3C', 'PLAUR', 'DNMBP', 'RND3', 'MKI67', 'RPL38', 'RPS28', 'VDAC3', 'PPP1CB', 'HSPA5', 'YARS', 'CCT5', 'PRAME', 'CENPA', 'SLBP', 'SMOX', 'HNRNPH1', 'AGR2', 'SLC7A5', 'COL5A2', 'RAN', 'NCL', 'MFGE8', 'HMGA1', 'LMO7', 'BCL2L1', 'STC2', 'CDC42EP1', 'SPP1', 'CD63', 'S100A4', 'IGFBP7', 'UBR4', 'MUC3A', 'IMMP2L', 'NAMPT', 'ORMDL2', 'CKS1B', 'CCT8', 'HSP90B1', 'HES4', 'MFSD12', 'F12', 'AP1S2', 'AMIGO2', 'CAPG', 'RILP', 'ATF4', 'EIF4A3', 'GCNT3', 'ECH1', 'RHOD', 'HSP90AA1', 'TUBA1A', 'LDHA', 'TMEM92', 'HSPE1', 'RPL28', 'RAD51C', 'MNS1', 'PYCARD', 'SFN', 'ASPM', 'MYL12A', 'ELF3', 'STMN1', 'UCHL1', 'TUBA1C', 'UTP6', 'ADA', 'DPM1', 'TRAPPC6A', 'COX7C', 'CHP1', 'CTNNAL1', 'PTTG1', 'RAP1GAP', 'TESC', 'STK17A', 'AHNAK2', 'PPA2', 'RPS29', 'VIM', 'HMMR', 'FA2H', 'PRMT1', 'MSH6', 'SET', 'AURKB', 'CTNNBL1', 'CD24', 'DDX39A', 'PSMA3', 'CDC25B', 'LDHB', 'RIN2', 'KRT19', 'CLU', 'BIRC5', 'ISG20', 'S100A16', 'ZFP36L2', 'S100A10', 'ACAT2', 'NPC2', 'SLC27A2', 'B2M', 'GCLC', 'MRPS22', 'ATXN10', 'PRDX1', 'PLK2', 'PIR', 'RPS24', 'CDC42', 'UHRF1']</t>
+          <t>['ALDH3A1', 'BIRC3', 'DKC1', 'NFKBIE', 'CALM2', 'XRCC5', 'MYL12B', 'TRAM1', 'CHP1', 'DDIT4', 'CDCA5', 'KRT19', 'CD44', 'KRT8', 'ANXA4', 'PPP1R7', 'TKT', 'GCNT3', 'GAL', 'FKBP11', 'TUBA1A', 'LMO7', 'AIMP2', 'MORC4', 'VDAC3', 'CCT7', 'ID3', 'RAB3B', 'ATXN10', 'UNC50', 'LOXL2', 'NDUFC2', 'SUCLG1', 'NDRG1', 'CDC42', 'CCT4', 'HMMR', 'UQCR11', 'AHNAK', 'LGALS3', 'PDHB', 'EREG', 'ANXA2', 'LMNA', 'ARL6IP1', 'TNRC6B', 'UTP18', 'SFN', 'COL5A2', 'PLK2', 'NTS', 'GLRX', 'AKR1C3', 'CTNNBL1', 'AKAP12', 'ANXA1', 'SKIL', 'TUBA4A', 'NPTX1', 'MFSD12', 'DUSP5', 'DHRS3', 'RND3', 'HMOX1', 'JADE1', 'MZT1', 'ASPM', 'FAM64A', 'ANP32A', 'FOS', 'GAL3ST1', 'RPL39', 'F12', 'NRDC', 'YARS', 'FSTL3', 'RPL41', 'MAP1LC3B', 'MARCKSL1', 'CKS1B', 'S100A6', 'MESP1', 'TMEM92', 'CAPN2', 'NPM1', 'TMSB10', 'RBM8A', 'REXO2', 'DUSP1', 'REEP5', 'MGLL', 'ANTXR1', 'HILPDA', 'S100A16', 'HOXB8', 'ID1', 'UBR4', 'HSPD1', 'ZFAS1', 'SMOX', 'GPRC5A', 'LY6K', 'PCSK1N', 'DDX10', 'NQO1', 'PRMT1', 'NUDT19', 'EIF4A3', 'DHRS7', 'SMIM6', 'SH3BGRL3', 'CD24', 'PDLIM7', 'UHRF1', 'TSPAN14', 'PLRG1', 'UPP1', 'CCND1', 'ID2', 'UCHL1', 'LITAF', 'EEF1A1', 'VIM', 'TMSB4X', 'TERF1', 'TIMP1', 'DDX21', 'PKM', 'S100A13', 'UBE2C', 'CBX6', 'BTG1', 'PPP1CB', 'TRIB3', 'PTPRS', 'CES1', 'KANK1', 'S100A10', 'RAB10', 'KYNU', 'SLC12A2', 'CAPG', 'SMIM14', 'EMC7', 'GSN', 'CCT3', 'NAMPT', 'TPPP3', 'AURKB', 'PLAUR', 'LGMN', 'GPX2', 'TUBB', 'CCT5', 'CAV2', 'RAN', 'FOSL1', 'NPC2', 'PHACTR2', 'UTP6', 'PPP1R15A', 'FSCN1', 'INA', 'PSMC1', 'STMN1', 'CCT2', 'DCAF13', 'PRDX4', 'NOLC1', 'PLAU', 'CTSH', 'BLVRB', 'CALB2', 'AKR1B10', 'SLBP', 'CTNNB1', 'FN1', 'TRAPPC6A', 'ITGB5', 'ZNF622', 'PTRH2', 'SPP1', 'ZFP36L2', 'DDX39A', 'SSB', 'PGD', 'KRT7', 'CAPZA1', 'TOP2A', 'EIF4EBP1', 'RAP2B', 'ALDH2', 'RPS27', 'AGR2', 'PPID', 'ASF1A', 'S100A3', 'LDHB', 'PUS1', 'CDC25B', 'RAD51C', 'LBH', 'ACTB', 'RAI14', 'CTNNAL1', 'ORC5', 'LDHA', 'YWHAE', 'RPS29', 'PSMD7', 'MCM7', 'SGOL1', 'ALG8', 'MAP1B', 'TOB1', 'SDHB', 'LACTB2', 'TOR1AIP2', 'INSIG1', 'NUPR1', 'TMPO', 'NDUFA12', 'PLK1', 'CDC42EP1', 'ZFP36L1', 'PRSS23', 'DNMBP', 'HSPE1', 'CTTN', 'B2M', 'RRS1', 'PKMYT1', 'MFGE8', 'IGFBP7', 'KPNA2', 'RIPK2', 'ACAT1', 'NOC3L', 'TIMP2', 'UQCRQ', 'LGALS1', 'MNS1', 'SLC16A3', 'PA2G4', 'PIR', 'CD68', 'CYP1B1', 'COX7B', 'SLC27A2', 'TXN', 'TESC', 'CYBA', 'GINS2', 'AURKA', 'ZFP36', 'REEP4', 'CD9', 'ATP1B3', 'MMD', 'NAA15', 'CDKN2D', 'B4GALT1', 'CEBPB', 'HSPA8', 'PSMA3', 'CTSB', 'RAP1GAP', 'CYB5B', 'HES4', 'RMI2', 'SQSTM1', 'SERPINB1', 'AHNAK2', 'STK17A', 'ANKRD1', 'TAGLN2', 'FA2H', 'SNRPF', 'RRM2', 'SERPINE2', 'CENPA', 'PYCARD', 'GAMT', 'CCNA2', 'CSRP1', 'RPS18', 'APOBEC3C', 'SRP54', 'NUF2', 'INO80C', 'TGFBI', 'SLC35F6', 'DNAJC3', 'IMMP2L', 'RPL28', 'PDLIM5', 'GCLC', 'RHOD', 'NDUFA9', 'EBNA1BP2', 'SERPINE1', 'ACTG1', 'RPS12', 'ISG20', 'VAMP8', 'NEAT1', 'CTSL', 'BASP1', 'SULT2B1', 'TEAD4', 'OAS1', 'DPM1', 'CCNB1', 'GTPBP4', 'RPL21', 'UQCRC2', 'KIF23', 'FBXO5', 'CLU', 'TPX2', 'NOL11', 'SLC7A5', 'RILP', 'MUC5AC', 'CAV1', 'PDXK', 'PPA2', 'RPL38', 'MT2A', 'GOLIM4', 'RPS24', 'SMC1A', 'S100A4', 'GADD45B', 'PRAME', 'CCT8', 'RIN2', 'TXNRD1', 'CD55', 'HSPA5', 'DYNLL1', 'PRDX1', 'KRT81', 'HMGB2', 'MYL6', 'PSMA4', 'SLPI', 'MSH6', 'EGR1', 'EIF3E', 'NOL7', 'MYBL2', 'PTTG1', 'HSPA2', 'ENO1', 'NUP37', 'PSMD14', 'MRPS22', 'HLA-A', 'ADM', 'UBB', 'UBC', 'BCL2L1', 'GPX1', 'CD63', 'LAPTM4A', 'SET', 'GLRX3', 'TSFM', 'CDK1', 'UBE2S', 'RPS28', 'PSMC2', 'COTL1', 'AKR1B1', 'NCL', 'ADA', 'AXL', 'PCNA', 'AMIGO2', 'HSP90AA1', 'PGK1', 'TUBB4B', 'HSP90AB1', 'IRF2BP2', 'CYB5A', 'COX7C', 'PIF1', 'GABRA5', 'AP1S2', 'HSP90B1', 'ARHGAP11A', 'TUBA1C', 'CCNB2', 'IGFBP4', 'CENPF', 'HNRNPH1', 'ABCG2', 'RPL31', 'BIRC5', 'NUCKS1', 'PMEPA1', 'CNIH4', 'TALDO1', 'STC2', 'SLC3A2', 'MTHFD2', 'CACYBP', 'MKI67', 'ELF3', 'ATF4', 'PTP4A1', 'HMGA1', 'PRSS3', 'RAD21', 'ITGB1', 'CCND3', 'PSMC4', 'UCP2', 'HSPA1A', 'HACD3', 'TK1', 'PPP3CA', 'FHL2', 'IGFBP3', 'HMGB3', 'CDC20', 'KLF6', 'KRT18', 'MUC3A', 'ORMDL2', 'ECH1', 'MYL12A', 'S100A11', 'FEN1', 'TUBA1B', 'TSC22D1', 'RPL37A', 'CPLX2']</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>[['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA'], ['ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['ISS', 'IBA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HTP'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['EXP', 'NAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IC', 'IEA']]</t>
+          <t>[['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'NAS', 'IEA'], ['ISA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IC', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IC', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IGI', 'IBA', 'TAS', 'IC', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
